--- a/scripts/codemagic-ci/testing/Regression-Test-Plan-Template-Android-QA.xlsx
+++ b/scripts/codemagic-ci/testing/Regression-Test-Plan-Template-Android-QA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbryant/UCSD/campusmobile/scripts/codemagic-ci/testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{041A76AF-137C-F44C-B3D3-7C50DC57EB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{370155BA-A1B0-43E7-BC11-1FBA5363962E}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{041A76AF-137C-F44C-B3D3-7C50DC57EB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47489CBE-3C84-4305-971F-C822E15196AB}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
   <si>
     <t xml:space="preserve">Regression Test Plan - ${APP_VERSION} - ${BUILD_ENV}  </t>
   </si>
@@ -213,30 +213,6 @@
   </si>
   <si>
     <t>Platform Duty Cycle - ESR iPaaS - UCSD Collab (atlassian.net)</t>
-  </si>
-  <si>
-    <t>Native Scanner (not logged in) link navigates to Profile SSO Login</t>
-  </si>
-  <si>
-    <t>Native Scanner (logged in) link launches Scandit Native Scanner</t>
-  </si>
-  <si>
-    <t>Native Scanner Code128 submission successful and verified</t>
-  </si>
-  <si>
-    <t>Native Scanner Code128 submission failed - duplicate barcode</t>
-  </si>
-  <si>
-    <t>Native Scanner Code128 submission failed - invalid barcode</t>
-  </si>
-  <si>
-    <t>Native Scanner 2D submission successful and verified</t>
-  </si>
-  <si>
-    <t>Native Scanner 2D submission failed - duplicate barcode</t>
-  </si>
-  <si>
-    <t>Native Scanner 2D submission failed - invalid barcode</t>
   </si>
   <si>
     <t>MyStudentChart card launches device browser, loads MyStudentChart login site</t>
@@ -992,7 +968,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:V982" headerRowCount="0" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:V974" headerRowCount="0" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="21"/>
     <tableColumn id="6" xr3:uid="{998C2409-DF77-488B-87C8-719F18DC5812}" name="Column2" dataDxfId="20"/>
@@ -1228,7 +1204,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:V982"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.1" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="96.5703125" style="8" customWidth="1"/>
     <col min="2" max="2" width="28.5703125" style="26" customWidth="1"/>
@@ -1863,7 +1839,7 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
     </row>
-    <row r="23" spans="1:22" ht="14.25">
+    <row r="23" spans="1:22" ht="14.25" outlineLevel="1">
       <c r="A23" s="7" t="s">
         <v>47</v>
       </c>
@@ -1889,13 +1865,14 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
     </row>
-    <row r="24" spans="1:22" ht="14.25">
+    <row r="24" spans="1:22" ht="14.25" outlineLevel="1">
       <c r="A24" s="7" t="s">
         <v>48</v>
       </c>
       <c r="B24" s="34"/>
       <c r="C24" s="34"/>
       <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1914,13 +1891,14 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
     </row>
-    <row r="25" spans="1:22" ht="14.25">
+    <row r="25" spans="1:22" ht="14.25" outlineLevel="1">
       <c r="A25" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="34"/>
       <c r="C25" s="34"/>
       <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -1939,13 +1917,14 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
     </row>
-    <row r="26" spans="1:22" ht="14.25">
+    <row r="26" spans="1:22" ht="14.25" outlineLevel="1">
       <c r="A26" s="7" t="s">
         <v>50</v>
       </c>
       <c r="B26" s="34"/>
       <c r="C26" s="34"/>
       <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1964,13 +1943,14 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
     </row>
-    <row r="27" spans="1:22" ht="14.25">
+    <row r="27" spans="1:22" ht="14.25" outlineLevel="1">
       <c r="A27" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
       <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1989,13 +1969,14 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" spans="1:22" ht="14.25">
+    <row r="28" spans="1:22" ht="14.25" outlineLevel="1">
       <c r="A28" s="7" t="s">
         <v>52</v>
       </c>
       <c r="B28" s="34"/>
       <c r="C28" s="34"/>
       <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -2014,16 +1995,16 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" spans="1:22" ht="14.25">
+    <row r="29" spans="1:22" ht="14.25" outlineLevel="1">
       <c r="A29" s="7" t="s">
         <v>53</v>
       </c>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
-      <c r="D29" s="1"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -2039,13 +2020,14 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
     </row>
-    <row r="30" spans="1:22" ht="14.25">
+    <row r="30" spans="1:22" ht="14.25" outlineLevel="1">
       <c r="A30" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B30" s="34"/>
       <c r="C30" s="34"/>
       <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -2117,11 +2099,11 @@
       <c r="V32" s="1"/>
     </row>
     <row r="33" spans="1:22" ht="14.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -2143,7 +2125,7 @@
       <c r="V33" s="1"/>
     </row>
     <row r="34" spans="1:22" ht="14.25">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="8" t="s">
         <v>58</v>
       </c>
       <c r="B34" s="34"/>
@@ -2169,7 +2151,7 @@
       <c r="V34" s="1"/>
     </row>
     <row r="35" spans="1:22" ht="14.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B35" s="34"/>
@@ -2195,7 +2177,7 @@
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="14.25">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="8" t="s">
         <v>60</v>
       </c>
       <c r="B36" s="34"/>
@@ -2221,15 +2203,16 @@
       <c r="V36" s="1"/>
     </row>
     <row r="37" spans="1:22" ht="14.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="8" t="s">
         <v>61</v>
       </c>
       <c r="B37" s="34"/>
       <c r="C37" s="34"/>
-      <c r="D37" s="10"/>
+      <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -2246,7 +2229,7 @@
       <c r="V37" s="1"/>
     </row>
     <row r="38" spans="1:22" ht="14.25">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="8" t="s">
         <v>62</v>
       </c>
       <c r="B38" s="34"/>
@@ -2272,7 +2255,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="14.25">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="8" t="s">
         <v>63</v>
       </c>
       <c r="B39" s="34"/>
@@ -2298,7 +2281,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="14.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="8" t="s">
         <v>64</v>
       </c>
       <c r="B40" s="34"/>
@@ -2324,7 +2307,7 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="14.25">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="31" t="s">
         <v>65</v>
       </c>
       <c r="B41" s="36"/>
@@ -2350,7 +2333,7 @@
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="14.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>66</v>
       </c>
       <c r="B42" s="34"/>
@@ -2376,7 +2359,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="14.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>67</v>
       </c>
       <c r="B43" s="34"/>
@@ -2402,7 +2385,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="14.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>68</v>
       </c>
       <c r="B44" s="34"/>
@@ -2428,11 +2411,11 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="14.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="36"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -2454,7 +2437,7 @@
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="7" t="s">
         <v>70</v>
       </c>
       <c r="B46" s="34"/>
@@ -2480,7 +2463,7 @@
       <c r="V46" s="1"/>
     </row>
     <row r="47" spans="1:22" ht="14.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="7" t="s">
         <v>71</v>
       </c>
       <c r="B47" s="34"/>
@@ -2506,7 +2489,7 @@
       <c r="V47" s="1"/>
     </row>
     <row r="48" spans="1:22" ht="14.25">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="7" t="s">
         <v>72</v>
       </c>
       <c r="B48" s="34"/>
@@ -2532,11 +2515,11 @@
       <c r="V48" s="1"/>
     </row>
     <row r="49" spans="1:22" ht="14.25">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -2558,11 +2541,11 @@
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="14.25">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B50" s="34"/>
-      <c r="C50" s="34"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -2584,11 +2567,11 @@
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="14.25">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="34"/>
-      <c r="C51" s="34"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="3"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -2609,12 +2592,12 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22" ht="14.25">
-      <c r="A52" s="7" t="s">
+    <row r="52" spans="1:22" ht="28.5">
+      <c r="A52" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B52" s="34"/>
-      <c r="C52" s="34"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="3"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -2636,11 +2619,9 @@
       <c r="V52" s="1"/>
     </row>
     <row r="53" spans="1:22" ht="14.25">
-      <c r="A53" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="B53" s="36"/>
-      <c r="C53" s="36"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="3"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -2662,11 +2643,9 @@
       <c r="V53" s="1"/>
     </row>
     <row r="54" spans="1:22" ht="14.25">
-      <c r="A54" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="34"/>
-      <c r="C54" s="34"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="3"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -2688,11 +2667,9 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="14.25">
-      <c r="A55" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B55" s="34"/>
-      <c r="C55" s="34"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="3"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -2714,11 +2691,9 @@
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="14.25">
-      <c r="A56" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B56" s="34"/>
-      <c r="C56" s="34"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="3"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -2740,11 +2715,9 @@
       <c r="V56" s="1"/>
     </row>
     <row r="57" spans="1:22" ht="14.25">
-      <c r="A57" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B57" s="34"/>
-      <c r="C57" s="34"/>
+      <c r="A57" s="7"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="3"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -2766,11 +2739,9 @@
       <c r="V57" s="1"/>
     </row>
     <row r="58" spans="1:22" ht="14.25">
-      <c r="A58" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B58" s="36"/>
-      <c r="C58" s="36"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="3"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
@@ -2792,9 +2763,7 @@
       <c r="V58" s="1"/>
     </row>
     <row r="59" spans="1:22" ht="14.25">
-      <c r="A59" s="24" t="s">
-        <v>83</v>
-      </c>
+      <c r="A59" s="7"/>
       <c r="B59" s="25"/>
       <c r="C59" s="3"/>
       <c r="D59" s="1"/>
@@ -2818,9 +2787,7 @@
       <c r="V59" s="1"/>
     </row>
     <row r="60" spans="1:22" ht="31.5" customHeight="1">
-      <c r="A60" s="41" t="s">
-        <v>84</v>
-      </c>
+      <c r="A60" s="7"/>
       <c r="B60" s="25"/>
       <c r="C60" s="3"/>
       <c r="D60" s="1"/>
@@ -2843,7 +2810,7 @@
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" ht="14.25">
       <c r="A61" s="7"/>
       <c r="B61" s="25"/>
       <c r="C61" s="3"/>
@@ -2867,7 +2834,7 @@
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" ht="14.25">
       <c r="A62" s="7"/>
       <c r="B62" s="25"/>
       <c r="C62" s="3"/>
@@ -2891,7 +2858,7 @@
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" ht="14.25">
       <c r="A63" s="7"/>
       <c r="B63" s="25"/>
       <c r="C63" s="3"/>
@@ -2915,7 +2882,7 @@
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" ht="14.25">
       <c r="A64" s="7"/>
       <c r="B64" s="25"/>
       <c r="C64" s="3"/>
@@ -2939,7 +2906,7 @@
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
     </row>
-    <row r="65" spans="1:22">
+    <row r="65" spans="1:22" ht="14.25">
       <c r="A65" s="7"/>
       <c r="B65" s="25"/>
       <c r="C65" s="3"/>
@@ -2963,7 +2930,7 @@
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
     </row>
-    <row r="66" spans="1:22">
+    <row r="66" spans="1:22" ht="14.25">
       <c r="A66" s="7"/>
       <c r="B66" s="25"/>
       <c r="C66" s="3"/>
@@ -2987,7 +2954,7 @@
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
     </row>
-    <row r="67" spans="1:22">
+    <row r="67" spans="1:22" ht="14.25">
       <c r="A67" s="7"/>
       <c r="B67" s="25"/>
       <c r="C67" s="3"/>
@@ -3011,7 +2978,7 @@
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:22" ht="14.25">
       <c r="A68" s="7"/>
       <c r="B68" s="25"/>
       <c r="C68" s="3"/>
@@ -3035,7 +3002,7 @@
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
     </row>
-    <row r="69" spans="1:22">
+    <row r="69" spans="1:22" ht="14.25">
       <c r="A69" s="7"/>
       <c r="B69" s="25"/>
       <c r="C69" s="3"/>
@@ -3059,7 +3026,7 @@
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:22" ht="14.25">
       <c r="A70" s="7"/>
       <c r="B70" s="25"/>
       <c r="C70" s="3"/>
@@ -3083,7 +3050,7 @@
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
     </row>
-    <row r="71" spans="1:22">
+    <row r="71" spans="1:22" ht="14.25">
       <c r="A71" s="7"/>
       <c r="B71" s="25"/>
       <c r="C71" s="3"/>
@@ -3107,7 +3074,7 @@
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:22" ht="14.25">
       <c r="A72" s="7"/>
       <c r="B72" s="25"/>
       <c r="C72" s="3"/>
@@ -3131,7 +3098,7 @@
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
     </row>
-    <row r="73" spans="1:22">
+    <row r="73" spans="1:22" ht="14.25">
       <c r="A73" s="7"/>
       <c r="B73" s="25"/>
       <c r="C73" s="3"/>
@@ -3155,7 +3122,7 @@
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
     </row>
-    <row r="74" spans="1:22">
+    <row r="74" spans="1:22" ht="14.25">
       <c r="A74" s="7"/>
       <c r="B74" s="25"/>
       <c r="C74" s="3"/>
@@ -3179,7 +3146,7 @@
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
     </row>
-    <row r="75" spans="1:22">
+    <row r="75" spans="1:22" ht="14.25">
       <c r="A75" s="7"/>
       <c r="B75" s="25"/>
       <c r="C75" s="3"/>
@@ -3203,7 +3170,7 @@
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
     </row>
-    <row r="76" spans="1:22">
+    <row r="76" spans="1:22" ht="14.25">
       <c r="A76" s="7"/>
       <c r="B76" s="25"/>
       <c r="C76" s="3"/>
@@ -3227,7 +3194,7 @@
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
     </row>
-    <row r="77" spans="1:22">
+    <row r="77" spans="1:22" ht="14.25">
       <c r="A77" s="7"/>
       <c r="B77" s="25"/>
       <c r="C77" s="3"/>
@@ -3251,7 +3218,7 @@
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
     </row>
-    <row r="78" spans="1:22">
+    <row r="78" spans="1:22" ht="14.25">
       <c r="A78" s="7"/>
       <c r="B78" s="25"/>
       <c r="C78" s="3"/>
@@ -3275,7 +3242,7 @@
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
     </row>
-    <row r="79" spans="1:22">
+    <row r="79" spans="1:22" ht="14.25">
       <c r="A79" s="7"/>
       <c r="B79" s="25"/>
       <c r="C79" s="3"/>
@@ -3299,7 +3266,7 @@
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:22" ht="14.25">
       <c r="A80" s="7"/>
       <c r="B80" s="25"/>
       <c r="C80" s="3"/>
@@ -3323,7 +3290,7 @@
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:22" ht="14.25">
       <c r="A81" s="7"/>
       <c r="B81" s="25"/>
       <c r="C81" s="3"/>
@@ -3347,7 +3314,7 @@
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
     </row>
-    <row r="82" spans="1:22">
+    <row r="82" spans="1:22" ht="14.25">
       <c r="A82" s="7"/>
       <c r="B82" s="25"/>
       <c r="C82" s="3"/>
@@ -3371,7 +3338,7 @@
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:22" ht="14.25">
       <c r="A83" s="7"/>
       <c r="B83" s="25"/>
       <c r="C83" s="3"/>
@@ -3395,7 +3362,7 @@
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:22" ht="14.25">
       <c r="A84" s="7"/>
       <c r="B84" s="25"/>
       <c r="C84" s="3"/>
@@ -3419,7 +3386,7 @@
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
     </row>
-    <row r="85" spans="1:22">
+    <row r="85" spans="1:22" ht="14.25">
       <c r="A85" s="7"/>
       <c r="B85" s="25"/>
       <c r="C85" s="3"/>
@@ -3443,7 +3410,7 @@
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
     </row>
-    <row r="86" spans="1:22">
+    <row r="86" spans="1:22" ht="14.25">
       <c r="A86" s="7"/>
       <c r="B86" s="25"/>
       <c r="C86" s="3"/>
@@ -3467,7 +3434,7 @@
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
     </row>
-    <row r="87" spans="1:22">
+    <row r="87" spans="1:22" ht="14.25">
       <c r="A87" s="7"/>
       <c r="B87" s="25"/>
       <c r="C87" s="3"/>
@@ -3491,7 +3458,7 @@
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
     </row>
-    <row r="88" spans="1:22">
+    <row r="88" spans="1:22" ht="14.25">
       <c r="A88" s="7"/>
       <c r="B88" s="25"/>
       <c r="C88" s="3"/>
@@ -3515,7 +3482,7 @@
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
     </row>
-    <row r="89" spans="1:22">
+    <row r="89" spans="1:22" ht="14.25">
       <c r="A89" s="7"/>
       <c r="B89" s="25"/>
       <c r="C89" s="3"/>
@@ -3539,7 +3506,7 @@
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
     </row>
-    <row r="90" spans="1:22">
+    <row r="90" spans="1:22" ht="14.25">
       <c r="A90" s="7"/>
       <c r="B90" s="25"/>
       <c r="C90" s="3"/>
@@ -3563,7 +3530,7 @@
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
     </row>
-    <row r="91" spans="1:22">
+    <row r="91" spans="1:22" ht="14.25">
       <c r="A91" s="7"/>
       <c r="B91" s="25"/>
       <c r="C91" s="3"/>
@@ -3587,7 +3554,7 @@
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
     </row>
-    <row r="92" spans="1:22">
+    <row r="92" spans="1:22" ht="14.25">
       <c r="A92" s="7"/>
       <c r="B92" s="25"/>
       <c r="C92" s="3"/>
@@ -3611,7 +3578,7 @@
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
     </row>
-    <row r="93" spans="1:22">
+    <row r="93" spans="1:22" ht="14.25">
       <c r="A93" s="7"/>
       <c r="B93" s="25"/>
       <c r="C93" s="3"/>
@@ -3635,7 +3602,7 @@
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
     </row>
-    <row r="94" spans="1:22">
+    <row r="94" spans="1:22" ht="14.25">
       <c r="A94" s="7"/>
       <c r="B94" s="25"/>
       <c r="C94" s="3"/>
@@ -3659,7 +3626,7 @@
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
     </row>
-    <row r="95" spans="1:22">
+    <row r="95" spans="1:22" ht="14.25">
       <c r="A95" s="7"/>
       <c r="B95" s="25"/>
       <c r="C95" s="3"/>
@@ -3683,7 +3650,7 @@
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
     </row>
-    <row r="96" spans="1:22">
+    <row r="96" spans="1:22" ht="14.25">
       <c r="A96" s="7"/>
       <c r="B96" s="25"/>
       <c r="C96" s="3"/>
@@ -3707,7 +3674,7 @@
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
     </row>
-    <row r="97" spans="1:22">
+    <row r="97" spans="1:22" ht="14.25">
       <c r="A97" s="7"/>
       <c r="B97" s="25"/>
       <c r="C97" s="3"/>
@@ -3731,7 +3698,7 @@
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
     </row>
-    <row r="98" spans="1:22">
+    <row r="98" spans="1:22" ht="14.25">
       <c r="A98" s="7"/>
       <c r="B98" s="25"/>
       <c r="C98" s="3"/>
@@ -3755,7 +3722,7 @@
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
     </row>
-    <row r="99" spans="1:22">
+    <row r="99" spans="1:22" ht="14.25">
       <c r="A99" s="7"/>
       <c r="B99" s="25"/>
       <c r="C99" s="3"/>
@@ -3779,7 +3746,7 @@
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
     </row>
-    <row r="100" spans="1:22">
+    <row r="100" spans="1:22" ht="14.25">
       <c r="A100" s="7"/>
       <c r="B100" s="25"/>
       <c r="C100" s="3"/>
@@ -3803,7 +3770,7 @@
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
     </row>
-    <row r="101" spans="1:22">
+    <row r="101" spans="1:22" ht="14.25">
       <c r="A101" s="7"/>
       <c r="B101" s="25"/>
       <c r="C101" s="3"/>
@@ -3827,7 +3794,7 @@
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
     </row>
-    <row r="102" spans="1:22">
+    <row r="102" spans="1:22" ht="14.25">
       <c r="A102" s="7"/>
       <c r="B102" s="25"/>
       <c r="C102" s="3"/>
@@ -3851,7 +3818,7 @@
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
     </row>
-    <row r="103" spans="1:22">
+    <row r="103" spans="1:22" ht="14.25">
       <c r="A103" s="7"/>
       <c r="B103" s="25"/>
       <c r="C103" s="3"/>
@@ -3875,7 +3842,7 @@
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
     </row>
-    <row r="104" spans="1:22">
+    <row r="104" spans="1:22" ht="14.25">
       <c r="A104" s="7"/>
       <c r="B104" s="25"/>
       <c r="C104" s="3"/>
@@ -3899,7 +3866,7 @@
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
     </row>
-    <row r="105" spans="1:22">
+    <row r="105" spans="1:22" ht="14.25">
       <c r="A105" s="7"/>
       <c r="B105" s="25"/>
       <c r="C105" s="3"/>
@@ -3923,7 +3890,7 @@
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
     </row>
-    <row r="106" spans="1:22">
+    <row r="106" spans="1:22" ht="14.25">
       <c r="A106" s="7"/>
       <c r="B106" s="25"/>
       <c r="C106" s="3"/>
@@ -3947,7 +3914,7 @@
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
     </row>
-    <row r="107" spans="1:22">
+    <row r="107" spans="1:22" ht="14.25">
       <c r="A107" s="7"/>
       <c r="B107" s="25"/>
       <c r="C107" s="3"/>
@@ -3971,7 +3938,7 @@
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
     </row>
-    <row r="108" spans="1:22">
+    <row r="108" spans="1:22" ht="14.25">
       <c r="A108" s="7"/>
       <c r="B108" s="25"/>
       <c r="C108" s="3"/>
@@ -3995,7 +3962,7 @@
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
     </row>
-    <row r="109" spans="1:22">
+    <row r="109" spans="1:22" ht="14.25">
       <c r="A109" s="7"/>
       <c r="B109" s="25"/>
       <c r="C109" s="3"/>
@@ -4019,7 +3986,7 @@
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
     </row>
-    <row r="110" spans="1:22">
+    <row r="110" spans="1:22" ht="14.25">
       <c r="A110" s="7"/>
       <c r="B110" s="25"/>
       <c r="C110" s="3"/>
@@ -4043,7 +4010,7 @@
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
     </row>
-    <row r="111" spans="1:22">
+    <row r="111" spans="1:22" ht="14.25">
       <c r="A111" s="7"/>
       <c r="B111" s="25"/>
       <c r="C111" s="3"/>
@@ -4067,7 +4034,7 @@
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
     </row>
-    <row r="112" spans="1:22">
+    <row r="112" spans="1:22" ht="14.25">
       <c r="A112" s="7"/>
       <c r="B112" s="25"/>
       <c r="C112" s="3"/>
@@ -4091,7 +4058,7 @@
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
     </row>
-    <row r="113" spans="1:22">
+    <row r="113" spans="1:22" ht="14.25">
       <c r="A113" s="7"/>
       <c r="B113" s="25"/>
       <c r="C113" s="3"/>
@@ -4115,7 +4082,7 @@
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
     </row>
-    <row r="114" spans="1:22">
+    <row r="114" spans="1:22" ht="14.25">
       <c r="A114" s="7"/>
       <c r="B114" s="25"/>
       <c r="C114" s="3"/>
@@ -4139,7 +4106,7 @@
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
     </row>
-    <row r="115" spans="1:22">
+    <row r="115" spans="1:22" ht="14.25">
       <c r="A115" s="7"/>
       <c r="B115" s="25"/>
       <c r="C115" s="3"/>
@@ -4163,7 +4130,7 @@
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
     </row>
-    <row r="116" spans="1:22">
+    <row r="116" spans="1:22" ht="14.25">
       <c r="A116" s="7"/>
       <c r="B116" s="25"/>
       <c r="C116" s="3"/>
@@ -4187,7 +4154,7 @@
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
     </row>
-    <row r="117" spans="1:22">
+    <row r="117" spans="1:22" ht="14.25">
       <c r="A117" s="7"/>
       <c r="B117" s="25"/>
       <c r="C117" s="3"/>
@@ -4211,7 +4178,7 @@
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
     </row>
-    <row r="118" spans="1:22">
+    <row r="118" spans="1:22" ht="14.25">
       <c r="A118" s="7"/>
       <c r="B118" s="25"/>
       <c r="C118" s="3"/>
@@ -4235,7 +4202,7 @@
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
     </row>
-    <row r="119" spans="1:22">
+    <row r="119" spans="1:22" ht="14.25">
       <c r="A119" s="7"/>
       <c r="B119" s="25"/>
       <c r="C119" s="3"/>
@@ -4259,7 +4226,7 @@
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
     </row>
-    <row r="120" spans="1:22">
+    <row r="120" spans="1:22" ht="14.25">
       <c r="A120" s="7"/>
       <c r="B120" s="25"/>
       <c r="C120" s="3"/>
@@ -4283,7 +4250,7 @@
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
     </row>
-    <row r="121" spans="1:22">
+    <row r="121" spans="1:22" ht="14.25">
       <c r="A121" s="7"/>
       <c r="B121" s="25"/>
       <c r="C121" s="3"/>
@@ -4307,7 +4274,7 @@
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
     </row>
-    <row r="122" spans="1:22">
+    <row r="122" spans="1:22" ht="14.25">
       <c r="A122" s="7"/>
       <c r="B122" s="25"/>
       <c r="C122" s="3"/>
@@ -4331,7 +4298,7 @@
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
     </row>
-    <row r="123" spans="1:22">
+    <row r="123" spans="1:22" ht="14.25">
       <c r="A123" s="7"/>
       <c r="B123" s="25"/>
       <c r="C123" s="3"/>
@@ -4355,7 +4322,7 @@
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
     </row>
-    <row r="124" spans="1:22">
+    <row r="124" spans="1:22" ht="14.25">
       <c r="A124" s="7"/>
       <c r="B124" s="25"/>
       <c r="C124" s="3"/>
@@ -4379,7 +4346,7 @@
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
     </row>
-    <row r="125" spans="1:22">
+    <row r="125" spans="1:22" ht="14.25">
       <c r="A125" s="7"/>
       <c r="B125" s="25"/>
       <c r="C125" s="3"/>
@@ -4403,7 +4370,7 @@
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
     </row>
-    <row r="126" spans="1:22">
+    <row r="126" spans="1:22" ht="14.25">
       <c r="A126" s="7"/>
       <c r="B126" s="25"/>
       <c r="C126" s="3"/>
@@ -4427,7 +4394,7 @@
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
     </row>
-    <row r="127" spans="1:22">
+    <row r="127" spans="1:22" ht="14.25">
       <c r="A127" s="7"/>
       <c r="B127" s="25"/>
       <c r="C127" s="3"/>
@@ -4451,7 +4418,7 @@
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
     </row>
-    <row r="128" spans="1:22">
+    <row r="128" spans="1:22" ht="14.25">
       <c r="A128" s="7"/>
       <c r="B128" s="25"/>
       <c r="C128" s="3"/>
@@ -4475,7 +4442,7 @@
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
     </row>
-    <row r="129" spans="1:22">
+    <row r="129" spans="1:22" ht="14.25">
       <c r="A129" s="7"/>
       <c r="B129" s="25"/>
       <c r="C129" s="3"/>
@@ -4499,7 +4466,7 @@
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
     </row>
-    <row r="130" spans="1:22">
+    <row r="130" spans="1:22" ht="14.25">
       <c r="A130" s="7"/>
       <c r="B130" s="25"/>
       <c r="C130" s="3"/>
@@ -4523,7 +4490,7 @@
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
     </row>
-    <row r="131" spans="1:22">
+    <row r="131" spans="1:22" ht="14.25">
       <c r="A131" s="7"/>
       <c r="B131" s="25"/>
       <c r="C131" s="3"/>
@@ -4547,7 +4514,7 @@
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
     </row>
-    <row r="132" spans="1:22">
+    <row r="132" spans="1:22" ht="14.25">
       <c r="A132" s="7"/>
       <c r="B132" s="25"/>
       <c r="C132" s="3"/>
@@ -4571,7 +4538,7 @@
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
     </row>
-    <row r="133" spans="1:22">
+    <row r="133" spans="1:22" ht="14.25">
       <c r="A133" s="7"/>
       <c r="B133" s="25"/>
       <c r="C133" s="3"/>
@@ -4595,7 +4562,7 @@
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
     </row>
-    <row r="134" spans="1:22">
+    <row r="134" spans="1:22" ht="14.25">
       <c r="A134" s="7"/>
       <c r="B134" s="25"/>
       <c r="C134" s="3"/>
@@ -4619,7 +4586,7 @@
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
     </row>
-    <row r="135" spans="1:22">
+    <row r="135" spans="1:22" ht="14.25">
       <c r="A135" s="7"/>
       <c r="B135" s="25"/>
       <c r="C135" s="3"/>
@@ -4643,7 +4610,7 @@
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
     </row>
-    <row r="136" spans="1:22">
+    <row r="136" spans="1:22" ht="14.25">
       <c r="A136" s="7"/>
       <c r="B136" s="25"/>
       <c r="C136" s="3"/>
@@ -4667,7 +4634,7 @@
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
     </row>
-    <row r="137" spans="1:22">
+    <row r="137" spans="1:22" ht="14.25">
       <c r="A137" s="7"/>
       <c r="B137" s="25"/>
       <c r="C137" s="3"/>
@@ -4691,7 +4658,7 @@
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
     </row>
-    <row r="138" spans="1:22">
+    <row r="138" spans="1:22" ht="14.25">
       <c r="A138" s="7"/>
       <c r="B138" s="25"/>
       <c r="C138" s="3"/>
@@ -4715,7 +4682,7 @@
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
     </row>
-    <row r="139" spans="1:22">
+    <row r="139" spans="1:22" ht="14.25">
       <c r="A139" s="7"/>
       <c r="B139" s="25"/>
       <c r="C139" s="3"/>
@@ -4739,7 +4706,7 @@
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
     </row>
-    <row r="140" spans="1:22">
+    <row r="140" spans="1:22" ht="14.25">
       <c r="A140" s="7"/>
       <c r="B140" s="25"/>
       <c r="C140" s="3"/>
@@ -4763,7 +4730,7 @@
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
     </row>
-    <row r="141" spans="1:22">
+    <row r="141" spans="1:22" ht="14.25">
       <c r="A141" s="7"/>
       <c r="B141" s="25"/>
       <c r="C141" s="3"/>
@@ -4787,7 +4754,7 @@
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
     </row>
-    <row r="142" spans="1:22">
+    <row r="142" spans="1:22" ht="14.25">
       <c r="A142" s="7"/>
       <c r="B142" s="25"/>
       <c r="C142" s="3"/>
@@ -4811,7 +4778,7 @@
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
     </row>
-    <row r="143" spans="1:22">
+    <row r="143" spans="1:22" ht="14.25">
       <c r="A143" s="7"/>
       <c r="B143" s="25"/>
       <c r="C143" s="3"/>
@@ -4835,7 +4802,7 @@
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
     </row>
-    <row r="144" spans="1:22">
+    <row r="144" spans="1:22" ht="14.25">
       <c r="A144" s="7"/>
       <c r="B144" s="25"/>
       <c r="C144" s="3"/>
@@ -4859,7 +4826,7 @@
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
     </row>
-    <row r="145" spans="1:22">
+    <row r="145" spans="1:22" ht="14.25">
       <c r="A145" s="7"/>
       <c r="B145" s="25"/>
       <c r="C145" s="3"/>
@@ -4883,7 +4850,7 @@
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
     </row>
-    <row r="146" spans="1:22">
+    <row r="146" spans="1:22" ht="14.25">
       <c r="A146" s="7"/>
       <c r="B146" s="25"/>
       <c r="C146" s="3"/>
@@ -4907,7 +4874,7 @@
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
     </row>
-    <row r="147" spans="1:22">
+    <row r="147" spans="1:22" ht="14.25">
       <c r="A147" s="7"/>
       <c r="B147" s="25"/>
       <c r="C147" s="3"/>
@@ -4931,7 +4898,7 @@
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
     </row>
-    <row r="148" spans="1:22">
+    <row r="148" spans="1:22" ht="14.25">
       <c r="A148" s="7"/>
       <c r="B148" s="25"/>
       <c r="C148" s="3"/>
@@ -4955,7 +4922,7 @@
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
     </row>
-    <row r="149" spans="1:22">
+    <row r="149" spans="1:22" ht="14.25">
       <c r="A149" s="7"/>
       <c r="B149" s="25"/>
       <c r="C149" s="3"/>
@@ -4979,7 +4946,7 @@
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
     </row>
-    <row r="150" spans="1:22">
+    <row r="150" spans="1:22" ht="14.25">
       <c r="A150" s="7"/>
       <c r="B150" s="25"/>
       <c r="C150" s="3"/>
@@ -5003,7 +4970,7 @@
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
     </row>
-    <row r="151" spans="1:22">
+    <row r="151" spans="1:22" ht="14.25">
       <c r="A151" s="7"/>
       <c r="B151" s="25"/>
       <c r="C151" s="3"/>
@@ -5027,7 +4994,7 @@
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
     </row>
-    <row r="152" spans="1:22">
+    <row r="152" spans="1:22" ht="14.25">
       <c r="A152" s="7"/>
       <c r="B152" s="25"/>
       <c r="C152" s="3"/>
@@ -5051,7 +5018,7 @@
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
     </row>
-    <row r="153" spans="1:22">
+    <row r="153" spans="1:22" ht="14.25">
       <c r="A153" s="7"/>
       <c r="B153" s="25"/>
       <c r="C153" s="3"/>
@@ -5075,7 +5042,7 @@
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
     </row>
-    <row r="154" spans="1:22">
+    <row r="154" spans="1:22" ht="14.25">
       <c r="A154" s="7"/>
       <c r="B154" s="25"/>
       <c r="C154" s="3"/>
@@ -5099,7 +5066,7 @@
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
     </row>
-    <row r="155" spans="1:22">
+    <row r="155" spans="1:22" ht="14.25">
       <c r="A155" s="7"/>
       <c r="B155" s="25"/>
       <c r="C155" s="3"/>
@@ -5123,7 +5090,7 @@
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
     </row>
-    <row r="156" spans="1:22">
+    <row r="156" spans="1:22" ht="14.25">
       <c r="A156" s="7"/>
       <c r="B156" s="25"/>
       <c r="C156" s="3"/>
@@ -5147,7 +5114,7 @@
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
     </row>
-    <row r="157" spans="1:22">
+    <row r="157" spans="1:22" ht="14.25">
       <c r="A157" s="7"/>
       <c r="B157" s="25"/>
       <c r="C157" s="3"/>
@@ -5171,7 +5138,7 @@
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
     </row>
-    <row r="158" spans="1:22">
+    <row r="158" spans="1:22" ht="14.25">
       <c r="A158" s="7"/>
       <c r="B158" s="25"/>
       <c r="C158" s="3"/>
@@ -5195,7 +5162,7 @@
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
     </row>
-    <row r="159" spans="1:22">
+    <row r="159" spans="1:22" ht="14.25">
       <c r="A159" s="7"/>
       <c r="B159" s="25"/>
       <c r="C159" s="3"/>
@@ -5219,7 +5186,7 @@
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
     </row>
-    <row r="160" spans="1:22">
+    <row r="160" spans="1:22" ht="14.25">
       <c r="A160" s="7"/>
       <c r="B160" s="25"/>
       <c r="C160" s="3"/>
@@ -5243,7 +5210,7 @@
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
     </row>
-    <row r="161" spans="1:22">
+    <row r="161" spans="1:22" ht="14.25">
       <c r="A161" s="7"/>
       <c r="B161" s="25"/>
       <c r="C161" s="3"/>
@@ -5267,7 +5234,7 @@
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
     </row>
-    <row r="162" spans="1:22">
+    <row r="162" spans="1:22" ht="14.25">
       <c r="A162" s="7"/>
       <c r="B162" s="25"/>
       <c r="C162" s="3"/>
@@ -5291,7 +5258,7 @@
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
     </row>
-    <row r="163" spans="1:22">
+    <row r="163" spans="1:22" ht="14.25">
       <c r="A163" s="7"/>
       <c r="B163" s="25"/>
       <c r="C163" s="3"/>
@@ -5315,7 +5282,7 @@
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
     </row>
-    <row r="164" spans="1:22">
+    <row r="164" spans="1:22" ht="14.25">
       <c r="A164" s="7"/>
       <c r="B164" s="25"/>
       <c r="C164" s="3"/>
@@ -5339,7 +5306,7 @@
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
     </row>
-    <row r="165" spans="1:22">
+    <row r="165" spans="1:22" ht="14.25">
       <c r="A165" s="7"/>
       <c r="B165" s="25"/>
       <c r="C165" s="3"/>
@@ -5363,7 +5330,7 @@
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
     </row>
-    <row r="166" spans="1:22">
+    <row r="166" spans="1:22" ht="14.25">
       <c r="A166" s="7"/>
       <c r="B166" s="25"/>
       <c r="C166" s="3"/>
@@ -5387,7 +5354,7 @@
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
     </row>
-    <row r="167" spans="1:22">
+    <row r="167" spans="1:22" ht="14.25">
       <c r="A167" s="7"/>
       <c r="B167" s="25"/>
       <c r="C167" s="3"/>
@@ -5411,7 +5378,7 @@
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
     </row>
-    <row r="168" spans="1:22">
+    <row r="168" spans="1:22" ht="14.25">
       <c r="A168" s="7"/>
       <c r="B168" s="25"/>
       <c r="C168" s="3"/>
@@ -5435,7 +5402,7 @@
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
     </row>
-    <row r="169" spans="1:22">
+    <row r="169" spans="1:22" ht="14.25">
       <c r="A169" s="7"/>
       <c r="B169" s="25"/>
       <c r="C169" s="3"/>
@@ -5459,7 +5426,7 @@
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
     </row>
-    <row r="170" spans="1:22">
+    <row r="170" spans="1:22" ht="14.25">
       <c r="A170" s="7"/>
       <c r="B170" s="25"/>
       <c r="C170" s="3"/>
@@ -5483,7 +5450,7 @@
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
     </row>
-    <row r="171" spans="1:22">
+    <row r="171" spans="1:22" ht="14.25">
       <c r="A171" s="7"/>
       <c r="B171" s="25"/>
       <c r="C171" s="3"/>
@@ -5507,7 +5474,7 @@
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
     </row>
-    <row r="172" spans="1:22">
+    <row r="172" spans="1:22" ht="14.25">
       <c r="A172" s="7"/>
       <c r="B172" s="25"/>
       <c r="C172" s="3"/>
@@ -5531,7 +5498,7 @@
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
     </row>
-    <row r="173" spans="1:22">
+    <row r="173" spans="1:22" ht="14.25">
       <c r="A173" s="7"/>
       <c r="B173" s="25"/>
       <c r="C173" s="3"/>
@@ -5555,7 +5522,7 @@
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
     </row>
-    <row r="174" spans="1:22">
+    <row r="174" spans="1:22" ht="14.25">
       <c r="A174" s="7"/>
       <c r="B174" s="25"/>
       <c r="C174" s="3"/>
@@ -5579,7 +5546,7 @@
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
     </row>
-    <row r="175" spans="1:22">
+    <row r="175" spans="1:22" ht="14.25">
       <c r="A175" s="7"/>
       <c r="B175" s="25"/>
       <c r="C175" s="3"/>
@@ -5603,7 +5570,7 @@
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
     </row>
-    <row r="176" spans="1:22">
+    <row r="176" spans="1:22" ht="14.25">
       <c r="A176" s="7"/>
       <c r="B176" s="25"/>
       <c r="C176" s="3"/>
@@ -5627,7 +5594,7 @@
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
     </row>
-    <row r="177" spans="1:22">
+    <row r="177" spans="1:22" ht="14.25">
       <c r="A177" s="7"/>
       <c r="B177" s="25"/>
       <c r="C177" s="3"/>
@@ -5651,7 +5618,7 @@
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
     </row>
-    <row r="178" spans="1:22">
+    <row r="178" spans="1:22" ht="14.25">
       <c r="A178" s="7"/>
       <c r="B178" s="25"/>
       <c r="C178" s="3"/>
@@ -5675,7 +5642,7 @@
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
     </row>
-    <row r="179" spans="1:22">
+    <row r="179" spans="1:22" ht="14.25">
       <c r="A179" s="7"/>
       <c r="B179" s="25"/>
       <c r="C179" s="3"/>
@@ -5699,7 +5666,7 @@
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
     </row>
-    <row r="180" spans="1:22">
+    <row r="180" spans="1:22" ht="14.25">
       <c r="A180" s="7"/>
       <c r="B180" s="25"/>
       <c r="C180" s="3"/>
@@ -5723,7 +5690,7 @@
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
     </row>
-    <row r="181" spans="1:22">
+    <row r="181" spans="1:22" ht="14.25">
       <c r="A181" s="7"/>
       <c r="B181" s="25"/>
       <c r="C181" s="3"/>
@@ -5747,7 +5714,7 @@
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
     </row>
-    <row r="182" spans="1:22">
+    <row r="182" spans="1:22" ht="14.25">
       <c r="A182" s="7"/>
       <c r="B182" s="25"/>
       <c r="C182" s="3"/>
@@ -5771,7 +5738,7 @@
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
     </row>
-    <row r="183" spans="1:22">
+    <row r="183" spans="1:22" ht="14.25">
       <c r="A183" s="7"/>
       <c r="B183" s="25"/>
       <c r="C183" s="3"/>
@@ -5795,7 +5762,7 @@
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
     </row>
-    <row r="184" spans="1:22">
+    <row r="184" spans="1:22" ht="14.25">
       <c r="A184" s="7"/>
       <c r="B184" s="25"/>
       <c r="C184" s="3"/>
@@ -5819,7 +5786,7 @@
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
     </row>
-    <row r="185" spans="1:22">
+    <row r="185" spans="1:22" ht="14.25">
       <c r="A185" s="7"/>
       <c r="B185" s="25"/>
       <c r="C185" s="3"/>
@@ -5843,7 +5810,7 @@
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
     </row>
-    <row r="186" spans="1:22">
+    <row r="186" spans="1:22" ht="14.25">
       <c r="A186" s="7"/>
       <c r="B186" s="25"/>
       <c r="C186" s="3"/>
@@ -5867,7 +5834,7 @@
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
     </row>
-    <row r="187" spans="1:22">
+    <row r="187" spans="1:22" ht="14.25">
       <c r="A187" s="7"/>
       <c r="B187" s="25"/>
       <c r="C187" s="3"/>
@@ -5891,7 +5858,7 @@
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
     </row>
-    <row r="188" spans="1:22">
+    <row r="188" spans="1:22" ht="14.25">
       <c r="A188" s="7"/>
       <c r="B188" s="25"/>
       <c r="C188" s="3"/>
@@ -5915,7 +5882,7 @@
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
     </row>
-    <row r="189" spans="1:22">
+    <row r="189" spans="1:22" ht="14.25">
       <c r="A189" s="7"/>
       <c r="B189" s="25"/>
       <c r="C189" s="3"/>
@@ -5939,7 +5906,7 @@
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
     </row>
-    <row r="190" spans="1:22">
+    <row r="190" spans="1:22" ht="14.25">
       <c r="A190" s="7"/>
       <c r="B190" s="25"/>
       <c r="C190" s="3"/>
@@ -5963,7 +5930,7 @@
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
     </row>
-    <row r="191" spans="1:22">
+    <row r="191" spans="1:22" ht="14.25">
       <c r="A191" s="7"/>
       <c r="B191" s="25"/>
       <c r="C191" s="3"/>
@@ -5987,7 +5954,7 @@
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
     </row>
-    <row r="192" spans="1:22">
+    <row r="192" spans="1:22" ht="14.25">
       <c r="A192" s="7"/>
       <c r="B192" s="25"/>
       <c r="C192" s="3"/>
@@ -6011,7 +5978,7 @@
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
     </row>
-    <row r="193" spans="1:22">
+    <row r="193" spans="1:22" ht="14.25">
       <c r="A193" s="7"/>
       <c r="B193" s="25"/>
       <c r="C193" s="3"/>
@@ -6035,7 +6002,7 @@
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
     </row>
-    <row r="194" spans="1:22">
+    <row r="194" spans="1:22" ht="14.25">
       <c r="A194" s="7"/>
       <c r="B194" s="25"/>
       <c r="C194" s="3"/>
@@ -6059,7 +6026,7 @@
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
     </row>
-    <row r="195" spans="1:22">
+    <row r="195" spans="1:22" ht="14.25">
       <c r="A195" s="7"/>
       <c r="B195" s="25"/>
       <c r="C195" s="3"/>
@@ -6083,7 +6050,7 @@
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
     </row>
-    <row r="196" spans="1:22">
+    <row r="196" spans="1:22" ht="14.25">
       <c r="A196" s="7"/>
       <c r="B196" s="25"/>
       <c r="C196" s="3"/>
@@ -6107,7 +6074,7 @@
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
     </row>
-    <row r="197" spans="1:22">
+    <row r="197" spans="1:22" ht="14.25">
       <c r="A197" s="7"/>
       <c r="B197" s="25"/>
       <c r="C197" s="3"/>
@@ -6131,7 +6098,7 @@
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
     </row>
-    <row r="198" spans="1:22">
+    <row r="198" spans="1:22" ht="14.25">
       <c r="A198" s="7"/>
       <c r="B198" s="25"/>
       <c r="C198" s="3"/>
@@ -6155,7 +6122,7 @@
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
     </row>
-    <row r="199" spans="1:22">
+    <row r="199" spans="1:22" ht="14.25">
       <c r="A199" s="7"/>
       <c r="B199" s="25"/>
       <c r="C199" s="3"/>
@@ -6179,7 +6146,7 @@
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
     </row>
-    <row r="200" spans="1:22">
+    <row r="200" spans="1:22" ht="14.25">
       <c r="A200" s="7"/>
       <c r="B200" s="25"/>
       <c r="C200" s="3"/>
@@ -6203,7 +6170,7 @@
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
     </row>
-    <row r="201" spans="1:22">
+    <row r="201" spans="1:22" ht="14.25">
       <c r="A201" s="7"/>
       <c r="B201" s="25"/>
       <c r="C201" s="3"/>
@@ -6227,7 +6194,7 @@
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
     </row>
-    <row r="202" spans="1:22">
+    <row r="202" spans="1:22" ht="14.25">
       <c r="A202" s="7"/>
       <c r="B202" s="25"/>
       <c r="C202" s="3"/>
@@ -6251,7 +6218,7 @@
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
     </row>
-    <row r="203" spans="1:22">
+    <row r="203" spans="1:22" ht="14.25">
       <c r="A203" s="7"/>
       <c r="B203" s="25"/>
       <c r="C203" s="3"/>
@@ -6275,7 +6242,7 @@
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
     </row>
-    <row r="204" spans="1:22">
+    <row r="204" spans="1:22" ht="14.25">
       <c r="A204" s="7"/>
       <c r="B204" s="25"/>
       <c r="C204" s="3"/>
@@ -6299,7 +6266,7 @@
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
     </row>
-    <row r="205" spans="1:22">
+    <row r="205" spans="1:22" ht="14.25">
       <c r="A205" s="7"/>
       <c r="B205" s="25"/>
       <c r="C205" s="3"/>
@@ -6323,7 +6290,7 @@
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
     </row>
-    <row r="206" spans="1:22">
+    <row r="206" spans="1:22" ht="14.25">
       <c r="A206" s="7"/>
       <c r="B206" s="25"/>
       <c r="C206" s="3"/>
@@ -6347,7 +6314,7 @@
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
     </row>
-    <row r="207" spans="1:22">
+    <row r="207" spans="1:22" ht="14.25">
       <c r="A207" s="7"/>
       <c r="B207" s="25"/>
       <c r="C207" s="3"/>
@@ -6371,7 +6338,7 @@
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
     </row>
-    <row r="208" spans="1:22">
+    <row r="208" spans="1:22" ht="14.25">
       <c r="A208" s="7"/>
       <c r="B208" s="25"/>
       <c r="C208" s="3"/>
@@ -6395,7 +6362,7 @@
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
     </row>
-    <row r="209" spans="1:22">
+    <row r="209" spans="1:22" ht="14.25">
       <c r="A209" s="7"/>
       <c r="B209" s="25"/>
       <c r="C209" s="3"/>
@@ -6419,7 +6386,7 @@
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
     </row>
-    <row r="210" spans="1:22">
+    <row r="210" spans="1:22" ht="14.25">
       <c r="A210" s="7"/>
       <c r="B210" s="25"/>
       <c r="C210" s="3"/>
@@ -6443,7 +6410,7 @@
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
     </row>
-    <row r="211" spans="1:22">
+    <row r="211" spans="1:22" ht="14.25">
       <c r="A211" s="7"/>
       <c r="B211" s="25"/>
       <c r="C211" s="3"/>
@@ -6467,7 +6434,7 @@
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
     </row>
-    <row r="212" spans="1:22">
+    <row r="212" spans="1:22" ht="14.25">
       <c r="A212" s="7"/>
       <c r="B212" s="25"/>
       <c r="C212" s="3"/>
@@ -6491,7 +6458,7 @@
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
     </row>
-    <row r="213" spans="1:22">
+    <row r="213" spans="1:22" ht="14.25">
       <c r="A213" s="7"/>
       <c r="B213" s="25"/>
       <c r="C213" s="3"/>
@@ -6515,7 +6482,7 @@
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
     </row>
-    <row r="214" spans="1:22">
+    <row r="214" spans="1:22" ht="14.25">
       <c r="A214" s="7"/>
       <c r="B214" s="25"/>
       <c r="C214" s="3"/>
@@ -6539,7 +6506,7 @@
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
     </row>
-    <row r="215" spans="1:22">
+    <row r="215" spans="1:22" ht="14.25">
       <c r="A215" s="7"/>
       <c r="B215" s="25"/>
       <c r="C215" s="3"/>
@@ -6563,7 +6530,7 @@
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
     </row>
-    <row r="216" spans="1:22">
+    <row r="216" spans="1:22" ht="14.25">
       <c r="A216" s="7"/>
       <c r="B216" s="25"/>
       <c r="C216" s="3"/>
@@ -6587,7 +6554,7 @@
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
     </row>
-    <row r="217" spans="1:22">
+    <row r="217" spans="1:22" ht="14.25">
       <c r="A217" s="7"/>
       <c r="B217" s="25"/>
       <c r="C217" s="3"/>
@@ -6611,7 +6578,7 @@
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
     </row>
-    <row r="218" spans="1:22">
+    <row r="218" spans="1:22" ht="14.25">
       <c r="A218" s="7"/>
       <c r="B218" s="25"/>
       <c r="C218" s="3"/>
@@ -6635,7 +6602,7 @@
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
     </row>
-    <row r="219" spans="1:22">
+    <row r="219" spans="1:22" ht="14.25">
       <c r="A219" s="7"/>
       <c r="B219" s="25"/>
       <c r="C219" s="3"/>
@@ -6659,7 +6626,7 @@
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
     </row>
-    <row r="220" spans="1:22">
+    <row r="220" spans="1:22" ht="14.25">
       <c r="A220" s="7"/>
       <c r="B220" s="25"/>
       <c r="C220" s="3"/>
@@ -6683,7 +6650,7 @@
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
     </row>
-    <row r="221" spans="1:22">
+    <row r="221" spans="1:22" ht="14.25">
       <c r="A221" s="7"/>
       <c r="B221" s="25"/>
       <c r="C221" s="3"/>
@@ -6707,7 +6674,7 @@
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
     </row>
-    <row r="222" spans="1:22">
+    <row r="222" spans="1:22" ht="14.25">
       <c r="A222" s="7"/>
       <c r="B222" s="25"/>
       <c r="C222" s="3"/>
@@ -6731,7 +6698,7 @@
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
     </row>
-    <row r="223" spans="1:22">
+    <row r="223" spans="1:22" ht="14.25">
       <c r="A223" s="7"/>
       <c r="B223" s="25"/>
       <c r="C223" s="3"/>
@@ -6755,7 +6722,7 @@
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
     </row>
-    <row r="224" spans="1:22">
+    <row r="224" spans="1:22" ht="14.25">
       <c r="A224" s="7"/>
       <c r="B224" s="25"/>
       <c r="C224" s="3"/>
@@ -6779,7 +6746,7 @@
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
     </row>
-    <row r="225" spans="1:22">
+    <row r="225" spans="1:22" ht="14.25">
       <c r="A225" s="7"/>
       <c r="B225" s="25"/>
       <c r="C225" s="3"/>
@@ -6803,7 +6770,7 @@
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
     </row>
-    <row r="226" spans="1:22">
+    <row r="226" spans="1:22" ht="14.25">
       <c r="A226" s="7"/>
       <c r="B226" s="25"/>
       <c r="C226" s="3"/>
@@ -6827,7 +6794,7 @@
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
     </row>
-    <row r="227" spans="1:22">
+    <row r="227" spans="1:22" ht="14.25">
       <c r="A227" s="7"/>
       <c r="B227" s="25"/>
       <c r="C227" s="3"/>
@@ -6851,7 +6818,7 @@
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
     </row>
-    <row r="228" spans="1:22">
+    <row r="228" spans="1:22" ht="14.25">
       <c r="A228" s="7"/>
       <c r="B228" s="25"/>
       <c r="C228" s="3"/>
@@ -6875,7 +6842,7 @@
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
     </row>
-    <row r="229" spans="1:22">
+    <row r="229" spans="1:22" ht="14.25">
       <c r="A229" s="7"/>
       <c r="B229" s="25"/>
       <c r="C229" s="3"/>
@@ -6899,7 +6866,7 @@
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
     </row>
-    <row r="230" spans="1:22">
+    <row r="230" spans="1:22" ht="14.25">
       <c r="A230" s="7"/>
       <c r="B230" s="25"/>
       <c r="C230" s="3"/>
@@ -6923,7 +6890,7 @@
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
     </row>
-    <row r="231" spans="1:22">
+    <row r="231" spans="1:22" ht="14.25">
       <c r="A231" s="7"/>
       <c r="B231" s="25"/>
       <c r="C231" s="3"/>
@@ -6947,7 +6914,7 @@
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
     </row>
-    <row r="232" spans="1:22">
+    <row r="232" spans="1:22" ht="14.25">
       <c r="A232" s="7"/>
       <c r="B232" s="25"/>
       <c r="C232" s="3"/>
@@ -6971,7 +6938,7 @@
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
     </row>
-    <row r="233" spans="1:22">
+    <row r="233" spans="1:22" ht="14.25">
       <c r="A233" s="7"/>
       <c r="B233" s="25"/>
       <c r="C233" s="3"/>
@@ -6995,7 +6962,7 @@
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
     </row>
-    <row r="234" spans="1:22">
+    <row r="234" spans="1:22" ht="14.25">
       <c r="A234" s="7"/>
       <c r="B234" s="25"/>
       <c r="C234" s="3"/>
@@ -7019,7 +6986,7 @@
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
     </row>
-    <row r="235" spans="1:22">
+    <row r="235" spans="1:22" ht="14.25">
       <c r="A235" s="7"/>
       <c r="B235" s="25"/>
       <c r="C235" s="3"/>
@@ -7043,7 +7010,7 @@
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
     </row>
-    <row r="236" spans="1:22">
+    <row r="236" spans="1:22" ht="14.25">
       <c r="A236" s="7"/>
       <c r="B236" s="25"/>
       <c r="C236" s="3"/>
@@ -7067,7 +7034,7 @@
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
     </row>
-    <row r="237" spans="1:22">
+    <row r="237" spans="1:22" ht="14.25">
       <c r="A237" s="7"/>
       <c r="B237" s="25"/>
       <c r="C237" s="3"/>
@@ -7091,7 +7058,7 @@
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
     </row>
-    <row r="238" spans="1:22">
+    <row r="238" spans="1:22" ht="14.25">
       <c r="A238" s="7"/>
       <c r="B238" s="25"/>
       <c r="C238" s="3"/>
@@ -7115,7 +7082,7 @@
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
     </row>
-    <row r="239" spans="1:22">
+    <row r="239" spans="1:22" ht="14.25">
       <c r="A239" s="7"/>
       <c r="B239" s="25"/>
       <c r="C239" s="3"/>
@@ -7139,7 +7106,7 @@
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
     </row>
-    <row r="240" spans="1:22">
+    <row r="240" spans="1:22" ht="14.25">
       <c r="A240" s="7"/>
       <c r="B240" s="25"/>
       <c r="C240" s="3"/>
@@ -7163,7 +7130,7 @@
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
     </row>
-    <row r="241" spans="1:22">
+    <row r="241" spans="1:22" ht="14.25">
       <c r="A241" s="7"/>
       <c r="B241" s="25"/>
       <c r="C241" s="3"/>
@@ -7187,7 +7154,7 @@
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
     </row>
-    <row r="242" spans="1:22">
+    <row r="242" spans="1:22" ht="14.25">
       <c r="A242" s="7"/>
       <c r="B242" s="25"/>
       <c r="C242" s="3"/>
@@ -7211,7 +7178,7 @@
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
     </row>
-    <row r="243" spans="1:22">
+    <row r="243" spans="1:22" ht="14.25">
       <c r="A243" s="7"/>
       <c r="B243" s="25"/>
       <c r="C243" s="3"/>
@@ -7235,7 +7202,7 @@
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
     </row>
-    <row r="244" spans="1:22">
+    <row r="244" spans="1:22" ht="14.25">
       <c r="A244" s="7"/>
       <c r="B244" s="25"/>
       <c r="C244" s="3"/>
@@ -7259,7 +7226,7 @@
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
     </row>
-    <row r="245" spans="1:22">
+    <row r="245" spans="1:22" ht="14.25">
       <c r="A245" s="7"/>
       <c r="B245" s="25"/>
       <c r="C245" s="3"/>
@@ -7283,7 +7250,7 @@
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
     </row>
-    <row r="246" spans="1:22">
+    <row r="246" spans="1:22" ht="14.25">
       <c r="A246" s="7"/>
       <c r="B246" s="25"/>
       <c r="C246" s="3"/>
@@ -7307,7 +7274,7 @@
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
     </row>
-    <row r="247" spans="1:22">
+    <row r="247" spans="1:22" ht="14.25">
       <c r="A247" s="7"/>
       <c r="B247" s="25"/>
       <c r="C247" s="3"/>
@@ -7331,7 +7298,7 @@
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
     </row>
-    <row r="248" spans="1:22">
+    <row r="248" spans="1:22" ht="14.25">
       <c r="A248" s="7"/>
       <c r="B248" s="25"/>
       <c r="C248" s="3"/>
@@ -7355,7 +7322,7 @@
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
     </row>
-    <row r="249" spans="1:22">
+    <row r="249" spans="1:22" ht="14.25">
       <c r="A249" s="7"/>
       <c r="B249" s="25"/>
       <c r="C249" s="3"/>
@@ -7379,7 +7346,7 @@
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
     </row>
-    <row r="250" spans="1:22">
+    <row r="250" spans="1:22" ht="14.25">
       <c r="A250" s="7"/>
       <c r="B250" s="25"/>
       <c r="C250" s="3"/>
@@ -7403,7 +7370,7 @@
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
     </row>
-    <row r="251" spans="1:22">
+    <row r="251" spans="1:22" ht="14.25">
       <c r="A251" s="7"/>
       <c r="B251" s="25"/>
       <c r="C251" s="3"/>
@@ -7427,7 +7394,7 @@
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
     </row>
-    <row r="252" spans="1:22">
+    <row r="252" spans="1:22" ht="14.25">
       <c r="A252" s="7"/>
       <c r="B252" s="25"/>
       <c r="C252" s="3"/>
@@ -7451,7 +7418,7 @@
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
     </row>
-    <row r="253" spans="1:22">
+    <row r="253" spans="1:22" ht="14.25">
       <c r="A253" s="7"/>
       <c r="B253" s="25"/>
       <c r="C253" s="3"/>
@@ -7475,7 +7442,7 @@
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
     </row>
-    <row r="254" spans="1:22">
+    <row r="254" spans="1:22" ht="14.25">
       <c r="A254" s="7"/>
       <c r="B254" s="25"/>
       <c r="C254" s="3"/>
@@ -7499,7 +7466,7 @@
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
     </row>
-    <row r="255" spans="1:22">
+    <row r="255" spans="1:22" ht="14.25">
       <c r="A255" s="7"/>
       <c r="B255" s="25"/>
       <c r="C255" s="3"/>
@@ -7523,7 +7490,7 @@
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
     </row>
-    <row r="256" spans="1:22">
+    <row r="256" spans="1:22" ht="14.25">
       <c r="A256" s="7"/>
       <c r="B256" s="25"/>
       <c r="C256" s="3"/>
@@ -7547,7 +7514,7 @@
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
     </row>
-    <row r="257" spans="1:22">
+    <row r="257" spans="1:22" ht="14.25">
       <c r="A257" s="7"/>
       <c r="B257" s="25"/>
       <c r="C257" s="3"/>
@@ -7571,7 +7538,7 @@
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
     </row>
-    <row r="258" spans="1:22">
+    <row r="258" spans="1:22" ht="14.25">
       <c r="A258" s="7"/>
       <c r="B258" s="25"/>
       <c r="C258" s="3"/>
@@ -7595,7 +7562,7 @@
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
     </row>
-    <row r="259" spans="1:22">
+    <row r="259" spans="1:22" ht="14.25">
       <c r="A259" s="7"/>
       <c r="B259" s="25"/>
       <c r="C259" s="3"/>
@@ -7619,7 +7586,7 @@
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
     </row>
-    <row r="260" spans="1:22">
+    <row r="260" spans="1:22" ht="14.25">
       <c r="A260" s="7"/>
       <c r="B260" s="25"/>
       <c r="C260" s="3"/>
@@ -7643,7 +7610,7 @@
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
     </row>
-    <row r="261" spans="1:22">
+    <row r="261" spans="1:22" ht="14.25">
       <c r="A261" s="7"/>
       <c r="B261" s="25"/>
       <c r="C261" s="3"/>
@@ -7667,7 +7634,7 @@
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
     </row>
-    <row r="262" spans="1:22">
+    <row r="262" spans="1:22" ht="14.25">
       <c r="A262" s="7"/>
       <c r="B262" s="25"/>
       <c r="C262" s="3"/>
@@ -7691,7 +7658,7 @@
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
     </row>
-    <row r="263" spans="1:22">
+    <row r="263" spans="1:22" ht="14.25">
       <c r="A263" s="7"/>
       <c r="B263" s="25"/>
       <c r="C263" s="3"/>
@@ -7715,7 +7682,7 @@
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
     </row>
-    <row r="264" spans="1:22">
+    <row r="264" spans="1:22" ht="14.25">
       <c r="A264" s="7"/>
       <c r="B264" s="25"/>
       <c r="C264" s="3"/>
@@ -7739,7 +7706,7 @@
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
     </row>
-    <row r="265" spans="1:22">
+    <row r="265" spans="1:22" ht="14.25">
       <c r="A265" s="7"/>
       <c r="B265" s="25"/>
       <c r="C265" s="3"/>
@@ -7763,7 +7730,7 @@
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
     </row>
-    <row r="266" spans="1:22">
+    <row r="266" spans="1:22" ht="14.25">
       <c r="A266" s="7"/>
       <c r="B266" s="25"/>
       <c r="C266" s="3"/>
@@ -7787,7 +7754,7 @@
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
     </row>
-    <row r="267" spans="1:22">
+    <row r="267" spans="1:22" ht="14.25">
       <c r="A267" s="7"/>
       <c r="B267" s="25"/>
       <c r="C267" s="3"/>
@@ -7811,7 +7778,7 @@
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
     </row>
-    <row r="268" spans="1:22">
+    <row r="268" spans="1:22" ht="14.25">
       <c r="A268" s="7"/>
       <c r="B268" s="25"/>
       <c r="C268" s="3"/>
@@ -7835,7 +7802,7 @@
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
     </row>
-    <row r="269" spans="1:22">
+    <row r="269" spans="1:22" ht="14.25">
       <c r="A269" s="7"/>
       <c r="B269" s="25"/>
       <c r="C269" s="3"/>
@@ -7859,7 +7826,7 @@
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
     </row>
-    <row r="270" spans="1:22">
+    <row r="270" spans="1:22" ht="14.25">
       <c r="A270" s="7"/>
       <c r="B270" s="25"/>
       <c r="C270" s="3"/>
@@ -7883,7 +7850,7 @@
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
     </row>
-    <row r="271" spans="1:22">
+    <row r="271" spans="1:22" ht="14.25">
       <c r="A271" s="7"/>
       <c r="B271" s="25"/>
       <c r="C271" s="3"/>
@@ -7907,7 +7874,7 @@
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
     </row>
-    <row r="272" spans="1:22">
+    <row r="272" spans="1:22" ht="14.25">
       <c r="A272" s="7"/>
       <c r="B272" s="25"/>
       <c r="C272" s="3"/>
@@ -7931,7 +7898,7 @@
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
     </row>
-    <row r="273" spans="1:22">
+    <row r="273" spans="1:22" ht="14.25">
       <c r="A273" s="7"/>
       <c r="B273" s="25"/>
       <c r="C273" s="3"/>
@@ -7955,7 +7922,7 @@
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
     </row>
-    <row r="274" spans="1:22">
+    <row r="274" spans="1:22" ht="14.25">
       <c r="A274" s="7"/>
       <c r="B274" s="25"/>
       <c r="C274" s="3"/>
@@ -7979,7 +7946,7 @@
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
     </row>
-    <row r="275" spans="1:22">
+    <row r="275" spans="1:22" ht="14.25">
       <c r="A275" s="7"/>
       <c r="B275" s="25"/>
       <c r="C275" s="3"/>
@@ -8003,7 +7970,7 @@
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
     </row>
-    <row r="276" spans="1:22">
+    <row r="276" spans="1:22" ht="14.25">
       <c r="A276" s="7"/>
       <c r="B276" s="25"/>
       <c r="C276" s="3"/>
@@ -8027,7 +7994,7 @@
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
     </row>
-    <row r="277" spans="1:22">
+    <row r="277" spans="1:22" ht="14.25">
       <c r="A277" s="7"/>
       <c r="B277" s="25"/>
       <c r="C277" s="3"/>
@@ -8051,7 +8018,7 @@
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
     </row>
-    <row r="278" spans="1:22">
+    <row r="278" spans="1:22" ht="14.25">
       <c r="A278" s="7"/>
       <c r="B278" s="25"/>
       <c r="C278" s="3"/>
@@ -8075,7 +8042,7 @@
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
     </row>
-    <row r="279" spans="1:22">
+    <row r="279" spans="1:22" ht="14.25">
       <c r="A279" s="7"/>
       <c r="B279" s="25"/>
       <c r="C279" s="3"/>
@@ -8099,7 +8066,7 @@
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
     </row>
-    <row r="280" spans="1:22">
+    <row r="280" spans="1:22" ht="14.25">
       <c r="A280" s="7"/>
       <c r="B280" s="25"/>
       <c r="C280" s="3"/>
@@ -8123,7 +8090,7 @@
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
     </row>
-    <row r="281" spans="1:22">
+    <row r="281" spans="1:22" ht="14.25">
       <c r="A281" s="7"/>
       <c r="B281" s="25"/>
       <c r="C281" s="3"/>
@@ -8147,7 +8114,7 @@
       <c r="U281" s="1"/>
       <c r="V281" s="1"/>
     </row>
-    <row r="282" spans="1:22">
+    <row r="282" spans="1:22" ht="14.25">
       <c r="A282" s="7"/>
       <c r="B282" s="25"/>
       <c r="C282" s="3"/>
@@ -8171,7 +8138,7 @@
       <c r="U282" s="1"/>
       <c r="V282" s="1"/>
     </row>
-    <row r="283" spans="1:22">
+    <row r="283" spans="1:22" ht="14.25">
       <c r="A283" s="7"/>
       <c r="B283" s="25"/>
       <c r="C283" s="3"/>
@@ -8195,7 +8162,7 @@
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
     </row>
-    <row r="284" spans="1:22">
+    <row r="284" spans="1:22" ht="14.25">
       <c r="A284" s="7"/>
       <c r="B284" s="25"/>
       <c r="C284" s="3"/>
@@ -8219,7 +8186,7 @@
       <c r="U284" s="1"/>
       <c r="V284" s="1"/>
     </row>
-    <row r="285" spans="1:22">
+    <row r="285" spans="1:22" ht="14.25">
       <c r="A285" s="7"/>
       <c r="B285" s="25"/>
       <c r="C285" s="3"/>
@@ -8243,7 +8210,7 @@
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
     </row>
-    <row r="286" spans="1:22">
+    <row r="286" spans="1:22" ht="14.25">
       <c r="A286" s="7"/>
       <c r="B286" s="25"/>
       <c r="C286" s="3"/>
@@ -8267,7 +8234,7 @@
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
     </row>
-    <row r="287" spans="1:22">
+    <row r="287" spans="1:22" ht="14.25">
       <c r="A287" s="7"/>
       <c r="B287" s="25"/>
       <c r="C287" s="3"/>
@@ -8291,7 +8258,7 @@
       <c r="U287" s="1"/>
       <c r="V287" s="1"/>
     </row>
-    <row r="288" spans="1:22">
+    <row r="288" spans="1:22" ht="14.25">
       <c r="A288" s="7"/>
       <c r="B288" s="25"/>
       <c r="C288" s="3"/>
@@ -8315,7 +8282,7 @@
       <c r="U288" s="1"/>
       <c r="V288" s="1"/>
     </row>
-    <row r="289" spans="1:22">
+    <row r="289" spans="1:22" ht="14.25">
       <c r="A289" s="7"/>
       <c r="B289" s="25"/>
       <c r="C289" s="3"/>
@@ -8339,7 +8306,7 @@
       <c r="U289" s="1"/>
       <c r="V289" s="1"/>
     </row>
-    <row r="290" spans="1:22">
+    <row r="290" spans="1:22" ht="14.25">
       <c r="A290" s="7"/>
       <c r="B290" s="25"/>
       <c r="C290" s="3"/>
@@ -8363,7 +8330,7 @@
       <c r="U290" s="1"/>
       <c r="V290" s="1"/>
     </row>
-    <row r="291" spans="1:22">
+    <row r="291" spans="1:22" ht="14.25">
       <c r="A291" s="7"/>
       <c r="B291" s="25"/>
       <c r="C291" s="3"/>
@@ -8387,7 +8354,7 @@
       <c r="U291" s="1"/>
       <c r="V291" s="1"/>
     </row>
-    <row r="292" spans="1:22">
+    <row r="292" spans="1:22" ht="14.25">
       <c r="A292" s="7"/>
       <c r="B292" s="25"/>
       <c r="C292" s="3"/>
@@ -8411,7 +8378,7 @@
       <c r="U292" s="1"/>
       <c r="V292" s="1"/>
     </row>
-    <row r="293" spans="1:22">
+    <row r="293" spans="1:22" ht="14.25">
       <c r="A293" s="7"/>
       <c r="B293" s="25"/>
       <c r="C293" s="3"/>
@@ -8435,7 +8402,7 @@
       <c r="U293" s="1"/>
       <c r="V293" s="1"/>
     </row>
-    <row r="294" spans="1:22">
+    <row r="294" spans="1:22" ht="14.25">
       <c r="A294" s="7"/>
       <c r="B294" s="25"/>
       <c r="C294" s="3"/>
@@ -8459,7 +8426,7 @@
       <c r="U294" s="1"/>
       <c r="V294" s="1"/>
     </row>
-    <row r="295" spans="1:22">
+    <row r="295" spans="1:22" ht="14.25">
       <c r="A295" s="7"/>
       <c r="B295" s="25"/>
       <c r="C295" s="3"/>
@@ -8483,7 +8450,7 @@
       <c r="U295" s="1"/>
       <c r="V295" s="1"/>
     </row>
-    <row r="296" spans="1:22">
+    <row r="296" spans="1:22" ht="14.25">
       <c r="A296" s="7"/>
       <c r="B296" s="25"/>
       <c r="C296" s="3"/>
@@ -8507,7 +8474,7 @@
       <c r="U296" s="1"/>
       <c r="V296" s="1"/>
     </row>
-    <row r="297" spans="1:22">
+    <row r="297" spans="1:22" ht="14.25">
       <c r="A297" s="7"/>
       <c r="B297" s="25"/>
       <c r="C297" s="3"/>
@@ -8531,7 +8498,7 @@
       <c r="U297" s="1"/>
       <c r="V297" s="1"/>
     </row>
-    <row r="298" spans="1:22">
+    <row r="298" spans="1:22" ht="14.25">
       <c r="A298" s="7"/>
       <c r="B298" s="25"/>
       <c r="C298" s="3"/>
@@ -8555,7 +8522,7 @@
       <c r="U298" s="1"/>
       <c r="V298" s="1"/>
     </row>
-    <row r="299" spans="1:22">
+    <row r="299" spans="1:22" ht="14.25">
       <c r="A299" s="7"/>
       <c r="B299" s="25"/>
       <c r="C299" s="3"/>
@@ -8579,7 +8546,7 @@
       <c r="U299" s="1"/>
       <c r="V299" s="1"/>
     </row>
-    <row r="300" spans="1:22">
+    <row r="300" spans="1:22" ht="14.25">
       <c r="A300" s="7"/>
       <c r="B300" s="25"/>
       <c r="C300" s="3"/>
@@ -8603,7 +8570,7 @@
       <c r="U300" s="1"/>
       <c r="V300" s="1"/>
     </row>
-    <row r="301" spans="1:22">
+    <row r="301" spans="1:22" ht="14.25">
       <c r="A301" s="7"/>
       <c r="B301" s="25"/>
       <c r="C301" s="3"/>
@@ -8627,7 +8594,7 @@
       <c r="U301" s="1"/>
       <c r="V301" s="1"/>
     </row>
-    <row r="302" spans="1:22">
+    <row r="302" spans="1:22" ht="14.25">
       <c r="A302" s="7"/>
       <c r="B302" s="25"/>
       <c r="C302" s="3"/>
@@ -8651,7 +8618,7 @@
       <c r="U302" s="1"/>
       <c r="V302" s="1"/>
     </row>
-    <row r="303" spans="1:22">
+    <row r="303" spans="1:22" ht="14.25">
       <c r="A303" s="7"/>
       <c r="B303" s="25"/>
       <c r="C303" s="3"/>
@@ -8675,7 +8642,7 @@
       <c r="U303" s="1"/>
       <c r="V303" s="1"/>
     </row>
-    <row r="304" spans="1:22">
+    <row r="304" spans="1:22" ht="14.25">
       <c r="A304" s="7"/>
       <c r="B304" s="25"/>
       <c r="C304" s="3"/>
@@ -8699,7 +8666,7 @@
       <c r="U304" s="1"/>
       <c r="V304" s="1"/>
     </row>
-    <row r="305" spans="1:22">
+    <row r="305" spans="1:22" ht="14.25">
       <c r="A305" s="7"/>
       <c r="B305" s="25"/>
       <c r="C305" s="3"/>
@@ -8723,7 +8690,7 @@
       <c r="U305" s="1"/>
       <c r="V305" s="1"/>
     </row>
-    <row r="306" spans="1:22">
+    <row r="306" spans="1:22" ht="14.25">
       <c r="A306" s="7"/>
       <c r="B306" s="25"/>
       <c r="C306" s="3"/>
@@ -8747,7 +8714,7 @@
       <c r="U306" s="1"/>
       <c r="V306" s="1"/>
     </row>
-    <row r="307" spans="1:22">
+    <row r="307" spans="1:22" ht="14.25">
       <c r="A307" s="7"/>
       <c r="B307" s="25"/>
       <c r="C307" s="3"/>
@@ -8771,7 +8738,7 @@
       <c r="U307" s="1"/>
       <c r="V307" s="1"/>
     </row>
-    <row r="308" spans="1:22">
+    <row r="308" spans="1:22" ht="14.25">
       <c r="A308" s="7"/>
       <c r="B308" s="25"/>
       <c r="C308" s="3"/>
@@ -8795,7 +8762,7 @@
       <c r="U308" s="1"/>
       <c r="V308" s="1"/>
     </row>
-    <row r="309" spans="1:22">
+    <row r="309" spans="1:22" ht="14.25">
       <c r="A309" s="7"/>
       <c r="B309" s="25"/>
       <c r="C309" s="3"/>
@@ -8819,7 +8786,7 @@
       <c r="U309" s="1"/>
       <c r="V309" s="1"/>
     </row>
-    <row r="310" spans="1:22">
+    <row r="310" spans="1:22" ht="14.25">
       <c r="A310" s="7"/>
       <c r="B310" s="25"/>
       <c r="C310" s="3"/>
@@ -8843,7 +8810,7 @@
       <c r="U310" s="1"/>
       <c r="V310" s="1"/>
     </row>
-    <row r="311" spans="1:22">
+    <row r="311" spans="1:22" ht="14.25">
       <c r="A311" s="7"/>
       <c r="B311" s="25"/>
       <c r="C311" s="3"/>
@@ -8867,7 +8834,7 @@
       <c r="U311" s="1"/>
       <c r="V311" s="1"/>
     </row>
-    <row r="312" spans="1:22">
+    <row r="312" spans="1:22" ht="14.25">
       <c r="A312" s="7"/>
       <c r="B312" s="25"/>
       <c r="C312" s="3"/>
@@ -8891,7 +8858,7 @@
       <c r="U312" s="1"/>
       <c r="V312" s="1"/>
     </row>
-    <row r="313" spans="1:22">
+    <row r="313" spans="1:22" ht="14.25">
       <c r="A313" s="7"/>
       <c r="B313" s="25"/>
       <c r="C313" s="3"/>
@@ -8915,7 +8882,7 @@
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
     </row>
-    <row r="314" spans="1:22">
+    <row r="314" spans="1:22" ht="14.25">
       <c r="A314" s="7"/>
       <c r="B314" s="25"/>
       <c r="C314" s="3"/>
@@ -8939,7 +8906,7 @@
       <c r="U314" s="1"/>
       <c r="V314" s="1"/>
     </row>
-    <row r="315" spans="1:22">
+    <row r="315" spans="1:22" ht="14.25">
       <c r="A315" s="7"/>
       <c r="B315" s="25"/>
       <c r="C315" s="3"/>
@@ -8963,7 +8930,7 @@
       <c r="U315" s="1"/>
       <c r="V315" s="1"/>
     </row>
-    <row r="316" spans="1:22">
+    <row r="316" spans="1:22" ht="14.25">
       <c r="A316" s="7"/>
       <c r="B316" s="25"/>
       <c r="C316" s="3"/>
@@ -8987,7 +8954,7 @@
       <c r="U316" s="1"/>
       <c r="V316" s="1"/>
     </row>
-    <row r="317" spans="1:22">
+    <row r="317" spans="1:22" ht="14.25">
       <c r="A317" s="7"/>
       <c r="B317" s="25"/>
       <c r="C317" s="3"/>
@@ -9011,7 +8978,7 @@
       <c r="U317" s="1"/>
       <c r="V317" s="1"/>
     </row>
-    <row r="318" spans="1:22">
+    <row r="318" spans="1:22" ht="14.25">
       <c r="A318" s="7"/>
       <c r="B318" s="25"/>
       <c r="C318" s="3"/>
@@ -9035,7 +9002,7 @@
       <c r="U318" s="1"/>
       <c r="V318" s="1"/>
     </row>
-    <row r="319" spans="1:22">
+    <row r="319" spans="1:22" ht="14.25">
       <c r="A319" s="7"/>
       <c r="B319" s="25"/>
       <c r="C319" s="3"/>
@@ -9059,7 +9026,7 @@
       <c r="U319" s="1"/>
       <c r="V319" s="1"/>
     </row>
-    <row r="320" spans="1:22">
+    <row r="320" spans="1:22" ht="14.25">
       <c r="A320" s="7"/>
       <c r="B320" s="25"/>
       <c r="C320" s="3"/>
@@ -9083,7 +9050,7 @@
       <c r="U320" s="1"/>
       <c r="V320" s="1"/>
     </row>
-    <row r="321" spans="1:22">
+    <row r="321" spans="1:22" ht="14.25">
       <c r="A321" s="7"/>
       <c r="B321" s="25"/>
       <c r="C321" s="3"/>
@@ -9107,7 +9074,7 @@
       <c r="U321" s="1"/>
       <c r="V321" s="1"/>
     </row>
-    <row r="322" spans="1:22">
+    <row r="322" spans="1:22" ht="14.25">
       <c r="A322" s="7"/>
       <c r="B322" s="25"/>
       <c r="C322" s="3"/>
@@ -9131,7 +9098,7 @@
       <c r="U322" s="1"/>
       <c r="V322" s="1"/>
     </row>
-    <row r="323" spans="1:22">
+    <row r="323" spans="1:22" ht="14.25">
       <c r="A323" s="7"/>
       <c r="B323" s="25"/>
       <c r="C323" s="3"/>
@@ -9155,7 +9122,7 @@
       <c r="U323" s="1"/>
       <c r="V323" s="1"/>
     </row>
-    <row r="324" spans="1:22">
+    <row r="324" spans="1:22" ht="14.25">
       <c r="A324" s="7"/>
       <c r="B324" s="25"/>
       <c r="C324" s="3"/>
@@ -9179,7 +9146,7 @@
       <c r="U324" s="1"/>
       <c r="V324" s="1"/>
     </row>
-    <row r="325" spans="1:22">
+    <row r="325" spans="1:22" ht="14.25">
       <c r="A325" s="7"/>
       <c r="B325" s="25"/>
       <c r="C325" s="3"/>
@@ -9203,7 +9170,7 @@
       <c r="U325" s="1"/>
       <c r="V325" s="1"/>
     </row>
-    <row r="326" spans="1:22">
+    <row r="326" spans="1:22" ht="14.25">
       <c r="A326" s="7"/>
       <c r="B326" s="25"/>
       <c r="C326" s="3"/>
@@ -9227,7 +9194,7 @@
       <c r="U326" s="1"/>
       <c r="V326" s="1"/>
     </row>
-    <row r="327" spans="1:22">
+    <row r="327" spans="1:22" ht="14.25">
       <c r="A327" s="7"/>
       <c r="B327" s="25"/>
       <c r="C327" s="3"/>
@@ -9251,7 +9218,7 @@
       <c r="U327" s="1"/>
       <c r="V327" s="1"/>
     </row>
-    <row r="328" spans="1:22">
+    <row r="328" spans="1:22" ht="14.25">
       <c r="A328" s="7"/>
       <c r="B328" s="25"/>
       <c r="C328" s="3"/>
@@ -9275,7 +9242,7 @@
       <c r="U328" s="1"/>
       <c r="V328" s="1"/>
     </row>
-    <row r="329" spans="1:22">
+    <row r="329" spans="1:22" ht="14.25">
       <c r="A329" s="7"/>
       <c r="B329" s="25"/>
       <c r="C329" s="3"/>
@@ -9299,7 +9266,7 @@
       <c r="U329" s="1"/>
       <c r="V329" s="1"/>
     </row>
-    <row r="330" spans="1:22">
+    <row r="330" spans="1:22" ht="14.25">
       <c r="A330" s="7"/>
       <c r="B330" s="25"/>
       <c r="C330" s="3"/>
@@ -9323,7 +9290,7 @@
       <c r="U330" s="1"/>
       <c r="V330" s="1"/>
     </row>
-    <row r="331" spans="1:22">
+    <row r="331" spans="1:22" ht="14.25">
       <c r="A331" s="7"/>
       <c r="B331" s="25"/>
       <c r="C331" s="3"/>
@@ -9347,7 +9314,7 @@
       <c r="U331" s="1"/>
       <c r="V331" s="1"/>
     </row>
-    <row r="332" spans="1:22">
+    <row r="332" spans="1:22" ht="14.25">
       <c r="A332" s="7"/>
       <c r="B332" s="25"/>
       <c r="C332" s="3"/>
@@ -9371,7 +9338,7 @@
       <c r="U332" s="1"/>
       <c r="V332" s="1"/>
     </row>
-    <row r="333" spans="1:22">
+    <row r="333" spans="1:22" ht="14.25">
       <c r="A333" s="7"/>
       <c r="B333" s="25"/>
       <c r="C333" s="3"/>
@@ -9395,7 +9362,7 @@
       <c r="U333" s="1"/>
       <c r="V333" s="1"/>
     </row>
-    <row r="334" spans="1:22">
+    <row r="334" spans="1:22" ht="14.25">
       <c r="A334" s="7"/>
       <c r="B334" s="25"/>
       <c r="C334" s="3"/>
@@ -9419,7 +9386,7 @@
       <c r="U334" s="1"/>
       <c r="V334" s="1"/>
     </row>
-    <row r="335" spans="1:22">
+    <row r="335" spans="1:22" ht="14.25">
       <c r="A335" s="7"/>
       <c r="B335" s="25"/>
       <c r="C335" s="3"/>
@@ -9443,7 +9410,7 @@
       <c r="U335" s="1"/>
       <c r="V335" s="1"/>
     </row>
-    <row r="336" spans="1:22">
+    <row r="336" spans="1:22" ht="14.25">
       <c r="A336" s="7"/>
       <c r="B336" s="25"/>
       <c r="C336" s="3"/>
@@ -9467,7 +9434,7 @@
       <c r="U336" s="1"/>
       <c r="V336" s="1"/>
     </row>
-    <row r="337" spans="1:22">
+    <row r="337" spans="1:22" ht="14.25">
       <c r="A337" s="7"/>
       <c r="B337" s="25"/>
       <c r="C337" s="3"/>
@@ -9491,7 +9458,7 @@
       <c r="U337" s="1"/>
       <c r="V337" s="1"/>
     </row>
-    <row r="338" spans="1:22">
+    <row r="338" spans="1:22" ht="14.25">
       <c r="A338" s="7"/>
       <c r="B338" s="25"/>
       <c r="C338" s="3"/>
@@ -9515,7 +9482,7 @@
       <c r="U338" s="1"/>
       <c r="V338" s="1"/>
     </row>
-    <row r="339" spans="1:22">
+    <row r="339" spans="1:22" ht="14.25">
       <c r="A339" s="7"/>
       <c r="B339" s="25"/>
       <c r="C339" s="3"/>
@@ -9539,7 +9506,7 @@
       <c r="U339" s="1"/>
       <c r="V339" s="1"/>
     </row>
-    <row r="340" spans="1:22">
+    <row r="340" spans="1:22" ht="14.25">
       <c r="A340" s="7"/>
       <c r="B340" s="25"/>
       <c r="C340" s="3"/>
@@ -9563,7 +9530,7 @@
       <c r="U340" s="1"/>
       <c r="V340" s="1"/>
     </row>
-    <row r="341" spans="1:22">
+    <row r="341" spans="1:22" ht="14.25">
       <c r="A341" s="7"/>
       <c r="B341" s="25"/>
       <c r="C341" s="3"/>
@@ -9587,7 +9554,7 @@
       <c r="U341" s="1"/>
       <c r="V341" s="1"/>
     </row>
-    <row r="342" spans="1:22">
+    <row r="342" spans="1:22" ht="14.25">
       <c r="A342" s="7"/>
       <c r="B342" s="25"/>
       <c r="C342" s="3"/>
@@ -9611,7 +9578,7 @@
       <c r="U342" s="1"/>
       <c r="V342" s="1"/>
     </row>
-    <row r="343" spans="1:22">
+    <row r="343" spans="1:22" ht="14.25">
       <c r="A343" s="7"/>
       <c r="B343" s="25"/>
       <c r="C343" s="3"/>
@@ -9635,7 +9602,7 @@
       <c r="U343" s="1"/>
       <c r="V343" s="1"/>
     </row>
-    <row r="344" spans="1:22">
+    <row r="344" spans="1:22" ht="14.25">
       <c r="A344" s="7"/>
       <c r="B344" s="25"/>
       <c r="C344" s="3"/>
@@ -9659,7 +9626,7 @@
       <c r="U344" s="1"/>
       <c r="V344" s="1"/>
     </row>
-    <row r="345" spans="1:22">
+    <row r="345" spans="1:22" ht="14.25">
       <c r="A345" s="7"/>
       <c r="B345" s="25"/>
       <c r="C345" s="3"/>
@@ -9683,7 +9650,7 @@
       <c r="U345" s="1"/>
       <c r="V345" s="1"/>
     </row>
-    <row r="346" spans="1:22">
+    <row r="346" spans="1:22" ht="14.25">
       <c r="A346" s="7"/>
       <c r="B346" s="25"/>
       <c r="C346" s="3"/>
@@ -9707,7 +9674,7 @@
       <c r="U346" s="1"/>
       <c r="V346" s="1"/>
     </row>
-    <row r="347" spans="1:22">
+    <row r="347" spans="1:22" ht="14.25">
       <c r="A347" s="7"/>
       <c r="B347" s="25"/>
       <c r="C347" s="3"/>
@@ -9731,7 +9698,7 @@
       <c r="U347" s="1"/>
       <c r="V347" s="1"/>
     </row>
-    <row r="348" spans="1:22">
+    <row r="348" spans="1:22" ht="14.25">
       <c r="A348" s="7"/>
       <c r="B348" s="25"/>
       <c r="C348" s="3"/>
@@ -9755,7 +9722,7 @@
       <c r="U348" s="1"/>
       <c r="V348" s="1"/>
     </row>
-    <row r="349" spans="1:22">
+    <row r="349" spans="1:22" ht="14.25">
       <c r="A349" s="7"/>
       <c r="B349" s="25"/>
       <c r="C349" s="3"/>
@@ -9779,7 +9746,7 @@
       <c r="U349" s="1"/>
       <c r="V349" s="1"/>
     </row>
-    <row r="350" spans="1:22">
+    <row r="350" spans="1:22" ht="14.25">
       <c r="A350" s="7"/>
       <c r="B350" s="25"/>
       <c r="C350" s="3"/>
@@ -9803,7 +9770,7 @@
       <c r="U350" s="1"/>
       <c r="V350" s="1"/>
     </row>
-    <row r="351" spans="1:22">
+    <row r="351" spans="1:22" ht="14.25">
       <c r="A351" s="7"/>
       <c r="B351" s="25"/>
       <c r="C351" s="3"/>
@@ -9827,7 +9794,7 @@
       <c r="U351" s="1"/>
       <c r="V351" s="1"/>
     </row>
-    <row r="352" spans="1:22">
+    <row r="352" spans="1:22" ht="14.25">
       <c r="A352" s="7"/>
       <c r="B352" s="25"/>
       <c r="C352" s="3"/>
@@ -9851,7 +9818,7 @@
       <c r="U352" s="1"/>
       <c r="V352" s="1"/>
     </row>
-    <row r="353" spans="1:22">
+    <row r="353" spans="1:22" ht="14.25">
       <c r="A353" s="7"/>
       <c r="B353" s="25"/>
       <c r="C353" s="3"/>
@@ -9875,7 +9842,7 @@
       <c r="U353" s="1"/>
       <c r="V353" s="1"/>
     </row>
-    <row r="354" spans="1:22">
+    <row r="354" spans="1:22" ht="14.25">
       <c r="A354" s="7"/>
       <c r="B354" s="25"/>
       <c r="C354" s="3"/>
@@ -9899,7 +9866,7 @@
       <c r="U354" s="1"/>
       <c r="V354" s="1"/>
     </row>
-    <row r="355" spans="1:22">
+    <row r="355" spans="1:22" ht="14.25">
       <c r="A355" s="7"/>
       <c r="B355" s="25"/>
       <c r="C355" s="3"/>
@@ -9923,7 +9890,7 @@
       <c r="U355" s="1"/>
       <c r="V355" s="1"/>
     </row>
-    <row r="356" spans="1:22">
+    <row r="356" spans="1:22" ht="14.25">
       <c r="A356" s="7"/>
       <c r="B356" s="25"/>
       <c r="C356" s="3"/>
@@ -9947,7 +9914,7 @@
       <c r="U356" s="1"/>
       <c r="V356" s="1"/>
     </row>
-    <row r="357" spans="1:22">
+    <row r="357" spans="1:22" ht="14.25">
       <c r="A357" s="7"/>
       <c r="B357" s="25"/>
       <c r="C357" s="3"/>
@@ -9971,7 +9938,7 @@
       <c r="U357" s="1"/>
       <c r="V357" s="1"/>
     </row>
-    <row r="358" spans="1:22">
+    <row r="358" spans="1:22" ht="14.25">
       <c r="A358" s="7"/>
       <c r="B358" s="25"/>
       <c r="C358" s="3"/>
@@ -9995,7 +9962,7 @@
       <c r="U358" s="1"/>
       <c r="V358" s="1"/>
     </row>
-    <row r="359" spans="1:22">
+    <row r="359" spans="1:22" ht="14.25">
       <c r="A359" s="7"/>
       <c r="B359" s="25"/>
       <c r="C359" s="3"/>
@@ -10019,7 +9986,7 @@
       <c r="U359" s="1"/>
       <c r="V359" s="1"/>
     </row>
-    <row r="360" spans="1:22">
+    <row r="360" spans="1:22" ht="14.25">
       <c r="A360" s="7"/>
       <c r="B360" s="25"/>
       <c r="C360" s="3"/>
@@ -10043,7 +10010,7 @@
       <c r="U360" s="1"/>
       <c r="V360" s="1"/>
     </row>
-    <row r="361" spans="1:22">
+    <row r="361" spans="1:22" ht="14.25">
       <c r="A361" s="7"/>
       <c r="B361" s="25"/>
       <c r="C361" s="3"/>
@@ -10067,7 +10034,7 @@
       <c r="U361" s="1"/>
       <c r="V361" s="1"/>
     </row>
-    <row r="362" spans="1:22">
+    <row r="362" spans="1:22" ht="14.25">
       <c r="A362" s="7"/>
       <c r="B362" s="25"/>
       <c r="C362" s="3"/>
@@ -10091,7 +10058,7 @@
       <c r="U362" s="1"/>
       <c r="V362" s="1"/>
     </row>
-    <row r="363" spans="1:22">
+    <row r="363" spans="1:22" ht="14.25">
       <c r="A363" s="7"/>
       <c r="B363" s="25"/>
       <c r="C363" s="3"/>
@@ -10115,7 +10082,7 @@
       <c r="U363" s="1"/>
       <c r="V363" s="1"/>
     </row>
-    <row r="364" spans="1:22">
+    <row r="364" spans="1:22" ht="14.25">
       <c r="A364" s="7"/>
       <c r="B364" s="25"/>
       <c r="C364" s="3"/>
@@ -10139,7 +10106,7 @@
       <c r="U364" s="1"/>
       <c r="V364" s="1"/>
     </row>
-    <row r="365" spans="1:22">
+    <row r="365" spans="1:22" ht="14.25">
       <c r="A365" s="7"/>
       <c r="B365" s="25"/>
       <c r="C365" s="3"/>
@@ -10163,7 +10130,7 @@
       <c r="U365" s="1"/>
       <c r="V365" s="1"/>
     </row>
-    <row r="366" spans="1:22">
+    <row r="366" spans="1:22" ht="14.25">
       <c r="A366" s="7"/>
       <c r="B366" s="25"/>
       <c r="C366" s="3"/>
@@ -10187,7 +10154,7 @@
       <c r="U366" s="1"/>
       <c r="V366" s="1"/>
     </row>
-    <row r="367" spans="1:22">
+    <row r="367" spans="1:22" ht="14.25">
       <c r="A367" s="7"/>
       <c r="B367" s="25"/>
       <c r="C367" s="3"/>
@@ -10211,7 +10178,7 @@
       <c r="U367" s="1"/>
       <c r="V367" s="1"/>
     </row>
-    <row r="368" spans="1:22">
+    <row r="368" spans="1:22" ht="14.25">
       <c r="A368" s="7"/>
       <c r="B368" s="25"/>
       <c r="C368" s="3"/>
@@ -10235,7 +10202,7 @@
       <c r="U368" s="1"/>
       <c r="V368" s="1"/>
     </row>
-    <row r="369" spans="1:22">
+    <row r="369" spans="1:22" ht="14.25">
       <c r="A369" s="7"/>
       <c r="B369" s="25"/>
       <c r="C369" s="3"/>
@@ -10259,7 +10226,7 @@
       <c r="U369" s="1"/>
       <c r="V369" s="1"/>
     </row>
-    <row r="370" spans="1:22">
+    <row r="370" spans="1:22" ht="14.25">
       <c r="A370" s="7"/>
       <c r="B370" s="25"/>
       <c r="C370" s="3"/>
@@ -10283,7 +10250,7 @@
       <c r="U370" s="1"/>
       <c r="V370" s="1"/>
     </row>
-    <row r="371" spans="1:22">
+    <row r="371" spans="1:22" ht="14.25">
       <c r="A371" s="7"/>
       <c r="B371" s="25"/>
       <c r="C371" s="3"/>
@@ -10307,7 +10274,7 @@
       <c r="U371" s="1"/>
       <c r="V371" s="1"/>
     </row>
-    <row r="372" spans="1:22">
+    <row r="372" spans="1:22" ht="14.25">
       <c r="A372" s="7"/>
       <c r="B372" s="25"/>
       <c r="C372" s="3"/>
@@ -10331,7 +10298,7 @@
       <c r="U372" s="1"/>
       <c r="V372" s="1"/>
     </row>
-    <row r="373" spans="1:22">
+    <row r="373" spans="1:22" ht="14.25">
       <c r="A373" s="7"/>
       <c r="B373" s="25"/>
       <c r="C373" s="3"/>
@@ -10355,7 +10322,7 @@
       <c r="U373" s="1"/>
       <c r="V373" s="1"/>
     </row>
-    <row r="374" spans="1:22">
+    <row r="374" spans="1:22" ht="14.25">
       <c r="A374" s="7"/>
       <c r="B374" s="25"/>
       <c r="C374" s="3"/>
@@ -10379,7 +10346,7 @@
       <c r="U374" s="1"/>
       <c r="V374" s="1"/>
     </row>
-    <row r="375" spans="1:22">
+    <row r="375" spans="1:22" ht="14.25">
       <c r="A375" s="7"/>
       <c r="B375" s="25"/>
       <c r="C375" s="3"/>
@@ -10403,7 +10370,7 @@
       <c r="U375" s="1"/>
       <c r="V375" s="1"/>
     </row>
-    <row r="376" spans="1:22">
+    <row r="376" spans="1:22" ht="14.25">
       <c r="A376" s="7"/>
       <c r="B376" s="25"/>
       <c r="C376" s="3"/>
@@ -10427,7 +10394,7 @@
       <c r="U376" s="1"/>
       <c r="V376" s="1"/>
     </row>
-    <row r="377" spans="1:22">
+    <row r="377" spans="1:22" ht="14.25">
       <c r="A377" s="7"/>
       <c r="B377" s="25"/>
       <c r="C377" s="3"/>
@@ -10451,7 +10418,7 @@
       <c r="U377" s="1"/>
       <c r="V377" s="1"/>
     </row>
-    <row r="378" spans="1:22">
+    <row r="378" spans="1:22" ht="14.25">
       <c r="A378" s="7"/>
       <c r="B378" s="25"/>
       <c r="C378" s="3"/>
@@ -10475,7 +10442,7 @@
       <c r="U378" s="1"/>
       <c r="V378" s="1"/>
     </row>
-    <row r="379" spans="1:22">
+    <row r="379" spans="1:22" ht="14.25">
       <c r="A379" s="7"/>
       <c r="B379" s="25"/>
       <c r="C379" s="3"/>
@@ -10499,7 +10466,7 @@
       <c r="U379" s="1"/>
       <c r="V379" s="1"/>
     </row>
-    <row r="380" spans="1:22">
+    <row r="380" spans="1:22" ht="14.25">
       <c r="A380" s="7"/>
       <c r="B380" s="25"/>
       <c r="C380" s="3"/>
@@ -10523,7 +10490,7 @@
       <c r="U380" s="1"/>
       <c r="V380" s="1"/>
     </row>
-    <row r="381" spans="1:22">
+    <row r="381" spans="1:22" ht="14.25">
       <c r="A381" s="7"/>
       <c r="B381" s="25"/>
       <c r="C381" s="3"/>
@@ -10547,7 +10514,7 @@
       <c r="U381" s="1"/>
       <c r="V381" s="1"/>
     </row>
-    <row r="382" spans="1:22">
+    <row r="382" spans="1:22" ht="14.25">
       <c r="A382" s="7"/>
       <c r="B382" s="25"/>
       <c r="C382" s="3"/>
@@ -10571,7 +10538,7 @@
       <c r="U382" s="1"/>
       <c r="V382" s="1"/>
     </row>
-    <row r="383" spans="1:22">
+    <row r="383" spans="1:22" ht="14.25">
       <c r="A383" s="7"/>
       <c r="B383" s="25"/>
       <c r="C383" s="3"/>
@@ -10595,7 +10562,7 @@
       <c r="U383" s="1"/>
       <c r="V383" s="1"/>
     </row>
-    <row r="384" spans="1:22">
+    <row r="384" spans="1:22" ht="14.25">
       <c r="A384" s="7"/>
       <c r="B384" s="25"/>
       <c r="C384" s="3"/>
@@ -10619,7 +10586,7 @@
       <c r="U384" s="1"/>
       <c r="V384" s="1"/>
     </row>
-    <row r="385" spans="1:22">
+    <row r="385" spans="1:22" ht="14.25">
       <c r="A385" s="7"/>
       <c r="B385" s="25"/>
       <c r="C385" s="3"/>
@@ -10643,7 +10610,7 @@
       <c r="U385" s="1"/>
       <c r="V385" s="1"/>
     </row>
-    <row r="386" spans="1:22">
+    <row r="386" spans="1:22" ht="14.25">
       <c r="A386" s="7"/>
       <c r="B386" s="25"/>
       <c r="C386" s="3"/>
@@ -10667,7 +10634,7 @@
       <c r="U386" s="1"/>
       <c r="V386" s="1"/>
     </row>
-    <row r="387" spans="1:22">
+    <row r="387" spans="1:22" ht="14.25">
       <c r="A387" s="7"/>
       <c r="B387" s="25"/>
       <c r="C387" s="3"/>
@@ -10691,7 +10658,7 @@
       <c r="U387" s="1"/>
       <c r="V387" s="1"/>
     </row>
-    <row r="388" spans="1:22">
+    <row r="388" spans="1:22" ht="14.25">
       <c r="A388" s="7"/>
       <c r="B388" s="25"/>
       <c r="C388" s="3"/>
@@ -10715,7 +10682,7 @@
       <c r="U388" s="1"/>
       <c r="V388" s="1"/>
     </row>
-    <row r="389" spans="1:22">
+    <row r="389" spans="1:22" ht="14.25">
       <c r="A389" s="7"/>
       <c r="B389" s="25"/>
       <c r="C389" s="3"/>
@@ -10739,7 +10706,7 @@
       <c r="U389" s="1"/>
       <c r="V389" s="1"/>
     </row>
-    <row r="390" spans="1:22">
+    <row r="390" spans="1:22" ht="14.25">
       <c r="A390" s="7"/>
       <c r="B390" s="25"/>
       <c r="C390" s="3"/>
@@ -10763,7 +10730,7 @@
       <c r="U390" s="1"/>
       <c r="V390" s="1"/>
     </row>
-    <row r="391" spans="1:22">
+    <row r="391" spans="1:22" ht="14.25">
       <c r="A391" s="7"/>
       <c r="B391" s="25"/>
       <c r="C391" s="3"/>
@@ -10787,7 +10754,7 @@
       <c r="U391" s="1"/>
       <c r="V391" s="1"/>
     </row>
-    <row r="392" spans="1:22">
+    <row r="392" spans="1:22" ht="14.25">
       <c r="A392" s="7"/>
       <c r="B392" s="25"/>
       <c r="C392" s="3"/>
@@ -10811,7 +10778,7 @@
       <c r="U392" s="1"/>
       <c r="V392" s="1"/>
     </row>
-    <row r="393" spans="1:22">
+    <row r="393" spans="1:22" ht="14.25">
       <c r="A393" s="7"/>
       <c r="B393" s="25"/>
       <c r="C393" s="3"/>
@@ -10835,7 +10802,7 @@
       <c r="U393" s="1"/>
       <c r="V393" s="1"/>
     </row>
-    <row r="394" spans="1:22">
+    <row r="394" spans="1:22" ht="14.25">
       <c r="A394" s="7"/>
       <c r="B394" s="25"/>
       <c r="C394" s="3"/>
@@ -10859,7 +10826,7 @@
       <c r="U394" s="1"/>
       <c r="V394" s="1"/>
     </row>
-    <row r="395" spans="1:22">
+    <row r="395" spans="1:22" ht="14.25">
       <c r="A395" s="7"/>
       <c r="B395" s="25"/>
       <c r="C395" s="3"/>
@@ -10883,7 +10850,7 @@
       <c r="U395" s="1"/>
       <c r="V395" s="1"/>
     </row>
-    <row r="396" spans="1:22">
+    <row r="396" spans="1:22" ht="14.25">
       <c r="A396" s="7"/>
       <c r="B396" s="25"/>
       <c r="C396" s="3"/>
@@ -10907,7 +10874,7 @@
       <c r="U396" s="1"/>
       <c r="V396" s="1"/>
     </row>
-    <row r="397" spans="1:22">
+    <row r="397" spans="1:22" ht="14.25">
       <c r="A397" s="7"/>
       <c r="B397" s="25"/>
       <c r="C397" s="3"/>
@@ -10931,7 +10898,7 @@
       <c r="U397" s="1"/>
       <c r="V397" s="1"/>
     </row>
-    <row r="398" spans="1:22">
+    <row r="398" spans="1:22" ht="14.25">
       <c r="A398" s="7"/>
       <c r="B398" s="25"/>
       <c r="C398" s="3"/>
@@ -10955,7 +10922,7 @@
       <c r="U398" s="1"/>
       <c r="V398" s="1"/>
     </row>
-    <row r="399" spans="1:22">
+    <row r="399" spans="1:22" ht="14.25">
       <c r="A399" s="7"/>
       <c r="B399" s="25"/>
       <c r="C399" s="3"/>
@@ -10979,7 +10946,7 @@
       <c r="U399" s="1"/>
       <c r="V399" s="1"/>
     </row>
-    <row r="400" spans="1:22">
+    <row r="400" spans="1:22" ht="14.25">
       <c r="A400" s="7"/>
       <c r="B400" s="25"/>
       <c r="C400" s="3"/>
@@ -11003,7 +10970,7 @@
       <c r="U400" s="1"/>
       <c r="V400" s="1"/>
     </row>
-    <row r="401" spans="1:22">
+    <row r="401" spans="1:22" ht="14.25">
       <c r="A401" s="7"/>
       <c r="B401" s="25"/>
       <c r="C401" s="3"/>
@@ -11027,7 +10994,7 @@
       <c r="U401" s="1"/>
       <c r="V401" s="1"/>
     </row>
-    <row r="402" spans="1:22">
+    <row r="402" spans="1:22" ht="14.25">
       <c r="A402" s="7"/>
       <c r="B402" s="25"/>
       <c r="C402" s="3"/>
@@ -11051,7 +11018,7 @@
       <c r="U402" s="1"/>
       <c r="V402" s="1"/>
     </row>
-    <row r="403" spans="1:22">
+    <row r="403" spans="1:22" ht="14.25">
       <c r="A403" s="7"/>
       <c r="B403" s="25"/>
       <c r="C403" s="3"/>
@@ -11075,7 +11042,7 @@
       <c r="U403" s="1"/>
       <c r="V403" s="1"/>
     </row>
-    <row r="404" spans="1:22">
+    <row r="404" spans="1:22" ht="14.25">
       <c r="A404" s="7"/>
       <c r="B404" s="25"/>
       <c r="C404" s="3"/>
@@ -11099,7 +11066,7 @@
       <c r="U404" s="1"/>
       <c r="V404" s="1"/>
     </row>
-    <row r="405" spans="1:22">
+    <row r="405" spans="1:22" ht="14.25">
       <c r="A405" s="7"/>
       <c r="B405" s="25"/>
       <c r="C405" s="3"/>
@@ -11123,7 +11090,7 @@
       <c r="U405" s="1"/>
       <c r="V405" s="1"/>
     </row>
-    <row r="406" spans="1:22">
+    <row r="406" spans="1:22" ht="14.25">
       <c r="A406" s="7"/>
       <c r="B406" s="25"/>
       <c r="C406" s="3"/>
@@ -11147,7 +11114,7 @@
       <c r="U406" s="1"/>
       <c r="V406" s="1"/>
     </row>
-    <row r="407" spans="1:22">
+    <row r="407" spans="1:22" ht="14.25">
       <c r="A407" s="7"/>
       <c r="B407" s="25"/>
       <c r="C407" s="3"/>
@@ -11171,7 +11138,7 @@
       <c r="U407" s="1"/>
       <c r="V407" s="1"/>
     </row>
-    <row r="408" spans="1:22">
+    <row r="408" spans="1:22" ht="14.25">
       <c r="A408" s="7"/>
       <c r="B408" s="25"/>
       <c r="C408" s="3"/>
@@ -11195,7 +11162,7 @@
       <c r="U408" s="1"/>
       <c r="V408" s="1"/>
     </row>
-    <row r="409" spans="1:22">
+    <row r="409" spans="1:22" ht="14.25">
       <c r="A409" s="7"/>
       <c r="B409" s="25"/>
       <c r="C409" s="3"/>
@@ -11219,7 +11186,7 @@
       <c r="U409" s="1"/>
       <c r="V409" s="1"/>
     </row>
-    <row r="410" spans="1:22">
+    <row r="410" spans="1:22" ht="14.25">
       <c r="A410" s="7"/>
       <c r="B410" s="25"/>
       <c r="C410" s="3"/>
@@ -11243,7 +11210,7 @@
       <c r="U410" s="1"/>
       <c r="V410" s="1"/>
     </row>
-    <row r="411" spans="1:22">
+    <row r="411" spans="1:22" ht="14.25">
       <c r="A411" s="7"/>
       <c r="B411" s="25"/>
       <c r="C411" s="3"/>
@@ -11267,7 +11234,7 @@
       <c r="U411" s="1"/>
       <c r="V411" s="1"/>
     </row>
-    <row r="412" spans="1:22">
+    <row r="412" spans="1:22" ht="14.25">
       <c r="A412" s="7"/>
       <c r="B412" s="25"/>
       <c r="C412" s="3"/>
@@ -11291,7 +11258,7 @@
       <c r="U412" s="1"/>
       <c r="V412" s="1"/>
     </row>
-    <row r="413" spans="1:22">
+    <row r="413" spans="1:22" ht="14.25">
       <c r="A413" s="7"/>
       <c r="B413" s="25"/>
       <c r="C413" s="3"/>
@@ -11315,7 +11282,7 @@
       <c r="U413" s="1"/>
       <c r="V413" s="1"/>
     </row>
-    <row r="414" spans="1:22">
+    <row r="414" spans="1:22" ht="14.25">
       <c r="A414" s="7"/>
       <c r="B414" s="25"/>
       <c r="C414" s="3"/>
@@ -11339,7 +11306,7 @@
       <c r="U414" s="1"/>
       <c r="V414" s="1"/>
     </row>
-    <row r="415" spans="1:22">
+    <row r="415" spans="1:22" ht="14.25">
       <c r="A415" s="7"/>
       <c r="B415" s="25"/>
       <c r="C415" s="3"/>
@@ -11363,7 +11330,7 @@
       <c r="U415" s="1"/>
       <c r="V415" s="1"/>
     </row>
-    <row r="416" spans="1:22">
+    <row r="416" spans="1:22" ht="14.25">
       <c r="A416" s="7"/>
       <c r="B416" s="25"/>
       <c r="C416" s="3"/>
@@ -11387,7 +11354,7 @@
       <c r="U416" s="1"/>
       <c r="V416" s="1"/>
     </row>
-    <row r="417" spans="1:22">
+    <row r="417" spans="1:22" ht="14.25">
       <c r="A417" s="7"/>
       <c r="B417" s="25"/>
       <c r="C417" s="3"/>
@@ -11411,7 +11378,7 @@
       <c r="U417" s="1"/>
       <c r="V417" s="1"/>
     </row>
-    <row r="418" spans="1:22">
+    <row r="418" spans="1:22" ht="14.25">
       <c r="A418" s="7"/>
       <c r="B418" s="25"/>
       <c r="C418" s="3"/>
@@ -11435,7 +11402,7 @@
       <c r="U418" s="1"/>
       <c r="V418" s="1"/>
     </row>
-    <row r="419" spans="1:22">
+    <row r="419" spans="1:22" ht="14.25">
       <c r="A419" s="7"/>
       <c r="B419" s="25"/>
       <c r="C419" s="3"/>
@@ -11459,7 +11426,7 @@
       <c r="U419" s="1"/>
       <c r="V419" s="1"/>
     </row>
-    <row r="420" spans="1:22">
+    <row r="420" spans="1:22" ht="14.25">
       <c r="A420" s="7"/>
       <c r="B420" s="25"/>
       <c r="C420" s="3"/>
@@ -11483,7 +11450,7 @@
       <c r="U420" s="1"/>
       <c r="V420" s="1"/>
     </row>
-    <row r="421" spans="1:22">
+    <row r="421" spans="1:22" ht="14.25">
       <c r="A421" s="7"/>
       <c r="B421" s="25"/>
       <c r="C421" s="3"/>
@@ -11507,7 +11474,7 @@
       <c r="U421" s="1"/>
       <c r="V421" s="1"/>
     </row>
-    <row r="422" spans="1:22">
+    <row r="422" spans="1:22" ht="14.25">
       <c r="A422" s="7"/>
       <c r="B422" s="25"/>
       <c r="C422" s="3"/>
@@ -11531,7 +11498,7 @@
       <c r="U422" s="1"/>
       <c r="V422" s="1"/>
     </row>
-    <row r="423" spans="1:22">
+    <row r="423" spans="1:22" ht="14.25">
       <c r="A423" s="7"/>
       <c r="B423" s="25"/>
       <c r="C423" s="3"/>
@@ -11555,7 +11522,7 @@
       <c r="U423" s="1"/>
       <c r="V423" s="1"/>
     </row>
-    <row r="424" spans="1:22">
+    <row r="424" spans="1:22" ht="14.25">
       <c r="A424" s="7"/>
       <c r="B424" s="25"/>
       <c r="C424" s="3"/>
@@ -11579,7 +11546,7 @@
       <c r="U424" s="1"/>
       <c r="V424" s="1"/>
     </row>
-    <row r="425" spans="1:22">
+    <row r="425" spans="1:22" ht="14.25">
       <c r="A425" s="7"/>
       <c r="B425" s="25"/>
       <c r="C425" s="3"/>
@@ -11603,7 +11570,7 @@
       <c r="U425" s="1"/>
       <c r="V425" s="1"/>
     </row>
-    <row r="426" spans="1:22">
+    <row r="426" spans="1:22" ht="14.25">
       <c r="A426" s="7"/>
       <c r="B426" s="25"/>
       <c r="C426" s="3"/>
@@ -11627,7 +11594,7 @@
       <c r="U426" s="1"/>
       <c r="V426" s="1"/>
     </row>
-    <row r="427" spans="1:22">
+    <row r="427" spans="1:22" ht="14.25">
       <c r="A427" s="7"/>
       <c r="B427" s="25"/>
       <c r="C427" s="3"/>
@@ -11651,7 +11618,7 @@
       <c r="U427" s="1"/>
       <c r="V427" s="1"/>
     </row>
-    <row r="428" spans="1:22">
+    <row r="428" spans="1:22" ht="14.25">
       <c r="A428" s="7"/>
       <c r="B428" s="25"/>
       <c r="C428" s="3"/>
@@ -11675,7 +11642,7 @@
       <c r="U428" s="1"/>
       <c r="V428" s="1"/>
     </row>
-    <row r="429" spans="1:22">
+    <row r="429" spans="1:22" ht="14.25">
       <c r="A429" s="7"/>
       <c r="B429" s="25"/>
       <c r="C429" s="3"/>
@@ -11699,7 +11666,7 @@
       <c r="U429" s="1"/>
       <c r="V429" s="1"/>
     </row>
-    <row r="430" spans="1:22">
+    <row r="430" spans="1:22" ht="14.25">
       <c r="A430" s="7"/>
       <c r="B430" s="25"/>
       <c r="C430" s="3"/>
@@ -11723,7 +11690,7 @@
       <c r="U430" s="1"/>
       <c r="V430" s="1"/>
     </row>
-    <row r="431" spans="1:22">
+    <row r="431" spans="1:22" ht="14.25">
       <c r="A431" s="7"/>
       <c r="B431" s="25"/>
       <c r="C431" s="3"/>
@@ -11747,7 +11714,7 @@
       <c r="U431" s="1"/>
       <c r="V431" s="1"/>
     </row>
-    <row r="432" spans="1:22">
+    <row r="432" spans="1:22" ht="14.25">
       <c r="A432" s="7"/>
       <c r="B432" s="25"/>
       <c r="C432" s="3"/>
@@ -11771,7 +11738,7 @@
       <c r="U432" s="1"/>
       <c r="V432" s="1"/>
     </row>
-    <row r="433" spans="1:22">
+    <row r="433" spans="1:22" ht="14.25">
       <c r="A433" s="7"/>
       <c r="B433" s="25"/>
       <c r="C433" s="3"/>
@@ -11795,7 +11762,7 @@
       <c r="U433" s="1"/>
       <c r="V433" s="1"/>
     </row>
-    <row r="434" spans="1:22">
+    <row r="434" spans="1:22" ht="14.25">
       <c r="A434" s="7"/>
       <c r="B434" s="25"/>
       <c r="C434" s="3"/>
@@ -11819,7 +11786,7 @@
       <c r="U434" s="1"/>
       <c r="V434" s="1"/>
     </row>
-    <row r="435" spans="1:22">
+    <row r="435" spans="1:22" ht="14.25">
       <c r="A435" s="7"/>
       <c r="B435" s="25"/>
       <c r="C435" s="3"/>
@@ -11843,7 +11810,7 @@
       <c r="U435" s="1"/>
       <c r="V435" s="1"/>
     </row>
-    <row r="436" spans="1:22">
+    <row r="436" spans="1:22" ht="14.25">
       <c r="A436" s="7"/>
       <c r="B436" s="25"/>
       <c r="C436" s="3"/>
@@ -11867,7 +11834,7 @@
       <c r="U436" s="1"/>
       <c r="V436" s="1"/>
     </row>
-    <row r="437" spans="1:22">
+    <row r="437" spans="1:22" ht="14.25">
       <c r="A437" s="7"/>
       <c r="B437" s="25"/>
       <c r="C437" s="3"/>
@@ -11891,7 +11858,7 @@
       <c r="U437" s="1"/>
       <c r="V437" s="1"/>
     </row>
-    <row r="438" spans="1:22">
+    <row r="438" spans="1:22" ht="14.25">
       <c r="A438" s="7"/>
       <c r="B438" s="25"/>
       <c r="C438" s="3"/>
@@ -11915,7 +11882,7 @@
       <c r="U438" s="1"/>
       <c r="V438" s="1"/>
     </row>
-    <row r="439" spans="1:22">
+    <row r="439" spans="1:22" ht="14.25">
       <c r="A439" s="7"/>
       <c r="B439" s="25"/>
       <c r="C439" s="3"/>
@@ -11939,7 +11906,7 @@
       <c r="U439" s="1"/>
       <c r="V439" s="1"/>
     </row>
-    <row r="440" spans="1:22">
+    <row r="440" spans="1:22" ht="14.25">
       <c r="A440" s="7"/>
       <c r="B440" s="25"/>
       <c r="C440" s="3"/>
@@ -11963,7 +11930,7 @@
       <c r="U440" s="1"/>
       <c r="V440" s="1"/>
     </row>
-    <row r="441" spans="1:22">
+    <row r="441" spans="1:22" ht="14.25">
       <c r="A441" s="7"/>
       <c r="B441" s="25"/>
       <c r="C441" s="3"/>
@@ -11987,7 +11954,7 @@
       <c r="U441" s="1"/>
       <c r="V441" s="1"/>
     </row>
-    <row r="442" spans="1:22">
+    <row r="442" spans="1:22" ht="14.25">
       <c r="A442" s="7"/>
       <c r="B442" s="25"/>
       <c r="C442" s="3"/>
@@ -12011,7 +11978,7 @@
       <c r="U442" s="1"/>
       <c r="V442" s="1"/>
     </row>
-    <row r="443" spans="1:22">
+    <row r="443" spans="1:22" ht="14.25">
       <c r="A443" s="7"/>
       <c r="B443" s="25"/>
       <c r="C443" s="3"/>
@@ -12035,7 +12002,7 @@
       <c r="U443" s="1"/>
       <c r="V443" s="1"/>
     </row>
-    <row r="444" spans="1:22">
+    <row r="444" spans="1:22" ht="14.25">
       <c r="A444" s="7"/>
       <c r="B444" s="25"/>
       <c r="C444" s="3"/>
@@ -12059,7 +12026,7 @@
       <c r="U444" s="1"/>
       <c r="V444" s="1"/>
     </row>
-    <row r="445" spans="1:22">
+    <row r="445" spans="1:22" ht="14.25">
       <c r="A445" s="7"/>
       <c r="B445" s="25"/>
       <c r="C445" s="3"/>
@@ -12083,7 +12050,7 @@
       <c r="U445" s="1"/>
       <c r="V445" s="1"/>
     </row>
-    <row r="446" spans="1:22">
+    <row r="446" spans="1:22" ht="14.25">
       <c r="A446" s="7"/>
       <c r="B446" s="25"/>
       <c r="C446" s="3"/>
@@ -12107,7 +12074,7 @@
       <c r="U446" s="1"/>
       <c r="V446" s="1"/>
     </row>
-    <row r="447" spans="1:22">
+    <row r="447" spans="1:22" ht="14.25">
       <c r="A447" s="7"/>
       <c r="B447" s="25"/>
       <c r="C447" s="3"/>
@@ -12131,7 +12098,7 @@
       <c r="U447" s="1"/>
       <c r="V447" s="1"/>
     </row>
-    <row r="448" spans="1:22">
+    <row r="448" spans="1:22" ht="14.25">
       <c r="A448" s="7"/>
       <c r="B448" s="25"/>
       <c r="C448" s="3"/>
@@ -12155,7 +12122,7 @@
       <c r="U448" s="1"/>
       <c r="V448" s="1"/>
     </row>
-    <row r="449" spans="1:22">
+    <row r="449" spans="1:22" ht="14.25">
       <c r="A449" s="7"/>
       <c r="B449" s="25"/>
       <c r="C449" s="3"/>
@@ -12179,7 +12146,7 @@
       <c r="U449" s="1"/>
       <c r="V449" s="1"/>
     </row>
-    <row r="450" spans="1:22">
+    <row r="450" spans="1:22" ht="14.25">
       <c r="A450" s="7"/>
       <c r="B450" s="25"/>
       <c r="C450" s="3"/>
@@ -12203,7 +12170,7 @@
       <c r="U450" s="1"/>
       <c r="V450" s="1"/>
     </row>
-    <row r="451" spans="1:22">
+    <row r="451" spans="1:22" ht="14.25">
       <c r="A451" s="7"/>
       <c r="B451" s="25"/>
       <c r="C451" s="3"/>
@@ -12227,7 +12194,7 @@
       <c r="U451" s="1"/>
       <c r="V451" s="1"/>
     </row>
-    <row r="452" spans="1:22">
+    <row r="452" spans="1:22" ht="14.25">
       <c r="A452" s="7"/>
       <c r="B452" s="25"/>
       <c r="C452" s="3"/>
@@ -12251,7 +12218,7 @@
       <c r="U452" s="1"/>
       <c r="V452" s="1"/>
     </row>
-    <row r="453" spans="1:22">
+    <row r="453" spans="1:22" ht="14.25">
       <c r="A453" s="7"/>
       <c r="B453" s="25"/>
       <c r="C453" s="3"/>
@@ -12275,7 +12242,7 @@
       <c r="U453" s="1"/>
       <c r="V453" s="1"/>
     </row>
-    <row r="454" spans="1:22">
+    <row r="454" spans="1:22" ht="14.25">
       <c r="A454" s="7"/>
       <c r="B454" s="25"/>
       <c r="C454" s="3"/>
@@ -12299,7 +12266,7 @@
       <c r="U454" s="1"/>
       <c r="V454" s="1"/>
     </row>
-    <row r="455" spans="1:22">
+    <row r="455" spans="1:22" ht="14.25">
       <c r="A455" s="7"/>
       <c r="B455" s="25"/>
       <c r="C455" s="3"/>
@@ -12323,7 +12290,7 @@
       <c r="U455" s="1"/>
       <c r="V455" s="1"/>
     </row>
-    <row r="456" spans="1:22">
+    <row r="456" spans="1:22" ht="14.25">
       <c r="A456" s="7"/>
       <c r="B456" s="25"/>
       <c r="C456" s="3"/>
@@ -12347,7 +12314,7 @@
       <c r="U456" s="1"/>
       <c r="V456" s="1"/>
     </row>
-    <row r="457" spans="1:22">
+    <row r="457" spans="1:22" ht="14.25">
       <c r="A457" s="7"/>
       <c r="B457" s="25"/>
       <c r="C457" s="3"/>
@@ -12371,7 +12338,7 @@
       <c r="U457" s="1"/>
       <c r="V457" s="1"/>
     </row>
-    <row r="458" spans="1:22">
+    <row r="458" spans="1:22" ht="14.25">
       <c r="A458" s="7"/>
       <c r="B458" s="25"/>
       <c r="C458" s="3"/>
@@ -12395,7 +12362,7 @@
       <c r="U458" s="1"/>
       <c r="V458" s="1"/>
     </row>
-    <row r="459" spans="1:22">
+    <row r="459" spans="1:22" ht="14.25">
       <c r="A459" s="7"/>
       <c r="B459" s="25"/>
       <c r="C459" s="3"/>
@@ -12419,7 +12386,7 @@
       <c r="U459" s="1"/>
       <c r="V459" s="1"/>
     </row>
-    <row r="460" spans="1:22">
+    <row r="460" spans="1:22" ht="14.25">
       <c r="A460" s="7"/>
       <c r="B460" s="25"/>
       <c r="C460" s="3"/>
@@ -12443,7 +12410,7 @@
       <c r="U460" s="1"/>
       <c r="V460" s="1"/>
     </row>
-    <row r="461" spans="1:22">
+    <row r="461" spans="1:22" ht="14.25">
       <c r="A461" s="7"/>
       <c r="B461" s="25"/>
       <c r="C461" s="3"/>
@@ -12467,7 +12434,7 @@
       <c r="U461" s="1"/>
       <c r="V461" s="1"/>
     </row>
-    <row r="462" spans="1:22">
+    <row r="462" spans="1:22" ht="14.25">
       <c r="A462" s="7"/>
       <c r="B462" s="25"/>
       <c r="C462" s="3"/>
@@ -12491,7 +12458,7 @@
       <c r="U462" s="1"/>
       <c r="V462" s="1"/>
     </row>
-    <row r="463" spans="1:22">
+    <row r="463" spans="1:22" ht="14.25">
       <c r="A463" s="7"/>
       <c r="B463" s="25"/>
       <c r="C463" s="3"/>
@@ -12515,7 +12482,7 @@
       <c r="U463" s="1"/>
       <c r="V463" s="1"/>
     </row>
-    <row r="464" spans="1:22">
+    <row r="464" spans="1:22" ht="14.25">
       <c r="A464" s="7"/>
       <c r="B464" s="25"/>
       <c r="C464" s="3"/>
@@ -12539,7 +12506,7 @@
       <c r="U464" s="1"/>
       <c r="V464" s="1"/>
     </row>
-    <row r="465" spans="1:22">
+    <row r="465" spans="1:22" ht="14.25">
       <c r="A465" s="7"/>
       <c r="B465" s="25"/>
       <c r="C465" s="3"/>
@@ -12563,7 +12530,7 @@
       <c r="U465" s="1"/>
       <c r="V465" s="1"/>
     </row>
-    <row r="466" spans="1:22">
+    <row r="466" spans="1:22" ht="14.25">
       <c r="A466" s="7"/>
       <c r="B466" s="25"/>
       <c r="C466" s="3"/>
@@ -12587,7 +12554,7 @@
       <c r="U466" s="1"/>
       <c r="V466" s="1"/>
     </row>
-    <row r="467" spans="1:22">
+    <row r="467" spans="1:22" ht="14.25">
       <c r="A467" s="7"/>
       <c r="B467" s="25"/>
       <c r="C467" s="3"/>
@@ -12611,7 +12578,7 @@
       <c r="U467" s="1"/>
       <c r="V467" s="1"/>
     </row>
-    <row r="468" spans="1:22">
+    <row r="468" spans="1:22" ht="14.25">
       <c r="A468" s="7"/>
       <c r="B468" s="25"/>
       <c r="C468" s="3"/>
@@ -12635,7 +12602,7 @@
       <c r="U468" s="1"/>
       <c r="V468" s="1"/>
     </row>
-    <row r="469" spans="1:22">
+    <row r="469" spans="1:22" ht="14.25">
       <c r="A469" s="7"/>
       <c r="B469" s="25"/>
       <c r="C469" s="3"/>
@@ -12659,7 +12626,7 @@
       <c r="U469" s="1"/>
       <c r="V469" s="1"/>
     </row>
-    <row r="470" spans="1:22">
+    <row r="470" spans="1:22" ht="14.25">
       <c r="A470" s="7"/>
       <c r="B470" s="25"/>
       <c r="C470" s="3"/>
@@ -12683,7 +12650,7 @@
       <c r="U470" s="1"/>
       <c r="V470" s="1"/>
     </row>
-    <row r="471" spans="1:22">
+    <row r="471" spans="1:22" ht="14.25">
       <c r="A471" s="7"/>
       <c r="B471" s="25"/>
       <c r="C471" s="3"/>
@@ -12707,7 +12674,7 @@
       <c r="U471" s="1"/>
       <c r="V471" s="1"/>
     </row>
-    <row r="472" spans="1:22">
+    <row r="472" spans="1:22" ht="14.25">
       <c r="A472" s="7"/>
       <c r="B472" s="25"/>
       <c r="C472" s="3"/>
@@ -12731,7 +12698,7 @@
       <c r="U472" s="1"/>
       <c r="V472" s="1"/>
     </row>
-    <row r="473" spans="1:22">
+    <row r="473" spans="1:22" ht="14.25">
       <c r="A473" s="7"/>
       <c r="B473" s="25"/>
       <c r="C473" s="3"/>
@@ -12755,7 +12722,7 @@
       <c r="U473" s="1"/>
       <c r="V473" s="1"/>
     </row>
-    <row r="474" spans="1:22">
+    <row r="474" spans="1:22" ht="14.25">
       <c r="A474" s="7"/>
       <c r="B474" s="25"/>
       <c r="C474" s="3"/>
@@ -12779,7 +12746,7 @@
       <c r="U474" s="1"/>
       <c r="V474" s="1"/>
     </row>
-    <row r="475" spans="1:22">
+    <row r="475" spans="1:22" ht="14.25">
       <c r="A475" s="7"/>
       <c r="B475" s="25"/>
       <c r="C475" s="3"/>
@@ -12803,7 +12770,7 @@
       <c r="U475" s="1"/>
       <c r="V475" s="1"/>
     </row>
-    <row r="476" spans="1:22">
+    <row r="476" spans="1:22" ht="14.25">
       <c r="A476" s="7"/>
       <c r="B476" s="25"/>
       <c r="C476" s="3"/>
@@ -12827,7 +12794,7 @@
       <c r="U476" s="1"/>
       <c r="V476" s="1"/>
     </row>
-    <row r="477" spans="1:22">
+    <row r="477" spans="1:22" ht="14.25">
       <c r="A477" s="7"/>
       <c r="B477" s="25"/>
       <c r="C477" s="3"/>
@@ -12851,7 +12818,7 @@
       <c r="U477" s="1"/>
       <c r="V477" s="1"/>
     </row>
-    <row r="478" spans="1:22">
+    <row r="478" spans="1:22" ht="14.25">
       <c r="A478" s="7"/>
       <c r="B478" s="25"/>
       <c r="C478" s="3"/>
@@ -12875,7 +12842,7 @@
       <c r="U478" s="1"/>
       <c r="V478" s="1"/>
     </row>
-    <row r="479" spans="1:22">
+    <row r="479" spans="1:22" ht="14.25">
       <c r="A479" s="7"/>
       <c r="B479" s="25"/>
       <c r="C479" s="3"/>
@@ -12899,7 +12866,7 @@
       <c r="U479" s="1"/>
       <c r="V479" s="1"/>
     </row>
-    <row r="480" spans="1:22">
+    <row r="480" spans="1:22" ht="14.25">
       <c r="A480" s="7"/>
       <c r="B480" s="25"/>
       <c r="C480" s="3"/>
@@ -12923,7 +12890,7 @@
       <c r="U480" s="1"/>
       <c r="V480" s="1"/>
     </row>
-    <row r="481" spans="1:22">
+    <row r="481" spans="1:22" ht="14.25">
       <c r="A481" s="7"/>
       <c r="B481" s="25"/>
       <c r="C481" s="3"/>
@@ -12947,7 +12914,7 @@
       <c r="U481" s="1"/>
       <c r="V481" s="1"/>
     </row>
-    <row r="482" spans="1:22">
+    <row r="482" spans="1:22" ht="14.25">
       <c r="A482" s="7"/>
       <c r="B482" s="25"/>
       <c r="C482" s="3"/>
@@ -12971,7 +12938,7 @@
       <c r="U482" s="1"/>
       <c r="V482" s="1"/>
     </row>
-    <row r="483" spans="1:22">
+    <row r="483" spans="1:22" ht="14.25">
       <c r="A483" s="7"/>
       <c r="B483" s="25"/>
       <c r="C483" s="3"/>
@@ -12995,7 +12962,7 @@
       <c r="U483" s="1"/>
       <c r="V483" s="1"/>
     </row>
-    <row r="484" spans="1:22">
+    <row r="484" spans="1:22" ht="14.25">
       <c r="A484" s="7"/>
       <c r="B484" s="25"/>
       <c r="C484" s="3"/>
@@ -13019,7 +12986,7 @@
       <c r="U484" s="1"/>
       <c r="V484" s="1"/>
     </row>
-    <row r="485" spans="1:22">
+    <row r="485" spans="1:22" ht="14.25">
       <c r="A485" s="7"/>
       <c r="B485" s="25"/>
       <c r="C485" s="3"/>
@@ -13043,7 +13010,7 @@
       <c r="U485" s="1"/>
       <c r="V485" s="1"/>
     </row>
-    <row r="486" spans="1:22">
+    <row r="486" spans="1:22" ht="14.25">
       <c r="A486" s="7"/>
       <c r="B486" s="25"/>
       <c r="C486" s="3"/>
@@ -13067,7 +13034,7 @@
       <c r="U486" s="1"/>
       <c r="V486" s="1"/>
     </row>
-    <row r="487" spans="1:22">
+    <row r="487" spans="1:22" ht="14.25">
       <c r="A487" s="7"/>
       <c r="B487" s="25"/>
       <c r="C487" s="3"/>
@@ -13091,7 +13058,7 @@
       <c r="U487" s="1"/>
       <c r="V487" s="1"/>
     </row>
-    <row r="488" spans="1:22">
+    <row r="488" spans="1:22" ht="14.25">
       <c r="A488" s="7"/>
       <c r="B488" s="25"/>
       <c r="C488" s="3"/>
@@ -13115,7 +13082,7 @@
       <c r="U488" s="1"/>
       <c r="V488" s="1"/>
     </row>
-    <row r="489" spans="1:22">
+    <row r="489" spans="1:22" ht="14.25">
       <c r="A489" s="7"/>
       <c r="B489" s="25"/>
       <c r="C489" s="3"/>
@@ -13139,7 +13106,7 @@
       <c r="U489" s="1"/>
       <c r="V489" s="1"/>
     </row>
-    <row r="490" spans="1:22">
+    <row r="490" spans="1:22" ht="14.25">
       <c r="A490" s="7"/>
       <c r="B490" s="25"/>
       <c r="C490" s="3"/>
@@ -13163,7 +13130,7 @@
       <c r="U490" s="1"/>
       <c r="V490" s="1"/>
     </row>
-    <row r="491" spans="1:22">
+    <row r="491" spans="1:22" ht="14.25">
       <c r="A491" s="7"/>
       <c r="B491" s="25"/>
       <c r="C491" s="3"/>
@@ -13187,7 +13154,7 @@
       <c r="U491" s="1"/>
       <c r="V491" s="1"/>
     </row>
-    <row r="492" spans="1:22">
+    <row r="492" spans="1:22" ht="14.25">
       <c r="A492" s="7"/>
       <c r="B492" s="25"/>
       <c r="C492" s="3"/>
@@ -13211,7 +13178,7 @@
       <c r="U492" s="1"/>
       <c r="V492" s="1"/>
     </row>
-    <row r="493" spans="1:22">
+    <row r="493" spans="1:22" ht="14.25">
       <c r="A493" s="7"/>
       <c r="B493" s="25"/>
       <c r="C493" s="3"/>
@@ -13235,7 +13202,7 @@
       <c r="U493" s="1"/>
       <c r="V493" s="1"/>
     </row>
-    <row r="494" spans="1:22">
+    <row r="494" spans="1:22" ht="14.25">
       <c r="A494" s="7"/>
       <c r="B494" s="25"/>
       <c r="C494" s="3"/>
@@ -13259,7 +13226,7 @@
       <c r="U494" s="1"/>
       <c r="V494" s="1"/>
     </row>
-    <row r="495" spans="1:22">
+    <row r="495" spans="1:22" ht="14.25">
       <c r="A495" s="7"/>
       <c r="B495" s="25"/>
       <c r="C495" s="3"/>
@@ -13283,7 +13250,7 @@
       <c r="U495" s="1"/>
       <c r="V495" s="1"/>
     </row>
-    <row r="496" spans="1:22">
+    <row r="496" spans="1:22" ht="14.25">
       <c r="A496" s="7"/>
       <c r="B496" s="25"/>
       <c r="C496" s="3"/>
@@ -13307,7 +13274,7 @@
       <c r="U496" s="1"/>
       <c r="V496" s="1"/>
     </row>
-    <row r="497" spans="1:22">
+    <row r="497" spans="1:22" ht="14.25">
       <c r="A497" s="7"/>
       <c r="B497" s="25"/>
       <c r="C497" s="3"/>
@@ -13331,7 +13298,7 @@
       <c r="U497" s="1"/>
       <c r="V497" s="1"/>
     </row>
-    <row r="498" spans="1:22">
+    <row r="498" spans="1:22" ht="14.25">
       <c r="A498" s="7"/>
       <c r="B498" s="25"/>
       <c r="C498" s="3"/>
@@ -13355,7 +13322,7 @@
       <c r="U498" s="1"/>
       <c r="V498" s="1"/>
     </row>
-    <row r="499" spans="1:22">
+    <row r="499" spans="1:22" ht="14.25">
       <c r="A499" s="7"/>
       <c r="B499" s="25"/>
       <c r="C499" s="3"/>
@@ -13379,7 +13346,7 @@
       <c r="U499" s="1"/>
       <c r="V499" s="1"/>
     </row>
-    <row r="500" spans="1:22">
+    <row r="500" spans="1:22" ht="14.25">
       <c r="A500" s="7"/>
       <c r="B500" s="25"/>
       <c r="C500" s="3"/>
@@ -13403,7 +13370,7 @@
       <c r="U500" s="1"/>
       <c r="V500" s="1"/>
     </row>
-    <row r="501" spans="1:22">
+    <row r="501" spans="1:22" ht="14.25">
       <c r="A501" s="7"/>
       <c r="B501" s="25"/>
       <c r="C501" s="3"/>
@@ -13427,7 +13394,7 @@
       <c r="U501" s="1"/>
       <c r="V501" s="1"/>
     </row>
-    <row r="502" spans="1:22">
+    <row r="502" spans="1:22" ht="14.25">
       <c r="A502" s="7"/>
       <c r="B502" s="25"/>
       <c r="C502" s="3"/>
@@ -13451,7 +13418,7 @@
       <c r="U502" s="1"/>
       <c r="V502" s="1"/>
     </row>
-    <row r="503" spans="1:22">
+    <row r="503" spans="1:22" ht="14.25">
       <c r="A503" s="7"/>
       <c r="B503" s="25"/>
       <c r="C503" s="3"/>
@@ -13475,7 +13442,7 @@
       <c r="U503" s="1"/>
       <c r="V503" s="1"/>
     </row>
-    <row r="504" spans="1:22">
+    <row r="504" spans="1:22" ht="14.25">
       <c r="A504" s="7"/>
       <c r="B504" s="25"/>
       <c r="C504" s="3"/>
@@ -13499,7 +13466,7 @@
       <c r="U504" s="1"/>
       <c r="V504" s="1"/>
     </row>
-    <row r="505" spans="1:22">
+    <row r="505" spans="1:22" ht="14.25">
       <c r="A505" s="7"/>
       <c r="B505" s="25"/>
       <c r="C505" s="3"/>
@@ -13523,7 +13490,7 @@
       <c r="U505" s="1"/>
       <c r="V505" s="1"/>
     </row>
-    <row r="506" spans="1:22">
+    <row r="506" spans="1:22" ht="14.25">
       <c r="A506" s="7"/>
       <c r="B506" s="25"/>
       <c r="C506" s="3"/>
@@ -13547,7 +13514,7 @@
       <c r="U506" s="1"/>
       <c r="V506" s="1"/>
     </row>
-    <row r="507" spans="1:22">
+    <row r="507" spans="1:22" ht="14.25">
       <c r="A507" s="7"/>
       <c r="B507" s="25"/>
       <c r="C507" s="3"/>
@@ -13571,7 +13538,7 @@
       <c r="U507" s="1"/>
       <c r="V507" s="1"/>
     </row>
-    <row r="508" spans="1:22">
+    <row r="508" spans="1:22" ht="14.25">
       <c r="A508" s="7"/>
       <c r="B508" s="25"/>
       <c r="C508" s="3"/>
@@ -13595,7 +13562,7 @@
       <c r="U508" s="1"/>
       <c r="V508" s="1"/>
     </row>
-    <row r="509" spans="1:22">
+    <row r="509" spans="1:22" ht="14.25">
       <c r="A509" s="7"/>
       <c r="B509" s="25"/>
       <c r="C509" s="3"/>
@@ -13619,7 +13586,7 @@
       <c r="U509" s="1"/>
       <c r="V509" s="1"/>
     </row>
-    <row r="510" spans="1:22">
+    <row r="510" spans="1:22" ht="14.25">
       <c r="A510" s="7"/>
       <c r="B510" s="25"/>
       <c r="C510" s="3"/>
@@ -13643,7 +13610,7 @@
       <c r="U510" s="1"/>
       <c r="V510" s="1"/>
     </row>
-    <row r="511" spans="1:22">
+    <row r="511" spans="1:22" ht="14.25">
       <c r="A511" s="7"/>
       <c r="B511" s="25"/>
       <c r="C511" s="3"/>
@@ -13667,7 +13634,7 @@
       <c r="U511" s="1"/>
       <c r="V511" s="1"/>
     </row>
-    <row r="512" spans="1:22">
+    <row r="512" spans="1:22" ht="14.25">
       <c r="A512" s="7"/>
       <c r="B512" s="25"/>
       <c r="C512" s="3"/>
@@ -13691,7 +13658,7 @@
       <c r="U512" s="1"/>
       <c r="V512" s="1"/>
     </row>
-    <row r="513" spans="1:22">
+    <row r="513" spans="1:22" ht="14.25">
       <c r="A513" s="7"/>
       <c r="B513" s="25"/>
       <c r="C513" s="3"/>
@@ -13715,7 +13682,7 @@
       <c r="U513" s="1"/>
       <c r="V513" s="1"/>
     </row>
-    <row r="514" spans="1:22">
+    <row r="514" spans="1:22" ht="14.25">
       <c r="A514" s="7"/>
       <c r="B514" s="25"/>
       <c r="C514" s="3"/>
@@ -13739,7 +13706,7 @@
       <c r="U514" s="1"/>
       <c r="V514" s="1"/>
     </row>
-    <row r="515" spans="1:22">
+    <row r="515" spans="1:22" ht="14.25">
       <c r="A515" s="7"/>
       <c r="B515" s="25"/>
       <c r="C515" s="3"/>
@@ -13763,7 +13730,7 @@
       <c r="U515" s="1"/>
       <c r="V515" s="1"/>
     </row>
-    <row r="516" spans="1:22">
+    <row r="516" spans="1:22" ht="14.25">
       <c r="A516" s="7"/>
       <c r="B516" s="25"/>
       <c r="C516" s="3"/>
@@ -13787,7 +13754,7 @@
       <c r="U516" s="1"/>
       <c r="V516" s="1"/>
     </row>
-    <row r="517" spans="1:22">
+    <row r="517" spans="1:22" ht="14.25">
       <c r="A517" s="7"/>
       <c r="B517" s="25"/>
       <c r="C517" s="3"/>
@@ -13811,7 +13778,7 @@
       <c r="U517" s="1"/>
       <c r="V517" s="1"/>
     </row>
-    <row r="518" spans="1:22">
+    <row r="518" spans="1:22" ht="14.25">
       <c r="A518" s="7"/>
       <c r="B518" s="25"/>
       <c r="C518" s="3"/>
@@ -13835,7 +13802,7 @@
       <c r="U518" s="1"/>
       <c r="V518" s="1"/>
     </row>
-    <row r="519" spans="1:22">
+    <row r="519" spans="1:22" ht="14.25">
       <c r="A519" s="7"/>
       <c r="B519" s="25"/>
       <c r="C519" s="3"/>
@@ -13859,7 +13826,7 @@
       <c r="U519" s="1"/>
       <c r="V519" s="1"/>
     </row>
-    <row r="520" spans="1:22">
+    <row r="520" spans="1:22" ht="14.25">
       <c r="A520" s="7"/>
       <c r="B520" s="25"/>
       <c r="C520" s="3"/>
@@ -13883,7 +13850,7 @@
       <c r="U520" s="1"/>
       <c r="V520" s="1"/>
     </row>
-    <row r="521" spans="1:22">
+    <row r="521" spans="1:22" ht="14.25">
       <c r="A521" s="7"/>
       <c r="B521" s="25"/>
       <c r="C521" s="3"/>
@@ -13907,7 +13874,7 @@
       <c r="U521" s="1"/>
       <c r="V521" s="1"/>
     </row>
-    <row r="522" spans="1:22">
+    <row r="522" spans="1:22" ht="14.25">
       <c r="A522" s="7"/>
       <c r="B522" s="25"/>
       <c r="C522" s="3"/>
@@ -13931,7 +13898,7 @@
       <c r="U522" s="1"/>
       <c r="V522" s="1"/>
     </row>
-    <row r="523" spans="1:22">
+    <row r="523" spans="1:22" ht="14.25">
       <c r="A523" s="7"/>
       <c r="B523" s="25"/>
       <c r="C523" s="3"/>
@@ -13955,7 +13922,7 @@
       <c r="U523" s="1"/>
       <c r="V523" s="1"/>
     </row>
-    <row r="524" spans="1:22">
+    <row r="524" spans="1:22" ht="14.25">
       <c r="A524" s="7"/>
       <c r="B524" s="25"/>
       <c r="C524" s="3"/>
@@ -13979,7 +13946,7 @@
       <c r="U524" s="1"/>
       <c r="V524" s="1"/>
     </row>
-    <row r="525" spans="1:22">
+    <row r="525" spans="1:22" ht="14.25">
       <c r="A525" s="7"/>
       <c r="B525" s="25"/>
       <c r="C525" s="3"/>
@@ -14003,7 +13970,7 @@
       <c r="U525" s="1"/>
       <c r="V525" s="1"/>
     </row>
-    <row r="526" spans="1:22">
+    <row r="526" spans="1:22" ht="14.25">
       <c r="A526" s="7"/>
       <c r="B526" s="25"/>
       <c r="C526" s="3"/>
@@ -14027,7 +13994,7 @@
       <c r="U526" s="1"/>
       <c r="V526" s="1"/>
     </row>
-    <row r="527" spans="1:22">
+    <row r="527" spans="1:22" ht="14.25">
       <c r="A527" s="7"/>
       <c r="B527" s="25"/>
       <c r="C527" s="3"/>
@@ -14051,7 +14018,7 @@
       <c r="U527" s="1"/>
       <c r="V527" s="1"/>
     </row>
-    <row r="528" spans="1:22">
+    <row r="528" spans="1:22" ht="14.25">
       <c r="A528" s="7"/>
       <c r="B528" s="25"/>
       <c r="C528" s="3"/>
@@ -14075,7 +14042,7 @@
       <c r="U528" s="1"/>
       <c r="V528" s="1"/>
     </row>
-    <row r="529" spans="1:22">
+    <row r="529" spans="1:22" ht="14.25">
       <c r="A529" s="7"/>
       <c r="B529" s="25"/>
       <c r="C529" s="3"/>
@@ -14099,7 +14066,7 @@
       <c r="U529" s="1"/>
       <c r="V529" s="1"/>
     </row>
-    <row r="530" spans="1:22">
+    <row r="530" spans="1:22" ht="14.25">
       <c r="A530" s="7"/>
       <c r="B530" s="25"/>
       <c r="C530" s="3"/>
@@ -14123,7 +14090,7 @@
       <c r="U530" s="1"/>
       <c r="V530" s="1"/>
     </row>
-    <row r="531" spans="1:22">
+    <row r="531" spans="1:22" ht="14.25">
       <c r="A531" s="7"/>
       <c r="B531" s="25"/>
       <c r="C531" s="3"/>
@@ -14147,7 +14114,7 @@
       <c r="U531" s="1"/>
       <c r="V531" s="1"/>
     </row>
-    <row r="532" spans="1:22">
+    <row r="532" spans="1:22" ht="14.25">
       <c r="A532" s="7"/>
       <c r="B532" s="25"/>
       <c r="C532" s="3"/>
@@ -14171,7 +14138,7 @@
       <c r="U532" s="1"/>
       <c r="V532" s="1"/>
     </row>
-    <row r="533" spans="1:22">
+    <row r="533" spans="1:22" ht="14.25">
       <c r="A533" s="7"/>
       <c r="B533" s="25"/>
       <c r="C533" s="3"/>
@@ -14195,7 +14162,7 @@
       <c r="U533" s="1"/>
       <c r="V533" s="1"/>
     </row>
-    <row r="534" spans="1:22">
+    <row r="534" spans="1:22" ht="14.25">
       <c r="A534" s="7"/>
       <c r="B534" s="25"/>
       <c r="C534" s="3"/>
@@ -14219,7 +14186,7 @@
       <c r="U534" s="1"/>
       <c r="V534" s="1"/>
     </row>
-    <row r="535" spans="1:22">
+    <row r="535" spans="1:22" ht="14.25">
       <c r="A535" s="7"/>
       <c r="B535" s="25"/>
       <c r="C535" s="3"/>
@@ -14243,7 +14210,7 @@
       <c r="U535" s="1"/>
       <c r="V535" s="1"/>
     </row>
-    <row r="536" spans="1:22">
+    <row r="536" spans="1:22" ht="14.25">
       <c r="A536" s="7"/>
       <c r="B536" s="25"/>
       <c r="C536" s="3"/>
@@ -14267,7 +14234,7 @@
       <c r="U536" s="1"/>
       <c r="V536" s="1"/>
     </row>
-    <row r="537" spans="1:22">
+    <row r="537" spans="1:22" ht="14.25">
       <c r="A537" s="7"/>
       <c r="B537" s="25"/>
       <c r="C537" s="3"/>
@@ -14291,7 +14258,7 @@
       <c r="U537" s="1"/>
       <c r="V537" s="1"/>
     </row>
-    <row r="538" spans="1:22">
+    <row r="538" spans="1:22" ht="14.25">
       <c r="A538" s="7"/>
       <c r="B538" s="25"/>
       <c r="C538" s="3"/>
@@ -14315,7 +14282,7 @@
       <c r="U538" s="1"/>
       <c r="V538" s="1"/>
     </row>
-    <row r="539" spans="1:22">
+    <row r="539" spans="1:22" ht="14.25">
       <c r="A539" s="7"/>
       <c r="B539" s="25"/>
       <c r="C539" s="3"/>
@@ -14339,7 +14306,7 @@
       <c r="U539" s="1"/>
       <c r="V539" s="1"/>
     </row>
-    <row r="540" spans="1:22">
+    <row r="540" spans="1:22" ht="14.25">
       <c r="A540" s="7"/>
       <c r="B540" s="25"/>
       <c r="C540" s="3"/>
@@ -14363,7 +14330,7 @@
       <c r="U540" s="1"/>
       <c r="V540" s="1"/>
     </row>
-    <row r="541" spans="1:22">
+    <row r="541" spans="1:22" ht="14.25">
       <c r="A541" s="7"/>
       <c r="B541" s="25"/>
       <c r="C541" s="3"/>
@@ -14387,7 +14354,7 @@
       <c r="U541" s="1"/>
       <c r="V541" s="1"/>
     </row>
-    <row r="542" spans="1:22">
+    <row r="542" spans="1:22" ht="14.25">
       <c r="A542" s="7"/>
       <c r="B542" s="25"/>
       <c r="C542" s="3"/>
@@ -14411,7 +14378,7 @@
       <c r="U542" s="1"/>
       <c r="V542" s="1"/>
     </row>
-    <row r="543" spans="1:22">
+    <row r="543" spans="1:22" ht="14.25">
       <c r="A543" s="7"/>
       <c r="B543" s="25"/>
       <c r="C543" s="3"/>
@@ -14435,7 +14402,7 @@
       <c r="U543" s="1"/>
       <c r="V543" s="1"/>
     </row>
-    <row r="544" spans="1:22">
+    <row r="544" spans="1:22" ht="14.25">
       <c r="A544" s="7"/>
       <c r="B544" s="25"/>
       <c r="C544" s="3"/>
@@ -14459,7 +14426,7 @@
       <c r="U544" s="1"/>
       <c r="V544" s="1"/>
     </row>
-    <row r="545" spans="1:22">
+    <row r="545" spans="1:22" ht="14.25">
       <c r="A545" s="7"/>
       <c r="B545" s="25"/>
       <c r="C545" s="3"/>
@@ -14483,7 +14450,7 @@
       <c r="U545" s="1"/>
       <c r="V545" s="1"/>
     </row>
-    <row r="546" spans="1:22">
+    <row r="546" spans="1:22" ht="14.25">
       <c r="A546" s="7"/>
       <c r="B546" s="25"/>
       <c r="C546" s="3"/>
@@ -14507,7 +14474,7 @@
       <c r="U546" s="1"/>
       <c r="V546" s="1"/>
     </row>
-    <row r="547" spans="1:22">
+    <row r="547" spans="1:22" ht="14.25">
       <c r="A547" s="7"/>
       <c r="B547" s="25"/>
       <c r="C547" s="3"/>
@@ -14531,7 +14498,7 @@
       <c r="U547" s="1"/>
       <c r="V547" s="1"/>
     </row>
-    <row r="548" spans="1:22">
+    <row r="548" spans="1:22" ht="14.25">
       <c r="A548" s="7"/>
       <c r="B548" s="25"/>
       <c r="C548" s="3"/>
@@ -14555,7 +14522,7 @@
       <c r="U548" s="1"/>
       <c r="V548" s="1"/>
     </row>
-    <row r="549" spans="1:22">
+    <row r="549" spans="1:22" ht="14.25">
       <c r="A549" s="7"/>
       <c r="B549" s="25"/>
       <c r="C549" s="3"/>
@@ -14579,7 +14546,7 @@
       <c r="U549" s="1"/>
       <c r="V549" s="1"/>
     </row>
-    <row r="550" spans="1:22">
+    <row r="550" spans="1:22" ht="14.25">
       <c r="A550" s="7"/>
       <c r="B550" s="25"/>
       <c r="C550" s="3"/>
@@ -14603,7 +14570,7 @@
       <c r="U550" s="1"/>
       <c r="V550" s="1"/>
     </row>
-    <row r="551" spans="1:22">
+    <row r="551" spans="1:22" ht="14.25">
       <c r="A551" s="7"/>
       <c r="B551" s="25"/>
       <c r="C551" s="3"/>
@@ -14627,7 +14594,7 @@
       <c r="U551" s="1"/>
       <c r="V551" s="1"/>
     </row>
-    <row r="552" spans="1:22">
+    <row r="552" spans="1:22" ht="14.25">
       <c r="A552" s="7"/>
       <c r="B552" s="25"/>
       <c r="C552" s="3"/>
@@ -14651,7 +14618,7 @@
       <c r="U552" s="1"/>
       <c r="V552" s="1"/>
     </row>
-    <row r="553" spans="1:22">
+    <row r="553" spans="1:22" ht="14.25">
       <c r="A553" s="7"/>
       <c r="B553" s="25"/>
       <c r="C553" s="3"/>
@@ -14675,7 +14642,7 @@
       <c r="U553" s="1"/>
       <c r="V553" s="1"/>
     </row>
-    <row r="554" spans="1:22">
+    <row r="554" spans="1:22" ht="14.25">
       <c r="A554" s="7"/>
       <c r="B554" s="25"/>
       <c r="C554" s="3"/>
@@ -14699,7 +14666,7 @@
       <c r="U554" s="1"/>
       <c r="V554" s="1"/>
     </row>
-    <row r="555" spans="1:22">
+    <row r="555" spans="1:22" ht="14.25">
       <c r="A555" s="7"/>
       <c r="B555" s="25"/>
       <c r="C555" s="3"/>
@@ -14723,7 +14690,7 @@
       <c r="U555" s="1"/>
       <c r="V555" s="1"/>
     </row>
-    <row r="556" spans="1:22">
+    <row r="556" spans="1:22" ht="14.25">
       <c r="A556" s="7"/>
       <c r="B556" s="25"/>
       <c r="C556" s="3"/>
@@ -14747,7 +14714,7 @@
       <c r="U556" s="1"/>
       <c r="V556" s="1"/>
     </row>
-    <row r="557" spans="1:22">
+    <row r="557" spans="1:22" ht="14.25">
       <c r="A557" s="7"/>
       <c r="B557" s="25"/>
       <c r="C557" s="3"/>
@@ -14771,7 +14738,7 @@
       <c r="U557" s="1"/>
       <c r="V557" s="1"/>
     </row>
-    <row r="558" spans="1:22">
+    <row r="558" spans="1:22" ht="14.25">
       <c r="A558" s="7"/>
       <c r="B558" s="25"/>
       <c r="C558" s="3"/>
@@ -14795,7 +14762,7 @@
       <c r="U558" s="1"/>
       <c r="V558" s="1"/>
     </row>
-    <row r="559" spans="1:22">
+    <row r="559" spans="1:22" ht="14.25">
       <c r="A559" s="7"/>
       <c r="B559" s="25"/>
       <c r="C559" s="3"/>
@@ -14819,7 +14786,7 @@
       <c r="U559" s="1"/>
       <c r="V559" s="1"/>
     </row>
-    <row r="560" spans="1:22">
+    <row r="560" spans="1:22" ht="14.25">
       <c r="A560" s="7"/>
       <c r="B560" s="25"/>
       <c r="C560" s="3"/>
@@ -14843,7 +14810,7 @@
       <c r="U560" s="1"/>
       <c r="V560" s="1"/>
     </row>
-    <row r="561" spans="1:22">
+    <row r="561" spans="1:22" ht="14.25">
       <c r="A561" s="7"/>
       <c r="B561" s="25"/>
       <c r="C561" s="3"/>
@@ -14867,7 +14834,7 @@
       <c r="U561" s="1"/>
       <c r="V561" s="1"/>
     </row>
-    <row r="562" spans="1:22">
+    <row r="562" spans="1:22" ht="14.25">
       <c r="A562" s="7"/>
       <c r="B562" s="25"/>
       <c r="C562" s="3"/>
@@ -14891,7 +14858,7 @@
       <c r="U562" s="1"/>
       <c r="V562" s="1"/>
     </row>
-    <row r="563" spans="1:22">
+    <row r="563" spans="1:22" ht="14.25">
       <c r="A563" s="7"/>
       <c r="B563" s="25"/>
       <c r="C563" s="3"/>
@@ -14915,7 +14882,7 @@
       <c r="U563" s="1"/>
       <c r="V563" s="1"/>
     </row>
-    <row r="564" spans="1:22">
+    <row r="564" spans="1:22" ht="14.25">
       <c r="A564" s="7"/>
       <c r="B564" s="25"/>
       <c r="C564" s="3"/>
@@ -14939,7 +14906,7 @@
       <c r="U564" s="1"/>
       <c r="V564" s="1"/>
     </row>
-    <row r="565" spans="1:22">
+    <row r="565" spans="1:22" ht="14.25">
       <c r="A565" s="7"/>
       <c r="B565" s="25"/>
       <c r="C565" s="3"/>
@@ -14963,7 +14930,7 @@
       <c r="U565" s="1"/>
       <c r="V565" s="1"/>
     </row>
-    <row r="566" spans="1:22">
+    <row r="566" spans="1:22" ht="14.25">
       <c r="A566" s="7"/>
       <c r="B566" s="25"/>
       <c r="C566" s="3"/>
@@ -14987,7 +14954,7 @@
       <c r="U566" s="1"/>
       <c r="V566" s="1"/>
     </row>
-    <row r="567" spans="1:22">
+    <row r="567" spans="1:22" ht="14.25">
       <c r="A567" s="7"/>
       <c r="B567" s="25"/>
       <c r="C567" s="3"/>
@@ -15011,7 +14978,7 @@
       <c r="U567" s="1"/>
       <c r="V567" s="1"/>
     </row>
-    <row r="568" spans="1:22">
+    <row r="568" spans="1:22" ht="14.25">
       <c r="A568" s="7"/>
       <c r="B568" s="25"/>
       <c r="C568" s="3"/>
@@ -15035,7 +15002,7 @@
       <c r="U568" s="1"/>
       <c r="V568" s="1"/>
     </row>
-    <row r="569" spans="1:22">
+    <row r="569" spans="1:22" ht="14.25">
       <c r="A569" s="7"/>
       <c r="B569" s="25"/>
       <c r="C569" s="3"/>
@@ -15059,7 +15026,7 @@
       <c r="U569" s="1"/>
       <c r="V569" s="1"/>
     </row>
-    <row r="570" spans="1:22">
+    <row r="570" spans="1:22" ht="14.25">
       <c r="A570" s="7"/>
       <c r="B570" s="25"/>
       <c r="C570" s="3"/>
@@ -15083,7 +15050,7 @@
       <c r="U570" s="1"/>
       <c r="V570" s="1"/>
     </row>
-    <row r="571" spans="1:22">
+    <row r="571" spans="1:22" ht="14.25">
       <c r="A571" s="7"/>
       <c r="B571" s="25"/>
       <c r="C571" s="3"/>
@@ -15107,7 +15074,7 @@
       <c r="U571" s="1"/>
       <c r="V571" s="1"/>
     </row>
-    <row r="572" spans="1:22">
+    <row r="572" spans="1:22" ht="14.25">
       <c r="A572" s="7"/>
       <c r="B572" s="25"/>
       <c r="C572" s="3"/>
@@ -15131,7 +15098,7 @@
       <c r="U572" s="1"/>
       <c r="V572" s="1"/>
     </row>
-    <row r="573" spans="1:22">
+    <row r="573" spans="1:22" ht="14.25">
       <c r="A573" s="7"/>
       <c r="B573" s="25"/>
       <c r="C573" s="3"/>
@@ -15155,7 +15122,7 @@
       <c r="U573" s="1"/>
       <c r="V573" s="1"/>
     </row>
-    <row r="574" spans="1:22">
+    <row r="574" spans="1:22" ht="14.25">
       <c r="A574" s="7"/>
       <c r="B574" s="25"/>
       <c r="C574" s="3"/>
@@ -15179,7 +15146,7 @@
       <c r="U574" s="1"/>
       <c r="V574" s="1"/>
     </row>
-    <row r="575" spans="1:22">
+    <row r="575" spans="1:22" ht="14.25">
       <c r="A575" s="7"/>
       <c r="B575" s="25"/>
       <c r="C575" s="3"/>
@@ -15203,7 +15170,7 @@
       <c r="U575" s="1"/>
       <c r="V575" s="1"/>
     </row>
-    <row r="576" spans="1:22">
+    <row r="576" spans="1:22" ht="14.25">
       <c r="A576" s="7"/>
       <c r="B576" s="25"/>
       <c r="C576" s="3"/>
@@ -15227,7 +15194,7 @@
       <c r="U576" s="1"/>
       <c r="V576" s="1"/>
     </row>
-    <row r="577" spans="1:22">
+    <row r="577" spans="1:22" ht="14.25">
       <c r="A577" s="7"/>
       <c r="B577" s="25"/>
       <c r="C577" s="3"/>
@@ -15251,7 +15218,7 @@
       <c r="U577" s="1"/>
       <c r="V577" s="1"/>
     </row>
-    <row r="578" spans="1:22">
+    <row r="578" spans="1:22" ht="14.25">
       <c r="A578" s="7"/>
       <c r="B578" s="25"/>
       <c r="C578" s="3"/>
@@ -15275,7 +15242,7 @@
       <c r="U578" s="1"/>
       <c r="V578" s="1"/>
     </row>
-    <row r="579" spans="1:22">
+    <row r="579" spans="1:22" ht="14.25">
       <c r="A579" s="7"/>
       <c r="B579" s="25"/>
       <c r="C579" s="3"/>
@@ -15299,7 +15266,7 @@
       <c r="U579" s="1"/>
       <c r="V579" s="1"/>
     </row>
-    <row r="580" spans="1:22">
+    <row r="580" spans="1:22" ht="14.25">
       <c r="A580" s="7"/>
       <c r="B580" s="25"/>
       <c r="C580" s="3"/>
@@ -15323,7 +15290,7 @@
       <c r="U580" s="1"/>
       <c r="V580" s="1"/>
     </row>
-    <row r="581" spans="1:22">
+    <row r="581" spans="1:22" ht="14.25">
       <c r="A581" s="7"/>
       <c r="B581" s="25"/>
       <c r="C581" s="3"/>
@@ -15347,7 +15314,7 @@
       <c r="U581" s="1"/>
       <c r="V581" s="1"/>
     </row>
-    <row r="582" spans="1:22">
+    <row r="582" spans="1:22" ht="14.25">
       <c r="A582" s="7"/>
       <c r="B582" s="25"/>
       <c r="C582" s="3"/>
@@ -15371,7 +15338,7 @@
       <c r="U582" s="1"/>
       <c r="V582" s="1"/>
     </row>
-    <row r="583" spans="1:22">
+    <row r="583" spans="1:22" ht="14.25">
       <c r="A583" s="7"/>
       <c r="B583" s="25"/>
       <c r="C583" s="3"/>
@@ -15395,7 +15362,7 @@
       <c r="U583" s="1"/>
       <c r="V583" s="1"/>
     </row>
-    <row r="584" spans="1:22">
+    <row r="584" spans="1:22" ht="14.25">
       <c r="A584" s="7"/>
       <c r="B584" s="25"/>
       <c r="C584" s="3"/>
@@ -15419,7 +15386,7 @@
       <c r="U584" s="1"/>
       <c r="V584" s="1"/>
     </row>
-    <row r="585" spans="1:22">
+    <row r="585" spans="1:22" ht="14.25">
       <c r="A585" s="7"/>
       <c r="B585" s="25"/>
       <c r="C585" s="3"/>
@@ -15443,7 +15410,7 @@
       <c r="U585" s="1"/>
       <c r="V585" s="1"/>
     </row>
-    <row r="586" spans="1:22">
+    <row r="586" spans="1:22" ht="14.25">
       <c r="A586" s="7"/>
       <c r="B586" s="25"/>
       <c r="C586" s="3"/>
@@ -15467,7 +15434,7 @@
       <c r="U586" s="1"/>
       <c r="V586" s="1"/>
     </row>
-    <row r="587" spans="1:22">
+    <row r="587" spans="1:22" ht="14.25">
       <c r="A587" s="7"/>
       <c r="B587" s="25"/>
       <c r="C587" s="3"/>
@@ -15491,7 +15458,7 @@
       <c r="U587" s="1"/>
       <c r="V587" s="1"/>
     </row>
-    <row r="588" spans="1:22">
+    <row r="588" spans="1:22" ht="14.25">
       <c r="A588" s="7"/>
       <c r="B588" s="25"/>
       <c r="C588" s="3"/>
@@ -15515,7 +15482,7 @@
       <c r="U588" s="1"/>
       <c r="V588" s="1"/>
     </row>
-    <row r="589" spans="1:22">
+    <row r="589" spans="1:22" ht="14.25">
       <c r="A589" s="7"/>
       <c r="B589" s="25"/>
       <c r="C589" s="3"/>
@@ -15539,7 +15506,7 @@
       <c r="U589" s="1"/>
       <c r="V589" s="1"/>
     </row>
-    <row r="590" spans="1:22">
+    <row r="590" spans="1:22" ht="14.25">
       <c r="A590" s="7"/>
       <c r="B590" s="25"/>
       <c r="C590" s="3"/>
@@ -15563,7 +15530,7 @@
       <c r="U590" s="1"/>
       <c r="V590" s="1"/>
     </row>
-    <row r="591" spans="1:22">
+    <row r="591" spans="1:22" ht="14.25">
       <c r="A591" s="7"/>
       <c r="B591" s="25"/>
       <c r="C591" s="3"/>
@@ -15587,7 +15554,7 @@
       <c r="U591" s="1"/>
       <c r="V591" s="1"/>
     </row>
-    <row r="592" spans="1:22">
+    <row r="592" spans="1:22" ht="14.25">
       <c r="A592" s="7"/>
       <c r="B592" s="25"/>
       <c r="C592" s="3"/>
@@ -15611,7 +15578,7 @@
       <c r="U592" s="1"/>
       <c r="V592" s="1"/>
     </row>
-    <row r="593" spans="1:22">
+    <row r="593" spans="1:22" ht="14.25">
       <c r="A593" s="7"/>
       <c r="B593" s="25"/>
       <c r="C593" s="3"/>
@@ -15635,7 +15602,7 @@
       <c r="U593" s="1"/>
       <c r="V593" s="1"/>
     </row>
-    <row r="594" spans="1:22">
+    <row r="594" spans="1:22" ht="14.25">
       <c r="A594" s="7"/>
       <c r="B594" s="25"/>
       <c r="C594" s="3"/>
@@ -15659,7 +15626,7 @@
       <c r="U594" s="1"/>
       <c r="V594" s="1"/>
     </row>
-    <row r="595" spans="1:22">
+    <row r="595" spans="1:22" ht="14.25">
       <c r="A595" s="7"/>
       <c r="B595" s="25"/>
       <c r="C595" s="3"/>
@@ -15683,7 +15650,7 @@
       <c r="U595" s="1"/>
       <c r="V595" s="1"/>
     </row>
-    <row r="596" spans="1:22">
+    <row r="596" spans="1:22" ht="14.25">
       <c r="A596" s="7"/>
       <c r="B596" s="25"/>
       <c r="C596" s="3"/>
@@ -15707,7 +15674,7 @@
       <c r="U596" s="1"/>
       <c r="V596" s="1"/>
     </row>
-    <row r="597" spans="1:22">
+    <row r="597" spans="1:22" ht="14.25">
       <c r="A597" s="7"/>
       <c r="B597" s="25"/>
       <c r="C597" s="3"/>
@@ -15731,7 +15698,7 @@
       <c r="U597" s="1"/>
       <c r="V597" s="1"/>
     </row>
-    <row r="598" spans="1:22">
+    <row r="598" spans="1:22" ht="14.25">
       <c r="A598" s="7"/>
       <c r="B598" s="25"/>
       <c r="C598" s="3"/>
@@ -15755,7 +15722,7 @@
       <c r="U598" s="1"/>
       <c r="V598" s="1"/>
     </row>
-    <row r="599" spans="1:22">
+    <row r="599" spans="1:22" ht="14.25">
       <c r="A599" s="7"/>
       <c r="B599" s="25"/>
       <c r="C599" s="3"/>
@@ -15779,7 +15746,7 @@
       <c r="U599" s="1"/>
       <c r="V599" s="1"/>
     </row>
-    <row r="600" spans="1:22">
+    <row r="600" spans="1:22" ht="14.25">
       <c r="A600" s="7"/>
       <c r="B600" s="25"/>
       <c r="C600" s="3"/>
@@ -15803,7 +15770,7 @@
       <c r="U600" s="1"/>
       <c r="V600" s="1"/>
     </row>
-    <row r="601" spans="1:22">
+    <row r="601" spans="1:22" ht="14.25">
       <c r="A601" s="7"/>
       <c r="B601" s="25"/>
       <c r="C601" s="3"/>
@@ -15827,7 +15794,7 @@
       <c r="U601" s="1"/>
       <c r="V601" s="1"/>
     </row>
-    <row r="602" spans="1:22">
+    <row r="602" spans="1:22" ht="14.25">
       <c r="A602" s="7"/>
       <c r="B602" s="25"/>
       <c r="C602" s="3"/>
@@ -15851,7 +15818,7 @@
       <c r="U602" s="1"/>
       <c r="V602" s="1"/>
     </row>
-    <row r="603" spans="1:22">
+    <row r="603" spans="1:22" ht="14.25">
       <c r="A603" s="7"/>
       <c r="B603" s="25"/>
       <c r="C603" s="3"/>
@@ -15875,7 +15842,7 @@
       <c r="U603" s="1"/>
       <c r="V603" s="1"/>
     </row>
-    <row r="604" spans="1:22">
+    <row r="604" spans="1:22" ht="14.25">
       <c r="A604" s="7"/>
       <c r="B604" s="25"/>
       <c r="C604" s="3"/>
@@ -15899,7 +15866,7 @@
       <c r="U604" s="1"/>
       <c r="V604" s="1"/>
     </row>
-    <row r="605" spans="1:22">
+    <row r="605" spans="1:22" ht="14.25">
       <c r="A605" s="7"/>
       <c r="B605" s="25"/>
       <c r="C605" s="3"/>
@@ -15923,7 +15890,7 @@
       <c r="U605" s="1"/>
       <c r="V605" s="1"/>
     </row>
-    <row r="606" spans="1:22">
+    <row r="606" spans="1:22" ht="14.25">
       <c r="A606" s="7"/>
       <c r="B606" s="25"/>
       <c r="C606" s="3"/>
@@ -15947,7 +15914,7 @@
       <c r="U606" s="1"/>
       <c r="V606" s="1"/>
     </row>
-    <row r="607" spans="1:22">
+    <row r="607" spans="1:22" ht="14.25">
       <c r="A607" s="7"/>
       <c r="B607" s="25"/>
       <c r="C607" s="3"/>
@@ -15971,7 +15938,7 @@
       <c r="U607" s="1"/>
       <c r="V607" s="1"/>
     </row>
-    <row r="608" spans="1:22">
+    <row r="608" spans="1:22" ht="14.25">
       <c r="A608" s="7"/>
       <c r="B608" s="25"/>
       <c r="C608" s="3"/>
@@ -15995,7 +15962,7 @@
       <c r="U608" s="1"/>
       <c r="V608" s="1"/>
     </row>
-    <row r="609" spans="1:22">
+    <row r="609" spans="1:22" ht="14.25">
       <c r="A609" s="7"/>
       <c r="B609" s="25"/>
       <c r="C609" s="3"/>
@@ -16019,7 +15986,7 @@
       <c r="U609" s="1"/>
       <c r="V609" s="1"/>
     </row>
-    <row r="610" spans="1:22">
+    <row r="610" spans="1:22" ht="14.25">
       <c r="A610" s="7"/>
       <c r="B610" s="25"/>
       <c r="C610" s="3"/>
@@ -16043,7 +16010,7 @@
       <c r="U610" s="1"/>
       <c r="V610" s="1"/>
     </row>
-    <row r="611" spans="1:22">
+    <row r="611" spans="1:22" ht="14.25">
       <c r="A611" s="7"/>
       <c r="B611" s="25"/>
       <c r="C611" s="3"/>
@@ -16067,7 +16034,7 @@
       <c r="U611" s="1"/>
       <c r="V611" s="1"/>
     </row>
-    <row r="612" spans="1:22">
+    <row r="612" spans="1:22" ht="14.25">
       <c r="A612" s="7"/>
       <c r="B612" s="25"/>
       <c r="C612" s="3"/>
@@ -16091,7 +16058,7 @@
       <c r="U612" s="1"/>
       <c r="V612" s="1"/>
     </row>
-    <row r="613" spans="1:22">
+    <row r="613" spans="1:22" ht="14.25">
       <c r="A613" s="7"/>
       <c r="B613" s="25"/>
       <c r="C613" s="3"/>
@@ -16115,7 +16082,7 @@
       <c r="U613" s="1"/>
       <c r="V613" s="1"/>
     </row>
-    <row r="614" spans="1:22">
+    <row r="614" spans="1:22" ht="14.25">
       <c r="A614" s="7"/>
       <c r="B614" s="25"/>
       <c r="C614" s="3"/>
@@ -16139,7 +16106,7 @@
       <c r="U614" s="1"/>
       <c r="V614" s="1"/>
     </row>
-    <row r="615" spans="1:22">
+    <row r="615" spans="1:22" ht="14.25">
       <c r="A615" s="7"/>
       <c r="B615" s="25"/>
       <c r="C615" s="3"/>
@@ -16163,7 +16130,7 @@
       <c r="U615" s="1"/>
       <c r="V615" s="1"/>
     </row>
-    <row r="616" spans="1:22">
+    <row r="616" spans="1:22" ht="14.25">
       <c r="A616" s="7"/>
       <c r="B616" s="25"/>
       <c r="C616" s="3"/>
@@ -16187,7 +16154,7 @@
       <c r="U616" s="1"/>
       <c r="V616" s="1"/>
     </row>
-    <row r="617" spans="1:22">
+    <row r="617" spans="1:22" ht="14.25">
       <c r="A617" s="7"/>
       <c r="B617" s="25"/>
       <c r="C617" s="3"/>
@@ -16211,7 +16178,7 @@
       <c r="U617" s="1"/>
       <c r="V617" s="1"/>
     </row>
-    <row r="618" spans="1:22">
+    <row r="618" spans="1:22" ht="14.25">
       <c r="A618" s="7"/>
       <c r="B618" s="25"/>
       <c r="C618" s="3"/>
@@ -16235,7 +16202,7 @@
       <c r="U618" s="1"/>
       <c r="V618" s="1"/>
     </row>
-    <row r="619" spans="1:22">
+    <row r="619" spans="1:22" ht="14.25">
       <c r="A619" s="7"/>
       <c r="B619" s="25"/>
       <c r="C619" s="3"/>
@@ -16259,7 +16226,7 @@
       <c r="U619" s="1"/>
       <c r="V619" s="1"/>
     </row>
-    <row r="620" spans="1:22">
+    <row r="620" spans="1:22" ht="14.25">
       <c r="A620" s="7"/>
       <c r="B620" s="25"/>
       <c r="C620" s="3"/>
@@ -16283,7 +16250,7 @@
       <c r="U620" s="1"/>
       <c r="V620" s="1"/>
     </row>
-    <row r="621" spans="1:22">
+    <row r="621" spans="1:22" ht="14.25">
       <c r="A621" s="7"/>
       <c r="B621" s="25"/>
       <c r="C621" s="3"/>
@@ -16307,7 +16274,7 @@
       <c r="U621" s="1"/>
       <c r="V621" s="1"/>
     </row>
-    <row r="622" spans="1:22">
+    <row r="622" spans="1:22" ht="14.25">
       <c r="A622" s="7"/>
       <c r="B622" s="25"/>
       <c r="C622" s="3"/>
@@ -16331,7 +16298,7 @@
       <c r="U622" s="1"/>
       <c r="V622" s="1"/>
     </row>
-    <row r="623" spans="1:22">
+    <row r="623" spans="1:22" ht="14.25">
       <c r="A623" s="7"/>
       <c r="B623" s="25"/>
       <c r="C623" s="3"/>
@@ -16355,7 +16322,7 @@
       <c r="U623" s="1"/>
       <c r="V623" s="1"/>
     </row>
-    <row r="624" spans="1:22">
+    <row r="624" spans="1:22" ht="14.25">
       <c r="A624" s="7"/>
       <c r="B624" s="25"/>
       <c r="C624" s="3"/>
@@ -16379,7 +16346,7 @@
       <c r="U624" s="1"/>
       <c r="V624" s="1"/>
     </row>
-    <row r="625" spans="1:22">
+    <row r="625" spans="1:22" ht="14.25">
       <c r="A625" s="7"/>
       <c r="B625" s="25"/>
       <c r="C625" s="3"/>
@@ -16403,7 +16370,7 @@
       <c r="U625" s="1"/>
       <c r="V625" s="1"/>
     </row>
-    <row r="626" spans="1:22">
+    <row r="626" spans="1:22" ht="14.25">
       <c r="A626" s="7"/>
       <c r="B626" s="25"/>
       <c r="C626" s="3"/>
@@ -16427,7 +16394,7 @@
       <c r="U626" s="1"/>
       <c r="V626" s="1"/>
     </row>
-    <row r="627" spans="1:22">
+    <row r="627" spans="1:22" ht="14.25">
       <c r="A627" s="7"/>
       <c r="B627" s="25"/>
       <c r="C627" s="3"/>
@@ -16451,7 +16418,7 @@
       <c r="U627" s="1"/>
       <c r="V627" s="1"/>
     </row>
-    <row r="628" spans="1:22">
+    <row r="628" spans="1:22" ht="14.25">
       <c r="A628" s="7"/>
       <c r="B628" s="25"/>
       <c r="C628" s="3"/>
@@ -16475,7 +16442,7 @@
       <c r="U628" s="1"/>
       <c r="V628" s="1"/>
     </row>
-    <row r="629" spans="1:22">
+    <row r="629" spans="1:22" ht="14.25">
       <c r="A629" s="7"/>
       <c r="B629" s="25"/>
       <c r="C629" s="3"/>
@@ -16499,7 +16466,7 @@
       <c r="U629" s="1"/>
       <c r="V629" s="1"/>
     </row>
-    <row r="630" spans="1:22">
+    <row r="630" spans="1:22" ht="14.25">
       <c r="A630" s="7"/>
       <c r="B630" s="25"/>
       <c r="C630" s="3"/>
@@ -16523,7 +16490,7 @@
       <c r="U630" s="1"/>
       <c r="V630" s="1"/>
     </row>
-    <row r="631" spans="1:22">
+    <row r="631" spans="1:22" ht="14.25">
       <c r="A631" s="7"/>
       <c r="B631" s="25"/>
       <c r="C631" s="3"/>
@@ -16547,7 +16514,7 @@
       <c r="U631" s="1"/>
       <c r="V631" s="1"/>
     </row>
-    <row r="632" spans="1:22">
+    <row r="632" spans="1:22" ht="14.25">
       <c r="A632" s="7"/>
       <c r="B632" s="25"/>
       <c r="C632" s="3"/>
@@ -16571,7 +16538,7 @@
       <c r="U632" s="1"/>
       <c r="V632" s="1"/>
     </row>
-    <row r="633" spans="1:22">
+    <row r="633" spans="1:22" ht="14.25">
       <c r="A633" s="7"/>
       <c r="B633" s="25"/>
       <c r="C633" s="3"/>
@@ -16595,7 +16562,7 @@
       <c r="U633" s="1"/>
       <c r="V633" s="1"/>
     </row>
-    <row r="634" spans="1:22">
+    <row r="634" spans="1:22" ht="14.25">
       <c r="A634" s="7"/>
       <c r="B634" s="25"/>
       <c r="C634" s="3"/>
@@ -16619,7 +16586,7 @@
       <c r="U634" s="1"/>
       <c r="V634" s="1"/>
     </row>
-    <row r="635" spans="1:22">
+    <row r="635" spans="1:22" ht="14.25">
       <c r="A635" s="7"/>
       <c r="B635" s="25"/>
       <c r="C635" s="3"/>
@@ -16643,7 +16610,7 @@
       <c r="U635" s="1"/>
       <c r="V635" s="1"/>
     </row>
-    <row r="636" spans="1:22">
+    <row r="636" spans="1:22" ht="14.25">
       <c r="A636" s="7"/>
       <c r="B636" s="25"/>
       <c r="C636" s="3"/>
@@ -16667,7 +16634,7 @@
       <c r="U636" s="1"/>
       <c r="V636" s="1"/>
     </row>
-    <row r="637" spans="1:22">
+    <row r="637" spans="1:22" ht="14.25">
       <c r="A637" s="7"/>
       <c r="B637" s="25"/>
       <c r="C637" s="3"/>
@@ -16691,7 +16658,7 @@
       <c r="U637" s="1"/>
       <c r="V637" s="1"/>
     </row>
-    <row r="638" spans="1:22">
+    <row r="638" spans="1:22" ht="14.25">
       <c r="A638" s="7"/>
       <c r="B638" s="25"/>
       <c r="C638" s="3"/>
@@ -16715,7 +16682,7 @@
       <c r="U638" s="1"/>
       <c r="V638" s="1"/>
     </row>
-    <row r="639" spans="1:22">
+    <row r="639" spans="1:22" ht="14.25">
       <c r="A639" s="7"/>
       <c r="B639" s="25"/>
       <c r="C639" s="3"/>
@@ -16739,7 +16706,7 @@
       <c r="U639" s="1"/>
       <c r="V639" s="1"/>
     </row>
-    <row r="640" spans="1:22">
+    <row r="640" spans="1:22" ht="14.25">
       <c r="A640" s="7"/>
       <c r="B640" s="25"/>
       <c r="C640" s="3"/>
@@ -16763,7 +16730,7 @@
       <c r="U640" s="1"/>
       <c r="V640" s="1"/>
     </row>
-    <row r="641" spans="1:22">
+    <row r="641" spans="1:22" ht="14.25">
       <c r="A641" s="7"/>
       <c r="B641" s="25"/>
       <c r="C641" s="3"/>
@@ -16787,7 +16754,7 @@
       <c r="U641" s="1"/>
       <c r="V641" s="1"/>
     </row>
-    <row r="642" spans="1:22">
+    <row r="642" spans="1:22" ht="14.25">
       <c r="A642" s="7"/>
       <c r="B642" s="25"/>
       <c r="C642" s="3"/>
@@ -16811,7 +16778,7 @@
       <c r="U642" s="1"/>
       <c r="V642" s="1"/>
     </row>
-    <row r="643" spans="1:22">
+    <row r="643" spans="1:22" ht="14.25">
       <c r="A643" s="7"/>
       <c r="B643" s="25"/>
       <c r="C643" s="3"/>
@@ -16835,7 +16802,7 @@
       <c r="U643" s="1"/>
       <c r="V643" s="1"/>
     </row>
-    <row r="644" spans="1:22">
+    <row r="644" spans="1:22" ht="14.25">
       <c r="A644" s="7"/>
       <c r="B644" s="25"/>
       <c r="C644" s="3"/>
@@ -16859,7 +16826,7 @@
       <c r="U644" s="1"/>
       <c r="V644" s="1"/>
     </row>
-    <row r="645" spans="1:22">
+    <row r="645" spans="1:22" ht="14.25">
       <c r="A645" s="7"/>
       <c r="B645" s="25"/>
       <c r="C645" s="3"/>
@@ -16883,7 +16850,7 @@
       <c r="U645" s="1"/>
       <c r="V645" s="1"/>
     </row>
-    <row r="646" spans="1:22">
+    <row r="646" spans="1:22" ht="14.25">
       <c r="A646" s="7"/>
       <c r="B646" s="25"/>
       <c r="C646" s="3"/>
@@ -16907,7 +16874,7 @@
       <c r="U646" s="1"/>
       <c r="V646" s="1"/>
     </row>
-    <row r="647" spans="1:22">
+    <row r="647" spans="1:22" ht="14.25">
       <c r="A647" s="7"/>
       <c r="B647" s="25"/>
       <c r="C647" s="3"/>
@@ -16931,7 +16898,7 @@
       <c r="U647" s="1"/>
       <c r="V647" s="1"/>
     </row>
-    <row r="648" spans="1:22">
+    <row r="648" spans="1:22" ht="14.25">
       <c r="A648" s="7"/>
       <c r="B648" s="25"/>
       <c r="C648" s="3"/>
@@ -16955,7 +16922,7 @@
       <c r="U648" s="1"/>
       <c r="V648" s="1"/>
     </row>
-    <row r="649" spans="1:22">
+    <row r="649" spans="1:22" ht="14.25">
       <c r="A649" s="7"/>
       <c r="B649" s="25"/>
       <c r="C649" s="3"/>
@@ -16979,7 +16946,7 @@
       <c r="U649" s="1"/>
       <c r="V649" s="1"/>
     </row>
-    <row r="650" spans="1:22">
+    <row r="650" spans="1:22" ht="14.25">
       <c r="A650" s="7"/>
       <c r="B650" s="25"/>
       <c r="C650" s="3"/>
@@ -17003,7 +16970,7 @@
       <c r="U650" s="1"/>
       <c r="V650" s="1"/>
     </row>
-    <row r="651" spans="1:22">
+    <row r="651" spans="1:22" ht="14.25">
       <c r="A651" s="7"/>
       <c r="B651" s="25"/>
       <c r="C651" s="3"/>
@@ -17027,7 +16994,7 @@
       <c r="U651" s="1"/>
       <c r="V651" s="1"/>
     </row>
-    <row r="652" spans="1:22">
+    <row r="652" spans="1:22" ht="14.25">
       <c r="A652" s="7"/>
       <c r="B652" s="25"/>
       <c r="C652" s="3"/>
@@ -17051,7 +17018,7 @@
       <c r="U652" s="1"/>
       <c r="V652" s="1"/>
     </row>
-    <row r="653" spans="1:22">
+    <row r="653" spans="1:22" ht="14.25">
       <c r="A653" s="7"/>
       <c r="B653" s="25"/>
       <c r="C653" s="3"/>
@@ -17075,7 +17042,7 @@
       <c r="U653" s="1"/>
       <c r="V653" s="1"/>
     </row>
-    <row r="654" spans="1:22">
+    <row r="654" spans="1:22" ht="14.25">
       <c r="A654" s="7"/>
       <c r="B654" s="25"/>
       <c r="C654" s="3"/>
@@ -17099,7 +17066,7 @@
       <c r="U654" s="1"/>
       <c r="V654" s="1"/>
     </row>
-    <row r="655" spans="1:22">
+    <row r="655" spans="1:22" ht="14.25">
       <c r="A655" s="7"/>
       <c r="B655" s="25"/>
       <c r="C655" s="3"/>
@@ -17123,7 +17090,7 @@
       <c r="U655" s="1"/>
       <c r="V655" s="1"/>
     </row>
-    <row r="656" spans="1:22">
+    <row r="656" spans="1:22" ht="14.25">
       <c r="A656" s="7"/>
       <c r="B656" s="25"/>
       <c r="C656" s="3"/>
@@ -17147,7 +17114,7 @@
       <c r="U656" s="1"/>
       <c r="V656" s="1"/>
     </row>
-    <row r="657" spans="1:22">
+    <row r="657" spans="1:22" ht="14.25">
       <c r="A657" s="7"/>
       <c r="B657" s="25"/>
       <c r="C657" s="3"/>
@@ -17171,7 +17138,7 @@
       <c r="U657" s="1"/>
       <c r="V657" s="1"/>
     </row>
-    <row r="658" spans="1:22">
+    <row r="658" spans="1:22" ht="14.25">
       <c r="A658" s="7"/>
       <c r="B658" s="25"/>
       <c r="C658" s="3"/>
@@ -17195,7 +17162,7 @@
       <c r="U658" s="1"/>
       <c r="V658" s="1"/>
     </row>
-    <row r="659" spans="1:22">
+    <row r="659" spans="1:22" ht="14.25">
       <c r="A659" s="7"/>
       <c r="B659" s="25"/>
       <c r="C659" s="3"/>
@@ -17219,7 +17186,7 @@
       <c r="U659" s="1"/>
       <c r="V659" s="1"/>
     </row>
-    <row r="660" spans="1:22">
+    <row r="660" spans="1:22" ht="14.25">
       <c r="A660" s="7"/>
       <c r="B660" s="25"/>
       <c r="C660" s="3"/>
@@ -17243,7 +17210,7 @@
       <c r="U660" s="1"/>
       <c r="V660" s="1"/>
     </row>
-    <row r="661" spans="1:22">
+    <row r="661" spans="1:22" ht="14.25">
       <c r="A661" s="7"/>
       <c r="B661" s="25"/>
       <c r="C661" s="3"/>
@@ -17267,7 +17234,7 @@
       <c r="U661" s="1"/>
       <c r="V661" s="1"/>
     </row>
-    <row r="662" spans="1:22">
+    <row r="662" spans="1:22" ht="14.25">
       <c r="A662" s="7"/>
       <c r="B662" s="25"/>
       <c r="C662" s="3"/>
@@ -17291,7 +17258,7 @@
       <c r="U662" s="1"/>
       <c r="V662" s="1"/>
     </row>
-    <row r="663" spans="1:22">
+    <row r="663" spans="1:22" ht="14.25">
       <c r="A663" s="7"/>
       <c r="B663" s="25"/>
       <c r="C663" s="3"/>
@@ -17315,7 +17282,7 @@
       <c r="U663" s="1"/>
       <c r="V663" s="1"/>
     </row>
-    <row r="664" spans="1:22">
+    <row r="664" spans="1:22" ht="14.25">
       <c r="A664" s="7"/>
       <c r="B664" s="25"/>
       <c r="C664" s="3"/>
@@ -17339,7 +17306,7 @@
       <c r="U664" s="1"/>
       <c r="V664" s="1"/>
     </row>
-    <row r="665" spans="1:22">
+    <row r="665" spans="1:22" ht="14.25">
       <c r="A665" s="7"/>
       <c r="B665" s="25"/>
       <c r="C665" s="3"/>
@@ -17363,7 +17330,7 @@
       <c r="U665" s="1"/>
       <c r="V665" s="1"/>
     </row>
-    <row r="666" spans="1:22">
+    <row r="666" spans="1:22" ht="14.25">
       <c r="A666" s="7"/>
       <c r="B666" s="25"/>
       <c r="C666" s="3"/>
@@ -17387,7 +17354,7 @@
       <c r="U666" s="1"/>
       <c r="V666" s="1"/>
     </row>
-    <row r="667" spans="1:22">
+    <row r="667" spans="1:22" ht="14.25">
       <c r="A667" s="7"/>
       <c r="B667" s="25"/>
       <c r="C667" s="3"/>
@@ -17411,7 +17378,7 @@
       <c r="U667" s="1"/>
       <c r="V667" s="1"/>
     </row>
-    <row r="668" spans="1:22">
+    <row r="668" spans="1:22" ht="14.25">
       <c r="A668" s="7"/>
       <c r="B668" s="25"/>
       <c r="C668" s="3"/>
@@ -17435,7 +17402,7 @@
       <c r="U668" s="1"/>
       <c r="V668" s="1"/>
     </row>
-    <row r="669" spans="1:22">
+    <row r="669" spans="1:22" ht="14.25">
       <c r="A669" s="7"/>
       <c r="B669" s="25"/>
       <c r="C669" s="3"/>
@@ -17459,7 +17426,7 @@
       <c r="U669" s="1"/>
       <c r="V669" s="1"/>
     </row>
-    <row r="670" spans="1:22">
+    <row r="670" spans="1:22" ht="14.25">
       <c r="A670" s="7"/>
       <c r="B670" s="25"/>
       <c r="C670" s="3"/>
@@ -17483,7 +17450,7 @@
       <c r="U670" s="1"/>
       <c r="V670" s="1"/>
     </row>
-    <row r="671" spans="1:22">
+    <row r="671" spans="1:22" ht="14.25">
       <c r="A671" s="7"/>
       <c r="B671" s="25"/>
       <c r="C671" s="3"/>
@@ -17507,7 +17474,7 @@
       <c r="U671" s="1"/>
       <c r="V671" s="1"/>
     </row>
-    <row r="672" spans="1:22">
+    <row r="672" spans="1:22" ht="14.25">
       <c r="A672" s="7"/>
       <c r="B672" s="25"/>
       <c r="C672" s="3"/>
@@ -17531,7 +17498,7 @@
       <c r="U672" s="1"/>
       <c r="V672" s="1"/>
     </row>
-    <row r="673" spans="1:22">
+    <row r="673" spans="1:22" ht="14.25">
       <c r="A673" s="7"/>
       <c r="B673" s="25"/>
       <c r="C673" s="3"/>
@@ -17555,7 +17522,7 @@
       <c r="U673" s="1"/>
       <c r="V673" s="1"/>
     </row>
-    <row r="674" spans="1:22">
+    <row r="674" spans="1:22" ht="14.25">
       <c r="A674" s="7"/>
       <c r="B674" s="25"/>
       <c r="C674" s="3"/>
@@ -17579,7 +17546,7 @@
       <c r="U674" s="1"/>
       <c r="V674" s="1"/>
     </row>
-    <row r="675" spans="1:22">
+    <row r="675" spans="1:22" ht="14.25">
       <c r="A675" s="7"/>
       <c r="B675" s="25"/>
       <c r="C675" s="3"/>
@@ -17603,7 +17570,7 @@
       <c r="U675" s="1"/>
       <c r="V675" s="1"/>
     </row>
-    <row r="676" spans="1:22">
+    <row r="676" spans="1:22" ht="14.25">
       <c r="A676" s="7"/>
       <c r="B676" s="25"/>
       <c r="C676" s="3"/>
@@ -17627,7 +17594,7 @@
       <c r="U676" s="1"/>
       <c r="V676" s="1"/>
     </row>
-    <row r="677" spans="1:22">
+    <row r="677" spans="1:22" ht="14.25">
       <c r="A677" s="7"/>
       <c r="B677" s="25"/>
       <c r="C677" s="3"/>
@@ -17651,7 +17618,7 @@
       <c r="U677" s="1"/>
       <c r="V677" s="1"/>
     </row>
-    <row r="678" spans="1:22">
+    <row r="678" spans="1:22" ht="14.25">
       <c r="A678" s="7"/>
       <c r="B678" s="25"/>
       <c r="C678" s="3"/>
@@ -17675,7 +17642,7 @@
       <c r="U678" s="1"/>
       <c r="V678" s="1"/>
     </row>
-    <row r="679" spans="1:22">
+    <row r="679" spans="1:22" ht="14.25">
       <c r="A679" s="7"/>
       <c r="B679" s="25"/>
       <c r="C679" s="3"/>
@@ -17699,7 +17666,7 @@
       <c r="U679" s="1"/>
       <c r="V679" s="1"/>
     </row>
-    <row r="680" spans="1:22">
+    <row r="680" spans="1:22" ht="14.25">
       <c r="A680" s="7"/>
       <c r="B680" s="25"/>
       <c r="C680" s="3"/>
@@ -17723,7 +17690,7 @@
       <c r="U680" s="1"/>
       <c r="V680" s="1"/>
     </row>
-    <row r="681" spans="1:22">
+    <row r="681" spans="1:22" ht="14.25">
       <c r="A681" s="7"/>
       <c r="B681" s="25"/>
       <c r="C681" s="3"/>
@@ -17747,7 +17714,7 @@
       <c r="U681" s="1"/>
       <c r="V681" s="1"/>
     </row>
-    <row r="682" spans="1:22">
+    <row r="682" spans="1:22" ht="14.25">
       <c r="A682" s="7"/>
       <c r="B682" s="25"/>
       <c r="C682" s="3"/>
@@ -17771,7 +17738,7 @@
       <c r="U682" s="1"/>
       <c r="V682" s="1"/>
     </row>
-    <row r="683" spans="1:22">
+    <row r="683" spans="1:22" ht="14.25">
       <c r="A683" s="7"/>
       <c r="B683" s="25"/>
       <c r="C683" s="3"/>
@@ -17795,7 +17762,7 @@
       <c r="U683" s="1"/>
       <c r="V683" s="1"/>
     </row>
-    <row r="684" spans="1:22">
+    <row r="684" spans="1:22" ht="14.25">
       <c r="A684" s="7"/>
       <c r="B684" s="25"/>
       <c r="C684" s="3"/>
@@ -17819,7 +17786,7 @@
       <c r="U684" s="1"/>
       <c r="V684" s="1"/>
     </row>
-    <row r="685" spans="1:22">
+    <row r="685" spans="1:22" ht="14.25">
       <c r="A685" s="7"/>
       <c r="B685" s="25"/>
       <c r="C685" s="3"/>
@@ -17843,7 +17810,7 @@
       <c r="U685" s="1"/>
       <c r="V685" s="1"/>
     </row>
-    <row r="686" spans="1:22">
+    <row r="686" spans="1:22" ht="14.25">
       <c r="A686" s="7"/>
       <c r="B686" s="25"/>
       <c r="C686" s="3"/>
@@ -17867,7 +17834,7 @@
       <c r="U686" s="1"/>
       <c r="V686" s="1"/>
     </row>
-    <row r="687" spans="1:22">
+    <row r="687" spans="1:22" ht="14.25">
       <c r="A687" s="7"/>
       <c r="B687" s="25"/>
       <c r="C687" s="3"/>
@@ -17891,7 +17858,7 @@
       <c r="U687" s="1"/>
       <c r="V687" s="1"/>
     </row>
-    <row r="688" spans="1:22">
+    <row r="688" spans="1:22" ht="14.25">
       <c r="A688" s="7"/>
       <c r="B688" s="25"/>
       <c r="C688" s="3"/>
@@ -17915,7 +17882,7 @@
       <c r="U688" s="1"/>
       <c r="V688" s="1"/>
     </row>
-    <row r="689" spans="1:22">
+    <row r="689" spans="1:22" ht="14.25">
       <c r="A689" s="7"/>
       <c r="B689" s="25"/>
       <c r="C689" s="3"/>
@@ -17939,7 +17906,7 @@
       <c r="U689" s="1"/>
       <c r="V689" s="1"/>
     </row>
-    <row r="690" spans="1:22">
+    <row r="690" spans="1:22" ht="14.25">
       <c r="A690" s="7"/>
       <c r="B690" s="25"/>
       <c r="C690" s="3"/>
@@ -17963,7 +17930,7 @@
       <c r="U690" s="1"/>
       <c r="V690" s="1"/>
     </row>
-    <row r="691" spans="1:22">
+    <row r="691" spans="1:22" ht="14.25">
       <c r="A691" s="7"/>
       <c r="B691" s="25"/>
       <c r="C691" s="3"/>
@@ -17987,7 +17954,7 @@
       <c r="U691" s="1"/>
       <c r="V691" s="1"/>
     </row>
-    <row r="692" spans="1:22">
+    <row r="692" spans="1:22" ht="14.25">
       <c r="A692" s="7"/>
       <c r="B692" s="25"/>
       <c r="C692" s="3"/>
@@ -18011,7 +17978,7 @@
       <c r="U692" s="1"/>
       <c r="V692" s="1"/>
     </row>
-    <row r="693" spans="1:22">
+    <row r="693" spans="1:22" ht="14.25">
       <c r="A693" s="7"/>
       <c r="B693" s="25"/>
       <c r="C693" s="3"/>
@@ -18035,7 +18002,7 @@
       <c r="U693" s="1"/>
       <c r="V693" s="1"/>
     </row>
-    <row r="694" spans="1:22">
+    <row r="694" spans="1:22" ht="14.25">
       <c r="A694" s="7"/>
       <c r="B694" s="25"/>
       <c r="C694" s="3"/>
@@ -18059,7 +18026,7 @@
       <c r="U694" s="1"/>
       <c r="V694" s="1"/>
     </row>
-    <row r="695" spans="1:22">
+    <row r="695" spans="1:22" ht="14.25">
       <c r="A695" s="7"/>
       <c r="B695" s="25"/>
       <c r="C695" s="3"/>
@@ -18083,7 +18050,7 @@
       <c r="U695" s="1"/>
       <c r="V695" s="1"/>
     </row>
-    <row r="696" spans="1:22">
+    <row r="696" spans="1:22" ht="14.25">
       <c r="A696" s="7"/>
       <c r="B696" s="25"/>
       <c r="C696" s="3"/>
@@ -18107,7 +18074,7 @@
       <c r="U696" s="1"/>
       <c r="V696" s="1"/>
     </row>
-    <row r="697" spans="1:22">
+    <row r="697" spans="1:22" ht="14.25">
       <c r="A697" s="7"/>
       <c r="B697" s="25"/>
       <c r="C697" s="3"/>
@@ -18131,7 +18098,7 @@
       <c r="U697" s="1"/>
       <c r="V697" s="1"/>
     </row>
-    <row r="698" spans="1:22">
+    <row r="698" spans="1:22" ht="14.25">
       <c r="A698" s="7"/>
       <c r="B698" s="25"/>
       <c r="C698" s="3"/>
@@ -18155,7 +18122,7 @@
       <c r="U698" s="1"/>
       <c r="V698" s="1"/>
     </row>
-    <row r="699" spans="1:22">
+    <row r="699" spans="1:22" ht="14.25">
       <c r="A699" s="7"/>
       <c r="B699" s="25"/>
       <c r="C699" s="3"/>
@@ -18179,7 +18146,7 @@
       <c r="U699" s="1"/>
       <c r="V699" s="1"/>
     </row>
-    <row r="700" spans="1:22">
+    <row r="700" spans="1:22" ht="14.25">
       <c r="A700" s="7"/>
       <c r="B700" s="25"/>
       <c r="C700" s="3"/>
@@ -18203,7 +18170,7 @@
       <c r="U700" s="1"/>
       <c r="V700" s="1"/>
     </row>
-    <row r="701" spans="1:22">
+    <row r="701" spans="1:22" ht="14.25">
       <c r="A701" s="7"/>
       <c r="B701" s="25"/>
       <c r="C701" s="3"/>
@@ -18227,7 +18194,7 @@
       <c r="U701" s="1"/>
       <c r="V701" s="1"/>
     </row>
-    <row r="702" spans="1:22">
+    <row r="702" spans="1:22" ht="14.25">
       <c r="A702" s="7"/>
       <c r="B702" s="25"/>
       <c r="C702" s="3"/>
@@ -18251,7 +18218,7 @@
       <c r="U702" s="1"/>
       <c r="V702" s="1"/>
     </row>
-    <row r="703" spans="1:22">
+    <row r="703" spans="1:22" ht="14.25">
       <c r="A703" s="7"/>
       <c r="B703" s="25"/>
       <c r="C703" s="3"/>
@@ -18275,7 +18242,7 @@
       <c r="U703" s="1"/>
       <c r="V703" s="1"/>
     </row>
-    <row r="704" spans="1:22">
+    <row r="704" spans="1:22" ht="14.25">
       <c r="A704" s="7"/>
       <c r="B704" s="25"/>
       <c r="C704" s="3"/>
@@ -18299,7 +18266,7 @@
       <c r="U704" s="1"/>
       <c r="V704" s="1"/>
     </row>
-    <row r="705" spans="1:22">
+    <row r="705" spans="1:22" ht="14.25">
       <c r="A705" s="7"/>
       <c r="B705" s="25"/>
       <c r="C705" s="3"/>
@@ -18323,7 +18290,7 @@
       <c r="U705" s="1"/>
       <c r="V705" s="1"/>
     </row>
-    <row r="706" spans="1:22">
+    <row r="706" spans="1:22" ht="14.25">
       <c r="A706" s="7"/>
       <c r="B706" s="25"/>
       <c r="C706" s="3"/>
@@ -18347,7 +18314,7 @@
       <c r="U706" s="1"/>
       <c r="V706" s="1"/>
     </row>
-    <row r="707" spans="1:22">
+    <row r="707" spans="1:22" ht="14.25">
       <c r="A707" s="7"/>
       <c r="B707" s="25"/>
       <c r="C707" s="3"/>
@@ -18371,7 +18338,7 @@
       <c r="U707" s="1"/>
       <c r="V707" s="1"/>
     </row>
-    <row r="708" spans="1:22">
+    <row r="708" spans="1:22" ht="14.25">
       <c r="A708" s="7"/>
       <c r="B708" s="25"/>
       <c r="C708" s="3"/>
@@ -18395,7 +18362,7 @@
       <c r="U708" s="1"/>
       <c r="V708" s="1"/>
     </row>
-    <row r="709" spans="1:22">
+    <row r="709" spans="1:22" ht="14.25">
       <c r="A709" s="7"/>
       <c r="B709" s="25"/>
       <c r="C709" s="3"/>
@@ -18419,7 +18386,7 @@
       <c r="U709" s="1"/>
       <c r="V709" s="1"/>
     </row>
-    <row r="710" spans="1:22">
+    <row r="710" spans="1:22" ht="14.25">
       <c r="A710" s="7"/>
       <c r="B710" s="25"/>
       <c r="C710" s="3"/>
@@ -18443,7 +18410,7 @@
       <c r="U710" s="1"/>
       <c r="V710" s="1"/>
     </row>
-    <row r="711" spans="1:22">
+    <row r="711" spans="1:22" ht="14.25">
       <c r="A711" s="7"/>
       <c r="B711" s="25"/>
       <c r="C711" s="3"/>
@@ -18467,7 +18434,7 @@
       <c r="U711" s="1"/>
       <c r="V711" s="1"/>
     </row>
-    <row r="712" spans="1:22">
+    <row r="712" spans="1:22" ht="14.25">
       <c r="A712" s="7"/>
       <c r="B712" s="25"/>
       <c r="C712" s="3"/>
@@ -18491,7 +18458,7 @@
       <c r="U712" s="1"/>
       <c r="V712" s="1"/>
     </row>
-    <row r="713" spans="1:22">
+    <row r="713" spans="1:22" ht="14.25">
       <c r="A713" s="7"/>
       <c r="B713" s="25"/>
       <c r="C713" s="3"/>
@@ -18515,7 +18482,7 @@
       <c r="U713" s="1"/>
       <c r="V713" s="1"/>
     </row>
-    <row r="714" spans="1:22">
+    <row r="714" spans="1:22" ht="14.25">
       <c r="A714" s="7"/>
       <c r="B714" s="25"/>
       <c r="C714" s="3"/>
@@ -18539,7 +18506,7 @@
       <c r="U714" s="1"/>
       <c r="V714" s="1"/>
     </row>
-    <row r="715" spans="1:22">
+    <row r="715" spans="1:22" ht="14.25">
       <c r="A715" s="7"/>
       <c r="B715" s="25"/>
       <c r="C715" s="3"/>
@@ -18563,7 +18530,7 @@
       <c r="U715" s="1"/>
       <c r="V715" s="1"/>
     </row>
-    <row r="716" spans="1:22">
+    <row r="716" spans="1:22" ht="14.25">
       <c r="A716" s="7"/>
       <c r="B716" s="25"/>
       <c r="C716" s="3"/>
@@ -18587,7 +18554,7 @@
       <c r="U716" s="1"/>
       <c r="V716" s="1"/>
     </row>
-    <row r="717" spans="1:22">
+    <row r="717" spans="1:22" ht="14.25">
       <c r="A717" s="7"/>
       <c r="B717" s="25"/>
       <c r="C717" s="3"/>
@@ -18611,7 +18578,7 @@
       <c r="U717" s="1"/>
       <c r="V717" s="1"/>
     </row>
-    <row r="718" spans="1:22">
+    <row r="718" spans="1:22" ht="14.25">
       <c r="A718" s="7"/>
       <c r="B718" s="25"/>
       <c r="C718" s="3"/>
@@ -18635,7 +18602,7 @@
       <c r="U718" s="1"/>
       <c r="V718" s="1"/>
     </row>
-    <row r="719" spans="1:22">
+    <row r="719" spans="1:22" ht="14.25">
       <c r="A719" s="7"/>
       <c r="B719" s="25"/>
       <c r="C719" s="3"/>
@@ -18659,7 +18626,7 @@
       <c r="U719" s="1"/>
       <c r="V719" s="1"/>
     </row>
-    <row r="720" spans="1:22">
+    <row r="720" spans="1:22" ht="14.25">
       <c r="A720" s="7"/>
       <c r="B720" s="25"/>
       <c r="C720" s="3"/>
@@ -18683,7 +18650,7 @@
       <c r="U720" s="1"/>
       <c r="V720" s="1"/>
     </row>
-    <row r="721" spans="1:22">
+    <row r="721" spans="1:22" ht="14.25">
       <c r="A721" s="7"/>
       <c r="B721" s="25"/>
       <c r="C721" s="3"/>
@@ -18707,7 +18674,7 @@
       <c r="U721" s="1"/>
       <c r="V721" s="1"/>
     </row>
-    <row r="722" spans="1:22">
+    <row r="722" spans="1:22" ht="14.25">
       <c r="A722" s="7"/>
       <c r="B722" s="25"/>
       <c r="C722" s="3"/>
@@ -18731,7 +18698,7 @@
       <c r="U722" s="1"/>
       <c r="V722" s="1"/>
     </row>
-    <row r="723" spans="1:22">
+    <row r="723" spans="1:22" ht="14.25">
       <c r="A723" s="7"/>
       <c r="B723" s="25"/>
       <c r="C723" s="3"/>
@@ -18755,7 +18722,7 @@
       <c r="U723" s="1"/>
       <c r="V723" s="1"/>
     </row>
-    <row r="724" spans="1:22">
+    <row r="724" spans="1:22" ht="14.25">
       <c r="A724" s="7"/>
       <c r="B724" s="25"/>
       <c r="C724" s="3"/>
@@ -18779,7 +18746,7 @@
       <c r="U724" s="1"/>
       <c r="V724" s="1"/>
     </row>
-    <row r="725" spans="1:22">
+    <row r="725" spans="1:22" ht="14.25">
       <c r="A725" s="7"/>
       <c r="B725" s="25"/>
       <c r="C725" s="3"/>
@@ -18803,7 +18770,7 @@
       <c r="U725" s="1"/>
       <c r="V725" s="1"/>
     </row>
-    <row r="726" spans="1:22">
+    <row r="726" spans="1:22" ht="14.25">
       <c r="A726" s="7"/>
       <c r="B726" s="25"/>
       <c r="C726" s="3"/>
@@ -18827,7 +18794,7 @@
       <c r="U726" s="1"/>
       <c r="V726" s="1"/>
     </row>
-    <row r="727" spans="1:22">
+    <row r="727" spans="1:22" ht="14.25">
       <c r="A727" s="7"/>
       <c r="B727" s="25"/>
       <c r="C727" s="3"/>
@@ -18851,7 +18818,7 @@
       <c r="U727" s="1"/>
       <c r="V727" s="1"/>
     </row>
-    <row r="728" spans="1:22">
+    <row r="728" spans="1:22" ht="14.25">
       <c r="A728" s="7"/>
       <c r="B728" s="25"/>
       <c r="C728" s="3"/>
@@ -18875,7 +18842,7 @@
       <c r="U728" s="1"/>
       <c r="V728" s="1"/>
     </row>
-    <row r="729" spans="1:22">
+    <row r="729" spans="1:22" ht="14.25">
       <c r="A729" s="7"/>
       <c r="B729" s="25"/>
       <c r="C729" s="3"/>
@@ -18899,7 +18866,7 @@
       <c r="U729" s="1"/>
       <c r="V729" s="1"/>
     </row>
-    <row r="730" spans="1:22">
+    <row r="730" spans="1:22" ht="14.25">
       <c r="A730" s="7"/>
       <c r="B730" s="25"/>
       <c r="C730" s="3"/>
@@ -18923,7 +18890,7 @@
       <c r="U730" s="1"/>
       <c r="V730" s="1"/>
     </row>
-    <row r="731" spans="1:22">
+    <row r="731" spans="1:22" ht="14.25">
       <c r="A731" s="7"/>
       <c r="B731" s="25"/>
       <c r="C731" s="3"/>
@@ -18947,7 +18914,7 @@
       <c r="U731" s="1"/>
       <c r="V731" s="1"/>
     </row>
-    <row r="732" spans="1:22">
+    <row r="732" spans="1:22" ht="14.25">
       <c r="A732" s="7"/>
       <c r="B732" s="25"/>
       <c r="C732" s="3"/>
@@ -18971,7 +18938,7 @@
       <c r="U732" s="1"/>
       <c r="V732" s="1"/>
     </row>
-    <row r="733" spans="1:22">
+    <row r="733" spans="1:22" ht="14.25">
       <c r="A733" s="7"/>
       <c r="B733" s="25"/>
       <c r="C733" s="3"/>
@@ -18995,7 +18962,7 @@
       <c r="U733" s="1"/>
       <c r="V733" s="1"/>
     </row>
-    <row r="734" spans="1:22">
+    <row r="734" spans="1:22" ht="14.25">
       <c r="A734" s="7"/>
       <c r="B734" s="25"/>
       <c r="C734" s="3"/>
@@ -19019,7 +18986,7 @@
       <c r="U734" s="1"/>
       <c r="V734" s="1"/>
     </row>
-    <row r="735" spans="1:22">
+    <row r="735" spans="1:22" ht="14.25">
       <c r="A735" s="7"/>
       <c r="B735" s="25"/>
       <c r="C735" s="3"/>
@@ -19043,7 +19010,7 @@
       <c r="U735" s="1"/>
       <c r="V735" s="1"/>
     </row>
-    <row r="736" spans="1:22">
+    <row r="736" spans="1:22" ht="14.25">
       <c r="A736" s="7"/>
       <c r="B736" s="25"/>
       <c r="C736" s="3"/>
@@ -19067,7 +19034,7 @@
       <c r="U736" s="1"/>
       <c r="V736" s="1"/>
     </row>
-    <row r="737" spans="1:22">
+    <row r="737" spans="1:22" ht="14.25">
       <c r="A737" s="7"/>
       <c r="B737" s="25"/>
       <c r="C737" s="3"/>
@@ -19091,7 +19058,7 @@
       <c r="U737" s="1"/>
       <c r="V737" s="1"/>
     </row>
-    <row r="738" spans="1:22">
+    <row r="738" spans="1:22" ht="14.25">
       <c r="A738" s="7"/>
       <c r="B738" s="25"/>
       <c r="C738" s="3"/>
@@ -19115,7 +19082,7 @@
       <c r="U738" s="1"/>
       <c r="V738" s="1"/>
     </row>
-    <row r="739" spans="1:22">
+    <row r="739" spans="1:22" ht="14.25">
       <c r="A739" s="7"/>
       <c r="B739" s="25"/>
       <c r="C739" s="3"/>
@@ -19139,7 +19106,7 @@
       <c r="U739" s="1"/>
       <c r="V739" s="1"/>
     </row>
-    <row r="740" spans="1:22">
+    <row r="740" spans="1:22" ht="14.25">
       <c r="A740" s="7"/>
       <c r="B740" s="25"/>
       <c r="C740" s="3"/>
@@ -19163,7 +19130,7 @@
       <c r="U740" s="1"/>
       <c r="V740" s="1"/>
     </row>
-    <row r="741" spans="1:22">
+    <row r="741" spans="1:22" ht="14.25">
       <c r="A741" s="7"/>
       <c r="B741" s="25"/>
       <c r="C741" s="3"/>
@@ -19187,7 +19154,7 @@
       <c r="U741" s="1"/>
       <c r="V741" s="1"/>
     </row>
-    <row r="742" spans="1:22">
+    <row r="742" spans="1:22" ht="14.25">
       <c r="A742" s="7"/>
       <c r="B742" s="25"/>
       <c r="C742" s="3"/>
@@ -19211,7 +19178,7 @@
       <c r="U742" s="1"/>
       <c r="V742" s="1"/>
     </row>
-    <row r="743" spans="1:22">
+    <row r="743" spans="1:22" ht="14.25">
       <c r="A743" s="7"/>
       <c r="B743" s="25"/>
       <c r="C743" s="3"/>
@@ -19235,7 +19202,7 @@
       <c r="U743" s="1"/>
       <c r="V743" s="1"/>
     </row>
-    <row r="744" spans="1:22">
+    <row r="744" spans="1:22" ht="14.25">
       <c r="A744" s="7"/>
       <c r="B744" s="25"/>
       <c r="C744" s="3"/>
@@ -19259,7 +19226,7 @@
       <c r="U744" s="1"/>
       <c r="V744" s="1"/>
     </row>
-    <row r="745" spans="1:22">
+    <row r="745" spans="1:22" ht="14.25">
       <c r="A745" s="7"/>
       <c r="B745" s="25"/>
       <c r="C745" s="3"/>
@@ -19283,7 +19250,7 @@
       <c r="U745" s="1"/>
       <c r="V745" s="1"/>
     </row>
-    <row r="746" spans="1:22">
+    <row r="746" spans="1:22" ht="14.25">
       <c r="A746" s="7"/>
       <c r="B746" s="25"/>
       <c r="C746" s="3"/>
@@ -19307,7 +19274,7 @@
       <c r="U746" s="1"/>
       <c r="V746" s="1"/>
     </row>
-    <row r="747" spans="1:22">
+    <row r="747" spans="1:22" ht="14.25">
       <c r="A747" s="7"/>
       <c r="B747" s="25"/>
       <c r="C747" s="3"/>
@@ -19331,7 +19298,7 @@
       <c r="U747" s="1"/>
       <c r="V747" s="1"/>
     </row>
-    <row r="748" spans="1:22">
+    <row r="748" spans="1:22" ht="14.25">
       <c r="A748" s="7"/>
       <c r="B748" s="25"/>
       <c r="C748" s="3"/>
@@ -19355,7 +19322,7 @@
       <c r="U748" s="1"/>
       <c r="V748" s="1"/>
     </row>
-    <row r="749" spans="1:22">
+    <row r="749" spans="1:22" ht="14.25">
       <c r="A749" s="7"/>
       <c r="B749" s="25"/>
       <c r="C749" s="3"/>
@@ -19379,7 +19346,7 @@
       <c r="U749" s="1"/>
       <c r="V749" s="1"/>
     </row>
-    <row r="750" spans="1:22">
+    <row r="750" spans="1:22" ht="14.25">
       <c r="A750" s="7"/>
       <c r="B750" s="25"/>
       <c r="C750" s="3"/>
@@ -19403,7 +19370,7 @@
       <c r="U750" s="1"/>
       <c r="V750" s="1"/>
     </row>
-    <row r="751" spans="1:22">
+    <row r="751" spans="1:22" ht="14.25">
       <c r="A751" s="7"/>
       <c r="B751" s="25"/>
       <c r="C751" s="3"/>
@@ -19427,7 +19394,7 @@
       <c r="U751" s="1"/>
       <c r="V751" s="1"/>
     </row>
-    <row r="752" spans="1:22">
+    <row r="752" spans="1:22" ht="14.25">
       <c r="A752" s="7"/>
       <c r="B752" s="25"/>
       <c r="C752" s="3"/>
@@ -19451,7 +19418,7 @@
       <c r="U752" s="1"/>
       <c r="V752" s="1"/>
     </row>
-    <row r="753" spans="1:22">
+    <row r="753" spans="1:22" ht="14.25">
       <c r="A753" s="7"/>
       <c r="B753" s="25"/>
       <c r="C753" s="3"/>
@@ -19475,7 +19442,7 @@
       <c r="U753" s="1"/>
       <c r="V753" s="1"/>
     </row>
-    <row r="754" spans="1:22">
+    <row r="754" spans="1:22" ht="14.25">
       <c r="A754" s="7"/>
       <c r="B754" s="25"/>
       <c r="C754" s="3"/>
@@ -19499,7 +19466,7 @@
       <c r="U754" s="1"/>
       <c r="V754" s="1"/>
     </row>
-    <row r="755" spans="1:22">
+    <row r="755" spans="1:22" ht="14.25">
       <c r="A755" s="7"/>
       <c r="B755" s="25"/>
       <c r="C755" s="3"/>
@@ -19523,7 +19490,7 @@
       <c r="U755" s="1"/>
       <c r="V755" s="1"/>
     </row>
-    <row r="756" spans="1:22">
+    <row r="756" spans="1:22" ht="14.25">
       <c r="A756" s="7"/>
       <c r="B756" s="25"/>
       <c r="C756" s="3"/>
@@ -19547,7 +19514,7 @@
       <c r="U756" s="1"/>
       <c r="V756" s="1"/>
     </row>
-    <row r="757" spans="1:22">
+    <row r="757" spans="1:22" ht="14.25">
       <c r="A757" s="7"/>
       <c r="B757" s="25"/>
       <c r="C757" s="3"/>
@@ -19571,7 +19538,7 @@
       <c r="U757" s="1"/>
       <c r="V757" s="1"/>
     </row>
-    <row r="758" spans="1:22">
+    <row r="758" spans="1:22" ht="14.25">
       <c r="A758" s="7"/>
       <c r="B758" s="25"/>
       <c r="C758" s="3"/>
@@ -19595,7 +19562,7 @@
       <c r="U758" s="1"/>
       <c r="V758" s="1"/>
     </row>
-    <row r="759" spans="1:22">
+    <row r="759" spans="1:22" ht="14.25">
       <c r="A759" s="7"/>
       <c r="B759" s="25"/>
       <c r="C759" s="3"/>
@@ -19619,7 +19586,7 @@
       <c r="U759" s="1"/>
       <c r="V759" s="1"/>
     </row>
-    <row r="760" spans="1:22">
+    <row r="760" spans="1:22" ht="14.25">
       <c r="A760" s="7"/>
       <c r="B760" s="25"/>
       <c r="C760" s="3"/>
@@ -19643,7 +19610,7 @@
       <c r="U760" s="1"/>
       <c r="V760" s="1"/>
     </row>
-    <row r="761" spans="1:22">
+    <row r="761" spans="1:22" ht="14.25">
       <c r="A761" s="7"/>
       <c r="B761" s="25"/>
       <c r="C761" s="3"/>
@@ -19667,7 +19634,7 @@
       <c r="U761" s="1"/>
       <c r="V761" s="1"/>
     </row>
-    <row r="762" spans="1:22">
+    <row r="762" spans="1:22" ht="14.25">
       <c r="A762" s="7"/>
       <c r="B762" s="25"/>
       <c r="C762" s="3"/>
@@ -19691,7 +19658,7 @@
       <c r="U762" s="1"/>
       <c r="V762" s="1"/>
     </row>
-    <row r="763" spans="1:22">
+    <row r="763" spans="1:22" ht="14.25">
       <c r="A763" s="7"/>
       <c r="B763" s="25"/>
       <c r="C763" s="3"/>
@@ -19715,7 +19682,7 @@
       <c r="U763" s="1"/>
       <c r="V763" s="1"/>
     </row>
-    <row r="764" spans="1:22">
+    <row r="764" spans="1:22" ht="14.25">
       <c r="A764" s="7"/>
       <c r="B764" s="25"/>
       <c r="C764" s="3"/>
@@ -19739,7 +19706,7 @@
       <c r="U764" s="1"/>
       <c r="V764" s="1"/>
     </row>
-    <row r="765" spans="1:22">
+    <row r="765" spans="1:22" ht="14.25">
       <c r="A765" s="7"/>
       <c r="B765" s="25"/>
       <c r="C765" s="3"/>
@@ -19763,7 +19730,7 @@
       <c r="U765" s="1"/>
       <c r="V765" s="1"/>
     </row>
-    <row r="766" spans="1:22">
+    <row r="766" spans="1:22" ht="14.25">
       <c r="A766" s="7"/>
       <c r="B766" s="25"/>
       <c r="C766" s="3"/>
@@ -19787,7 +19754,7 @@
       <c r="U766" s="1"/>
       <c r="V766" s="1"/>
     </row>
-    <row r="767" spans="1:22">
+    <row r="767" spans="1:22" ht="14.25">
       <c r="A767" s="7"/>
       <c r="B767" s="25"/>
       <c r="C767" s="3"/>
@@ -19811,7 +19778,7 @@
       <c r="U767" s="1"/>
       <c r="V767" s="1"/>
     </row>
-    <row r="768" spans="1:22">
+    <row r="768" spans="1:22" ht="14.25">
       <c r="A768" s="7"/>
       <c r="B768" s="25"/>
       <c r="C768" s="3"/>
@@ -19835,7 +19802,7 @@
       <c r="U768" s="1"/>
       <c r="V768" s="1"/>
     </row>
-    <row r="769" spans="1:22">
+    <row r="769" spans="1:22" ht="14.25">
       <c r="A769" s="7"/>
       <c r="B769" s="25"/>
       <c r="C769" s="3"/>
@@ -19859,7 +19826,7 @@
       <c r="U769" s="1"/>
       <c r="V769" s="1"/>
     </row>
-    <row r="770" spans="1:22">
+    <row r="770" spans="1:22" ht="14.25">
       <c r="A770" s="7"/>
       <c r="B770" s="25"/>
       <c r="C770" s="3"/>
@@ -19883,7 +19850,7 @@
       <c r="U770" s="1"/>
       <c r="V770" s="1"/>
     </row>
-    <row r="771" spans="1:22">
+    <row r="771" spans="1:22" ht="14.25">
       <c r="A771" s="7"/>
       <c r="B771" s="25"/>
       <c r="C771" s="3"/>
@@ -19907,7 +19874,7 @@
       <c r="U771" s="1"/>
       <c r="V771" s="1"/>
     </row>
-    <row r="772" spans="1:22">
+    <row r="772" spans="1:22" ht="14.25">
       <c r="A772" s="7"/>
       <c r="B772" s="25"/>
       <c r="C772" s="3"/>
@@ -19931,7 +19898,7 @@
       <c r="U772" s="1"/>
       <c r="V772" s="1"/>
     </row>
-    <row r="773" spans="1:22">
+    <row r="773" spans="1:22" ht="14.25">
       <c r="A773" s="7"/>
       <c r="B773" s="25"/>
       <c r="C773" s="3"/>
@@ -19955,7 +19922,7 @@
       <c r="U773" s="1"/>
       <c r="V773" s="1"/>
     </row>
-    <row r="774" spans="1:22">
+    <row r="774" spans="1:22" ht="14.25">
       <c r="A774" s="7"/>
       <c r="B774" s="25"/>
       <c r="C774" s="3"/>
@@ -19979,7 +19946,7 @@
       <c r="U774" s="1"/>
       <c r="V774" s="1"/>
     </row>
-    <row r="775" spans="1:22">
+    <row r="775" spans="1:22" ht="14.25">
       <c r="A775" s="7"/>
       <c r="B775" s="25"/>
       <c r="C775" s="3"/>
@@ -20003,7 +19970,7 @@
       <c r="U775" s="1"/>
       <c r="V775" s="1"/>
     </row>
-    <row r="776" spans="1:22">
+    <row r="776" spans="1:22" ht="14.25">
       <c r="A776" s="7"/>
       <c r="B776" s="25"/>
       <c r="C776" s="3"/>
@@ -20027,7 +19994,7 @@
       <c r="U776" s="1"/>
       <c r="V776" s="1"/>
     </row>
-    <row r="777" spans="1:22">
+    <row r="777" spans="1:22" ht="14.25">
       <c r="A777" s="7"/>
       <c r="B777" s="25"/>
       <c r="C777" s="3"/>
@@ -20051,7 +20018,7 @@
       <c r="U777" s="1"/>
       <c r="V777" s="1"/>
     </row>
-    <row r="778" spans="1:22">
+    <row r="778" spans="1:22" ht="14.25">
       <c r="A778" s="7"/>
       <c r="B778" s="25"/>
       <c r="C778" s="3"/>
@@ -20075,7 +20042,7 @@
       <c r="U778" s="1"/>
       <c r="V778" s="1"/>
     </row>
-    <row r="779" spans="1:22">
+    <row r="779" spans="1:22" ht="14.25">
       <c r="A779" s="7"/>
       <c r="B779" s="25"/>
       <c r="C779" s="3"/>
@@ -20099,7 +20066,7 @@
       <c r="U779" s="1"/>
       <c r="V779" s="1"/>
     </row>
-    <row r="780" spans="1:22">
+    <row r="780" spans="1:22" ht="14.25">
       <c r="A780" s="7"/>
       <c r="B780" s="25"/>
       <c r="C780" s="3"/>
@@ -20123,7 +20090,7 @@
       <c r="U780" s="1"/>
       <c r="V780" s="1"/>
     </row>
-    <row r="781" spans="1:22">
+    <row r="781" spans="1:22" ht="14.25">
       <c r="A781" s="7"/>
       <c r="B781" s="25"/>
       <c r="C781" s="3"/>
@@ -20147,7 +20114,7 @@
       <c r="U781" s="1"/>
       <c r="V781" s="1"/>
     </row>
-    <row r="782" spans="1:22">
+    <row r="782" spans="1:22" ht="14.25">
       <c r="A782" s="7"/>
       <c r="B782" s="25"/>
       <c r="C782" s="3"/>
@@ -20171,7 +20138,7 @@
       <c r="U782" s="1"/>
       <c r="V782" s="1"/>
     </row>
-    <row r="783" spans="1:22">
+    <row r="783" spans="1:22" ht="14.25">
       <c r="A783" s="7"/>
       <c r="B783" s="25"/>
       <c r="C783" s="3"/>
@@ -20195,7 +20162,7 @@
       <c r="U783" s="1"/>
       <c r="V783" s="1"/>
     </row>
-    <row r="784" spans="1:22">
+    <row r="784" spans="1:22" ht="14.25">
       <c r="A784" s="7"/>
       <c r="B784" s="25"/>
       <c r="C784" s="3"/>
@@ -20219,7 +20186,7 @@
       <c r="U784" s="1"/>
       <c r="V784" s="1"/>
     </row>
-    <row r="785" spans="1:22">
+    <row r="785" spans="1:22" ht="14.25">
       <c r="A785" s="7"/>
       <c r="B785" s="25"/>
       <c r="C785" s="3"/>
@@ -20243,7 +20210,7 @@
       <c r="U785" s="1"/>
       <c r="V785" s="1"/>
     </row>
-    <row r="786" spans="1:22">
+    <row r="786" spans="1:22" ht="14.25">
       <c r="A786" s="7"/>
       <c r="B786" s="25"/>
       <c r="C786" s="3"/>
@@ -20267,7 +20234,7 @@
       <c r="U786" s="1"/>
       <c r="V786" s="1"/>
     </row>
-    <row r="787" spans="1:22">
+    <row r="787" spans="1:22" ht="14.25">
       <c r="A787" s="7"/>
       <c r="B787" s="25"/>
       <c r="C787" s="3"/>
@@ -20291,7 +20258,7 @@
       <c r="U787" s="1"/>
       <c r="V787" s="1"/>
     </row>
-    <row r="788" spans="1:22">
+    <row r="788" spans="1:22" ht="14.25">
       <c r="A788" s="7"/>
       <c r="B788" s="25"/>
       <c r="C788" s="3"/>
@@ -20315,7 +20282,7 @@
       <c r="U788" s="1"/>
       <c r="V788" s="1"/>
     </row>
-    <row r="789" spans="1:22">
+    <row r="789" spans="1:22" ht="14.25">
       <c r="A789" s="7"/>
       <c r="B789" s="25"/>
       <c r="C789" s="3"/>
@@ -20339,7 +20306,7 @@
       <c r="U789" s="1"/>
       <c r="V789" s="1"/>
     </row>
-    <row r="790" spans="1:22">
+    <row r="790" spans="1:22" ht="14.25">
       <c r="A790" s="7"/>
       <c r="B790" s="25"/>
       <c r="C790" s="3"/>
@@ -20363,7 +20330,7 @@
       <c r="U790" s="1"/>
       <c r="V790" s="1"/>
     </row>
-    <row r="791" spans="1:22">
+    <row r="791" spans="1:22" ht="14.25">
       <c r="A791" s="7"/>
       <c r="B791" s="25"/>
       <c r="C791" s="3"/>
@@ -20387,7 +20354,7 @@
       <c r="U791" s="1"/>
       <c r="V791" s="1"/>
     </row>
-    <row r="792" spans="1:22">
+    <row r="792" spans="1:22" ht="14.25">
       <c r="A792" s="7"/>
       <c r="B792" s="25"/>
       <c r="C792" s="3"/>
@@ -20411,7 +20378,7 @@
       <c r="U792" s="1"/>
       <c r="V792" s="1"/>
     </row>
-    <row r="793" spans="1:22">
+    <row r="793" spans="1:22" ht="14.25">
       <c r="A793" s="7"/>
       <c r="B793" s="25"/>
       <c r="C793" s="3"/>
@@ -20435,7 +20402,7 @@
       <c r="U793" s="1"/>
       <c r="V793" s="1"/>
     </row>
-    <row r="794" spans="1:22">
+    <row r="794" spans="1:22" ht="14.25">
       <c r="A794" s="7"/>
       <c r="B794" s="25"/>
       <c r="C794" s="3"/>
@@ -20459,7 +20426,7 @@
       <c r="U794" s="1"/>
       <c r="V794" s="1"/>
     </row>
-    <row r="795" spans="1:22">
+    <row r="795" spans="1:22" ht="14.25">
       <c r="A795" s="7"/>
       <c r="B795" s="25"/>
       <c r="C795" s="3"/>
@@ -20483,7 +20450,7 @@
       <c r="U795" s="1"/>
       <c r="V795" s="1"/>
     </row>
-    <row r="796" spans="1:22">
+    <row r="796" spans="1:22" ht="14.25">
       <c r="A796" s="7"/>
       <c r="B796" s="25"/>
       <c r="C796" s="3"/>
@@ -20507,7 +20474,7 @@
       <c r="U796" s="1"/>
       <c r="V796" s="1"/>
     </row>
-    <row r="797" spans="1:22">
+    <row r="797" spans="1:22" ht="14.25">
       <c r="A797" s="7"/>
       <c r="B797" s="25"/>
       <c r="C797" s="3"/>
@@ -20531,7 +20498,7 @@
       <c r="U797" s="1"/>
       <c r="V797" s="1"/>
     </row>
-    <row r="798" spans="1:22">
+    <row r="798" spans="1:22" ht="14.25">
       <c r="A798" s="7"/>
       <c r="B798" s="25"/>
       <c r="C798" s="3"/>
@@ -20555,7 +20522,7 @@
       <c r="U798" s="1"/>
       <c r="V798" s="1"/>
     </row>
-    <row r="799" spans="1:22">
+    <row r="799" spans="1:22" ht="14.25">
       <c r="A799" s="7"/>
       <c r="B799" s="25"/>
       <c r="C799" s="3"/>
@@ -20579,7 +20546,7 @@
       <c r="U799" s="1"/>
       <c r="V799" s="1"/>
     </row>
-    <row r="800" spans="1:22">
+    <row r="800" spans="1:22" ht="14.25">
       <c r="A800" s="7"/>
       <c r="B800" s="25"/>
       <c r="C800" s="3"/>
@@ -20603,7 +20570,7 @@
       <c r="U800" s="1"/>
       <c r="V800" s="1"/>
     </row>
-    <row r="801" spans="1:22">
+    <row r="801" spans="1:22" ht="14.25">
       <c r="A801" s="7"/>
       <c r="B801" s="25"/>
       <c r="C801" s="3"/>
@@ -20627,7 +20594,7 @@
       <c r="U801" s="1"/>
       <c r="V801" s="1"/>
     </row>
-    <row r="802" spans="1:22">
+    <row r="802" spans="1:22" ht="14.25">
       <c r="A802" s="7"/>
       <c r="B802" s="25"/>
       <c r="C802" s="3"/>
@@ -20651,7 +20618,7 @@
       <c r="U802" s="1"/>
       <c r="V802" s="1"/>
     </row>
-    <row r="803" spans="1:22">
+    <row r="803" spans="1:22" ht="14.25">
       <c r="A803" s="7"/>
       <c r="B803" s="25"/>
       <c r="C803" s="3"/>
@@ -20675,7 +20642,7 @@
       <c r="U803" s="1"/>
       <c r="V803" s="1"/>
     </row>
-    <row r="804" spans="1:22">
+    <row r="804" spans="1:22" ht="14.25">
       <c r="A804" s="7"/>
       <c r="B804" s="25"/>
       <c r="C804" s="3"/>
@@ -20699,7 +20666,7 @@
       <c r="U804" s="1"/>
       <c r="V804" s="1"/>
     </row>
-    <row r="805" spans="1:22">
+    <row r="805" spans="1:22" ht="14.25">
       <c r="A805" s="7"/>
       <c r="B805" s="25"/>
       <c r="C805" s="3"/>
@@ -20723,7 +20690,7 @@
       <c r="U805" s="1"/>
       <c r="V805" s="1"/>
     </row>
-    <row r="806" spans="1:22">
+    <row r="806" spans="1:22" ht="14.25">
       <c r="A806" s="7"/>
       <c r="B806" s="25"/>
       <c r="C806" s="3"/>
@@ -20747,7 +20714,7 @@
       <c r="U806" s="1"/>
       <c r="V806" s="1"/>
     </row>
-    <row r="807" spans="1:22">
+    <row r="807" spans="1:22" ht="14.25">
       <c r="A807" s="7"/>
       <c r="B807" s="25"/>
       <c r="C807" s="3"/>
@@ -20771,7 +20738,7 @@
       <c r="U807" s="1"/>
       <c r="V807" s="1"/>
     </row>
-    <row r="808" spans="1:22">
+    <row r="808" spans="1:22" ht="14.25">
       <c r="A808" s="7"/>
       <c r="B808" s="25"/>
       <c r="C808" s="3"/>
@@ -20795,7 +20762,7 @@
       <c r="U808" s="1"/>
       <c r="V808" s="1"/>
     </row>
-    <row r="809" spans="1:22">
+    <row r="809" spans="1:22" ht="14.25">
       <c r="A809" s="7"/>
       <c r="B809" s="25"/>
       <c r="C809" s="3"/>
@@ -20819,7 +20786,7 @@
       <c r="U809" s="1"/>
       <c r="V809" s="1"/>
     </row>
-    <row r="810" spans="1:22">
+    <row r="810" spans="1:22" ht="14.25">
       <c r="A810" s="7"/>
       <c r="B810" s="25"/>
       <c r="C810" s="3"/>
@@ -20843,7 +20810,7 @@
       <c r="U810" s="1"/>
       <c r="V810" s="1"/>
     </row>
-    <row r="811" spans="1:22">
+    <row r="811" spans="1:22" ht="14.25">
       <c r="A811" s="7"/>
       <c r="B811" s="25"/>
       <c r="C811" s="3"/>
@@ -20867,7 +20834,7 @@
       <c r="U811" s="1"/>
       <c r="V811" s="1"/>
     </row>
-    <row r="812" spans="1:22">
+    <row r="812" spans="1:22" ht="14.25">
       <c r="A812" s="7"/>
       <c r="B812" s="25"/>
       <c r="C812" s="3"/>
@@ -20891,7 +20858,7 @@
       <c r="U812" s="1"/>
       <c r="V812" s="1"/>
     </row>
-    <row r="813" spans="1:22">
+    <row r="813" spans="1:22" ht="14.25">
       <c r="A813" s="7"/>
       <c r="B813" s="25"/>
       <c r="C813" s="3"/>
@@ -20915,7 +20882,7 @@
       <c r="U813" s="1"/>
       <c r="V813" s="1"/>
     </row>
-    <row r="814" spans="1:22">
+    <row r="814" spans="1:22" ht="14.25">
       <c r="A814" s="7"/>
       <c r="B814" s="25"/>
       <c r="C814" s="3"/>
@@ -20939,7 +20906,7 @@
       <c r="U814" s="1"/>
       <c r="V814" s="1"/>
     </row>
-    <row r="815" spans="1:22">
+    <row r="815" spans="1:22" ht="14.25">
       <c r="A815" s="7"/>
       <c r="B815" s="25"/>
       <c r="C815" s="3"/>
@@ -20963,7 +20930,7 @@
       <c r="U815" s="1"/>
       <c r="V815" s="1"/>
     </row>
-    <row r="816" spans="1:22">
+    <row r="816" spans="1:22" ht="14.25">
       <c r="A816" s="7"/>
       <c r="B816" s="25"/>
       <c r="C816" s="3"/>
@@ -20987,7 +20954,7 @@
       <c r="U816" s="1"/>
       <c r="V816" s="1"/>
     </row>
-    <row r="817" spans="1:22">
+    <row r="817" spans="1:22" ht="14.25">
       <c r="A817" s="7"/>
       <c r="B817" s="25"/>
       <c r="C817" s="3"/>
@@ -21011,7 +20978,7 @@
       <c r="U817" s="1"/>
       <c r="V817" s="1"/>
     </row>
-    <row r="818" spans="1:22">
+    <row r="818" spans="1:22" ht="14.25">
       <c r="A818" s="7"/>
       <c r="B818" s="25"/>
       <c r="C818" s="3"/>
@@ -21035,7 +21002,7 @@
       <c r="U818" s="1"/>
       <c r="V818" s="1"/>
     </row>
-    <row r="819" spans="1:22">
+    <row r="819" spans="1:22" ht="14.25">
       <c r="A819" s="7"/>
       <c r="B819" s="25"/>
       <c r="C819" s="3"/>
@@ -21059,7 +21026,7 @@
       <c r="U819" s="1"/>
       <c r="V819" s="1"/>
     </row>
-    <row r="820" spans="1:22">
+    <row r="820" spans="1:22" ht="14.25">
       <c r="A820" s="7"/>
       <c r="B820" s="25"/>
       <c r="C820" s="3"/>
@@ -21083,7 +21050,7 @@
       <c r="U820" s="1"/>
       <c r="V820" s="1"/>
     </row>
-    <row r="821" spans="1:22">
+    <row r="821" spans="1:22" ht="14.25">
       <c r="A821" s="7"/>
       <c r="B821" s="25"/>
       <c r="C821" s="3"/>
@@ -21107,7 +21074,7 @@
       <c r="U821" s="1"/>
       <c r="V821" s="1"/>
     </row>
-    <row r="822" spans="1:22">
+    <row r="822" spans="1:22" ht="14.25">
       <c r="A822" s="7"/>
       <c r="B822" s="25"/>
       <c r="C822" s="3"/>
@@ -21131,7 +21098,7 @@
       <c r="U822" s="1"/>
       <c r="V822" s="1"/>
     </row>
-    <row r="823" spans="1:22">
+    <row r="823" spans="1:22" ht="14.25">
       <c r="A823" s="7"/>
       <c r="B823" s="25"/>
       <c r="C823" s="3"/>
@@ -21155,7 +21122,7 @@
       <c r="U823" s="1"/>
       <c r="V823" s="1"/>
     </row>
-    <row r="824" spans="1:22">
+    <row r="824" spans="1:22" ht="14.25">
       <c r="A824" s="7"/>
       <c r="B824" s="25"/>
       <c r="C824" s="3"/>
@@ -21179,7 +21146,7 @@
       <c r="U824" s="1"/>
       <c r="V824" s="1"/>
     </row>
-    <row r="825" spans="1:22">
+    <row r="825" spans="1:22" ht="14.25">
       <c r="A825" s="7"/>
       <c r="B825" s="25"/>
       <c r="C825" s="3"/>
@@ -21203,7 +21170,7 @@
       <c r="U825" s="1"/>
       <c r="V825" s="1"/>
     </row>
-    <row r="826" spans="1:22">
+    <row r="826" spans="1:22" ht="14.25">
       <c r="A826" s="7"/>
       <c r="B826" s="25"/>
       <c r="C826" s="3"/>
@@ -21227,7 +21194,7 @@
       <c r="U826" s="1"/>
       <c r="V826" s="1"/>
     </row>
-    <row r="827" spans="1:22">
+    <row r="827" spans="1:22" ht="14.25">
       <c r="A827" s="7"/>
       <c r="B827" s="25"/>
       <c r="C827" s="3"/>
@@ -21251,7 +21218,7 @@
       <c r="U827" s="1"/>
       <c r="V827" s="1"/>
     </row>
-    <row r="828" spans="1:22">
+    <row r="828" spans="1:22" ht="14.25">
       <c r="A828" s="7"/>
       <c r="B828" s="25"/>
       <c r="C828" s="3"/>
@@ -21275,7 +21242,7 @@
       <c r="U828" s="1"/>
       <c r="V828" s="1"/>
     </row>
-    <row r="829" spans="1:22">
+    <row r="829" spans="1:22" ht="14.25">
       <c r="A829" s="7"/>
       <c r="B829" s="25"/>
       <c r="C829" s="3"/>
@@ -21299,7 +21266,7 @@
       <c r="U829" s="1"/>
       <c r="V829" s="1"/>
     </row>
-    <row r="830" spans="1:22">
+    <row r="830" spans="1:22" ht="14.25">
       <c r="A830" s="7"/>
       <c r="B830" s="25"/>
       <c r="C830" s="3"/>
@@ -21323,7 +21290,7 @@
       <c r="U830" s="1"/>
       <c r="V830" s="1"/>
     </row>
-    <row r="831" spans="1:22">
+    <row r="831" spans="1:22" ht="14.25">
       <c r="A831" s="7"/>
       <c r="B831" s="25"/>
       <c r="C831" s="3"/>
@@ -21347,7 +21314,7 @@
       <c r="U831" s="1"/>
       <c r="V831" s="1"/>
     </row>
-    <row r="832" spans="1:22">
+    <row r="832" spans="1:22" ht="14.25">
       <c r="A832" s="7"/>
       <c r="B832" s="25"/>
       <c r="C832" s="3"/>
@@ -21371,7 +21338,7 @@
       <c r="U832" s="1"/>
       <c r="V832" s="1"/>
     </row>
-    <row r="833" spans="1:22">
+    <row r="833" spans="1:22" ht="14.25">
       <c r="A833" s="7"/>
       <c r="B833" s="25"/>
       <c r="C833" s="3"/>
@@ -21395,7 +21362,7 @@
       <c r="U833" s="1"/>
       <c r="V833" s="1"/>
     </row>
-    <row r="834" spans="1:22">
+    <row r="834" spans="1:22" ht="14.25">
       <c r="A834" s="7"/>
       <c r="B834" s="25"/>
       <c r="C834" s="3"/>
@@ -21419,7 +21386,7 @@
       <c r="U834" s="1"/>
       <c r="V834" s="1"/>
     </row>
-    <row r="835" spans="1:22">
+    <row r="835" spans="1:22" ht="14.25">
       <c r="A835" s="7"/>
       <c r="B835" s="25"/>
       <c r="C835" s="3"/>
@@ -21443,7 +21410,7 @@
       <c r="U835" s="1"/>
       <c r="V835" s="1"/>
     </row>
-    <row r="836" spans="1:22">
+    <row r="836" spans="1:22" ht="14.25">
       <c r="A836" s="7"/>
       <c r="B836" s="25"/>
       <c r="C836" s="3"/>
@@ -21467,7 +21434,7 @@
       <c r="U836" s="1"/>
       <c r="V836" s="1"/>
     </row>
-    <row r="837" spans="1:22">
+    <row r="837" spans="1:22" ht="14.25">
       <c r="A837" s="7"/>
       <c r="B837" s="25"/>
       <c r="C837" s="3"/>
@@ -21491,7 +21458,7 @@
       <c r="U837" s="1"/>
       <c r="V837" s="1"/>
     </row>
-    <row r="838" spans="1:22">
+    <row r="838" spans="1:22" ht="14.25">
       <c r="A838" s="7"/>
       <c r="B838" s="25"/>
       <c r="C838" s="3"/>
@@ -21515,7 +21482,7 @@
       <c r="U838" s="1"/>
       <c r="V838" s="1"/>
     </row>
-    <row r="839" spans="1:22">
+    <row r="839" spans="1:22" ht="14.25">
       <c r="A839" s="7"/>
       <c r="B839" s="25"/>
       <c r="C839" s="3"/>
@@ -21539,7 +21506,7 @@
       <c r="U839" s="1"/>
       <c r="V839" s="1"/>
     </row>
-    <row r="840" spans="1:22">
+    <row r="840" spans="1:22" ht="14.25">
       <c r="A840" s="7"/>
       <c r="B840" s="25"/>
       <c r="C840" s="3"/>
@@ -21563,7 +21530,7 @@
       <c r="U840" s="1"/>
       <c r="V840" s="1"/>
     </row>
-    <row r="841" spans="1:22">
+    <row r="841" spans="1:22" ht="14.25">
       <c r="A841" s="7"/>
       <c r="B841" s="25"/>
       <c r="C841" s="3"/>
@@ -21587,7 +21554,7 @@
       <c r="U841" s="1"/>
       <c r="V841" s="1"/>
     </row>
-    <row r="842" spans="1:22">
+    <row r="842" spans="1:22" ht="14.25">
       <c r="A842" s="7"/>
       <c r="B842" s="25"/>
       <c r="C842" s="3"/>
@@ -21611,7 +21578,7 @@
       <c r="U842" s="1"/>
       <c r="V842" s="1"/>
     </row>
-    <row r="843" spans="1:22">
+    <row r="843" spans="1:22" ht="14.25">
       <c r="A843" s="7"/>
       <c r="B843" s="25"/>
       <c r="C843" s="3"/>
@@ -21635,7 +21602,7 @@
       <c r="U843" s="1"/>
       <c r="V843" s="1"/>
     </row>
-    <row r="844" spans="1:22">
+    <row r="844" spans="1:22" ht="14.25">
       <c r="A844" s="7"/>
       <c r="B844" s="25"/>
       <c r="C844" s="3"/>
@@ -21659,7 +21626,7 @@
       <c r="U844" s="1"/>
       <c r="V844" s="1"/>
     </row>
-    <row r="845" spans="1:22">
+    <row r="845" spans="1:22" ht="14.25">
       <c r="A845" s="7"/>
       <c r="B845" s="25"/>
       <c r="C845" s="3"/>
@@ -21683,7 +21650,7 @@
       <c r="U845" s="1"/>
       <c r="V845" s="1"/>
     </row>
-    <row r="846" spans="1:22">
+    <row r="846" spans="1:22" ht="14.25">
       <c r="A846" s="7"/>
       <c r="B846" s="25"/>
       <c r="C846" s="3"/>
@@ -21707,7 +21674,7 @@
       <c r="U846" s="1"/>
       <c r="V846" s="1"/>
     </row>
-    <row r="847" spans="1:22">
+    <row r="847" spans="1:22" ht="14.25">
       <c r="A847" s="7"/>
       <c r="B847" s="25"/>
       <c r="C847" s="3"/>
@@ -21731,7 +21698,7 @@
       <c r="U847" s="1"/>
       <c r="V847" s="1"/>
     </row>
-    <row r="848" spans="1:22">
+    <row r="848" spans="1:22" ht="14.25">
       <c r="A848" s="7"/>
       <c r="B848" s="25"/>
       <c r="C848" s="3"/>
@@ -21755,7 +21722,7 @@
       <c r="U848" s="1"/>
       <c r="V848" s="1"/>
     </row>
-    <row r="849" spans="1:22">
+    <row r="849" spans="1:22" ht="14.25">
       <c r="A849" s="7"/>
       <c r="B849" s="25"/>
       <c r="C849" s="3"/>
@@ -21779,7 +21746,7 @@
       <c r="U849" s="1"/>
       <c r="V849" s="1"/>
     </row>
-    <row r="850" spans="1:22">
+    <row r="850" spans="1:22" ht="14.25">
       <c r="A850" s="7"/>
       <c r="B850" s="25"/>
       <c r="C850" s="3"/>
@@ -21803,7 +21770,7 @@
       <c r="U850" s="1"/>
       <c r="V850" s="1"/>
     </row>
-    <row r="851" spans="1:22">
+    <row r="851" spans="1:22" ht="14.25">
       <c r="A851" s="7"/>
       <c r="B851" s="25"/>
       <c r="C851" s="3"/>
@@ -21827,7 +21794,7 @@
       <c r="U851" s="1"/>
       <c r="V851" s="1"/>
     </row>
-    <row r="852" spans="1:22">
+    <row r="852" spans="1:22" ht="14.25">
       <c r="A852" s="7"/>
       <c r="B852" s="25"/>
       <c r="C852" s="3"/>
@@ -21851,7 +21818,7 @@
       <c r="U852" s="1"/>
       <c r="V852" s="1"/>
     </row>
-    <row r="853" spans="1:22">
+    <row r="853" spans="1:22" ht="14.25">
       <c r="A853" s="7"/>
       <c r="B853" s="25"/>
       <c r="C853" s="3"/>
@@ -21875,7 +21842,7 @@
       <c r="U853" s="1"/>
       <c r="V853" s="1"/>
     </row>
-    <row r="854" spans="1:22">
+    <row r="854" spans="1:22" ht="14.25">
       <c r="A854" s="7"/>
       <c r="B854" s="25"/>
       <c r="C854" s="3"/>
@@ -21899,7 +21866,7 @@
       <c r="U854" s="1"/>
       <c r="V854" s="1"/>
     </row>
-    <row r="855" spans="1:22">
+    <row r="855" spans="1:22" ht="14.25">
       <c r="A855" s="7"/>
       <c r="B855" s="25"/>
       <c r="C855" s="3"/>
@@ -21923,7 +21890,7 @@
       <c r="U855" s="1"/>
       <c r="V855" s="1"/>
     </row>
-    <row r="856" spans="1:22">
+    <row r="856" spans="1:22" ht="14.25">
       <c r="A856" s="7"/>
       <c r="B856" s="25"/>
       <c r="C856" s="3"/>
@@ -21947,7 +21914,7 @@
       <c r="U856" s="1"/>
       <c r="V856" s="1"/>
     </row>
-    <row r="857" spans="1:22">
+    <row r="857" spans="1:22" ht="14.25">
       <c r="A857" s="7"/>
       <c r="B857" s="25"/>
       <c r="C857" s="3"/>
@@ -21971,7 +21938,7 @@
       <c r="U857" s="1"/>
       <c r="V857" s="1"/>
     </row>
-    <row r="858" spans="1:22">
+    <row r="858" spans="1:22" ht="14.25">
       <c r="A858" s="7"/>
       <c r="B858" s="25"/>
       <c r="C858" s="3"/>
@@ -21995,7 +21962,7 @@
       <c r="U858" s="1"/>
       <c r="V858" s="1"/>
     </row>
-    <row r="859" spans="1:22">
+    <row r="859" spans="1:22" ht="14.25">
       <c r="A859" s="7"/>
       <c r="B859" s="25"/>
       <c r="C859" s="3"/>
@@ -22019,7 +21986,7 @@
       <c r="U859" s="1"/>
       <c r="V859" s="1"/>
     </row>
-    <row r="860" spans="1:22">
+    <row r="860" spans="1:22" ht="14.25">
       <c r="A860" s="7"/>
       <c r="B860" s="25"/>
       <c r="C860" s="3"/>
@@ -22043,7 +22010,7 @@
       <c r="U860" s="1"/>
       <c r="V860" s="1"/>
     </row>
-    <row r="861" spans="1:22">
+    <row r="861" spans="1:22" ht="14.25">
       <c r="A861" s="7"/>
       <c r="B861" s="25"/>
       <c r="C861" s="3"/>
@@ -22067,7 +22034,7 @@
       <c r="U861" s="1"/>
       <c r="V861" s="1"/>
     </row>
-    <row r="862" spans="1:22">
+    <row r="862" spans="1:22" ht="14.25">
       <c r="A862" s="7"/>
       <c r="B862" s="25"/>
       <c r="C862" s="3"/>
@@ -22091,7 +22058,7 @@
       <c r="U862" s="1"/>
       <c r="V862" s="1"/>
     </row>
-    <row r="863" spans="1:22">
+    <row r="863" spans="1:22" ht="14.25">
       <c r="A863" s="7"/>
       <c r="B863" s="25"/>
       <c r="C863" s="3"/>
@@ -22115,7 +22082,7 @@
       <c r="U863" s="1"/>
       <c r="V863" s="1"/>
     </row>
-    <row r="864" spans="1:22">
+    <row r="864" spans="1:22" ht="14.25">
       <c r="A864" s="7"/>
       <c r="B864" s="25"/>
       <c r="C864" s="3"/>
@@ -22139,7 +22106,7 @@
       <c r="U864" s="1"/>
       <c r="V864" s="1"/>
     </row>
-    <row r="865" spans="1:22">
+    <row r="865" spans="1:22" ht="14.25">
       <c r="A865" s="7"/>
       <c r="B865" s="25"/>
       <c r="C865" s="3"/>
@@ -22163,7 +22130,7 @@
       <c r="U865" s="1"/>
       <c r="V865" s="1"/>
     </row>
-    <row r="866" spans="1:22">
+    <row r="866" spans="1:22" ht="14.25">
       <c r="A866" s="7"/>
       <c r="B866" s="25"/>
       <c r="C866" s="3"/>
@@ -22187,7 +22154,7 @@
       <c r="U866" s="1"/>
       <c r="V866" s="1"/>
     </row>
-    <row r="867" spans="1:22">
+    <row r="867" spans="1:22" ht="14.25">
       <c r="A867" s="7"/>
       <c r="B867" s="25"/>
       <c r="C867" s="3"/>
@@ -22211,7 +22178,7 @@
       <c r="U867" s="1"/>
       <c r="V867" s="1"/>
     </row>
-    <row r="868" spans="1:22">
+    <row r="868" spans="1:22" ht="14.25">
       <c r="A868" s="7"/>
       <c r="B868" s="25"/>
       <c r="C868" s="3"/>
@@ -22235,7 +22202,7 @@
       <c r="U868" s="1"/>
       <c r="V868" s="1"/>
     </row>
-    <row r="869" spans="1:22">
+    <row r="869" spans="1:22" ht="14.25">
       <c r="A869" s="7"/>
       <c r="B869" s="25"/>
       <c r="C869" s="3"/>
@@ -22259,7 +22226,7 @@
       <c r="U869" s="1"/>
       <c r="V869" s="1"/>
     </row>
-    <row r="870" spans="1:22">
+    <row r="870" spans="1:22" ht="14.25">
       <c r="A870" s="7"/>
       <c r="B870" s="25"/>
       <c r="C870" s="3"/>
@@ -22283,7 +22250,7 @@
       <c r="U870" s="1"/>
       <c r="V870" s="1"/>
     </row>
-    <row r="871" spans="1:22">
+    <row r="871" spans="1:22" ht="14.25">
       <c r="A871" s="7"/>
       <c r="B871" s="25"/>
       <c r="C871" s="3"/>
@@ -22307,7 +22274,7 @@
       <c r="U871" s="1"/>
       <c r="V871" s="1"/>
     </row>
-    <row r="872" spans="1:22">
+    <row r="872" spans="1:22" ht="14.25">
       <c r="A872" s="7"/>
       <c r="B872" s="25"/>
       <c r="C872" s="3"/>
@@ -22331,7 +22298,7 @@
       <c r="U872" s="1"/>
       <c r="V872" s="1"/>
     </row>
-    <row r="873" spans="1:22">
+    <row r="873" spans="1:22" ht="14.25">
       <c r="A873" s="7"/>
       <c r="B873" s="25"/>
       <c r="C873" s="3"/>
@@ -22355,7 +22322,7 @@
       <c r="U873" s="1"/>
       <c r="V873" s="1"/>
     </row>
-    <row r="874" spans="1:22">
+    <row r="874" spans="1:22" ht="14.25">
       <c r="A874" s="7"/>
       <c r="B874" s="25"/>
       <c r="C874" s="3"/>
@@ -22379,7 +22346,7 @@
       <c r="U874" s="1"/>
       <c r="V874" s="1"/>
     </row>
-    <row r="875" spans="1:22">
+    <row r="875" spans="1:22" ht="14.25">
       <c r="A875" s="7"/>
       <c r="B875" s="25"/>
       <c r="C875" s="3"/>
@@ -22403,7 +22370,7 @@
       <c r="U875" s="1"/>
       <c r="V875" s="1"/>
     </row>
-    <row r="876" spans="1:22">
+    <row r="876" spans="1:22" ht="14.25">
       <c r="A876" s="7"/>
       <c r="B876" s="25"/>
       <c r="C876" s="3"/>
@@ -22427,7 +22394,7 @@
       <c r="U876" s="1"/>
       <c r="V876" s="1"/>
     </row>
-    <row r="877" spans="1:22">
+    <row r="877" spans="1:22" ht="14.25">
       <c r="A877" s="7"/>
       <c r="B877" s="25"/>
       <c r="C877" s="3"/>
@@ -22451,7 +22418,7 @@
       <c r="U877" s="1"/>
       <c r="V877" s="1"/>
     </row>
-    <row r="878" spans="1:22">
+    <row r="878" spans="1:22" ht="14.25">
       <c r="A878" s="7"/>
       <c r="B878" s="25"/>
       <c r="C878" s="3"/>
@@ -22475,7 +22442,7 @@
       <c r="U878" s="1"/>
       <c r="V878" s="1"/>
     </row>
-    <row r="879" spans="1:22">
+    <row r="879" spans="1:22" ht="14.25">
       <c r="A879" s="7"/>
       <c r="B879" s="25"/>
       <c r="C879" s="3"/>
@@ -22499,7 +22466,7 @@
       <c r="U879" s="1"/>
       <c r="V879" s="1"/>
     </row>
-    <row r="880" spans="1:22">
+    <row r="880" spans="1:22" ht="14.25">
       <c r="A880" s="7"/>
       <c r="B880" s="25"/>
       <c r="C880" s="3"/>
@@ -22523,7 +22490,7 @@
       <c r="U880" s="1"/>
       <c r="V880" s="1"/>
     </row>
-    <row r="881" spans="1:22">
+    <row r="881" spans="1:22" ht="14.25">
       <c r="A881" s="7"/>
       <c r="B881" s="25"/>
       <c r="C881" s="3"/>
@@ -22547,7 +22514,7 @@
       <c r="U881" s="1"/>
       <c r="V881" s="1"/>
     </row>
-    <row r="882" spans="1:22">
+    <row r="882" spans="1:22" ht="14.25">
       <c r="A882" s="7"/>
       <c r="B882" s="25"/>
       <c r="C882" s="3"/>
@@ -22571,7 +22538,7 @@
       <c r="U882" s="1"/>
       <c r="V882" s="1"/>
     </row>
-    <row r="883" spans="1:22">
+    <row r="883" spans="1:22" ht="14.25">
       <c r="A883" s="7"/>
       <c r="B883" s="25"/>
       <c r="C883" s="3"/>
@@ -22595,7 +22562,7 @@
       <c r="U883" s="1"/>
       <c r="V883" s="1"/>
     </row>
-    <row r="884" spans="1:22">
+    <row r="884" spans="1:22" ht="14.25">
       <c r="A884" s="7"/>
       <c r="B884" s="25"/>
       <c r="C884" s="3"/>
@@ -22619,7 +22586,7 @@
       <c r="U884" s="1"/>
       <c r="V884" s="1"/>
     </row>
-    <row r="885" spans="1:22">
+    <row r="885" spans="1:22" ht="14.25">
       <c r="A885" s="7"/>
       <c r="B885" s="25"/>
       <c r="C885" s="3"/>
@@ -22643,7 +22610,7 @@
       <c r="U885" s="1"/>
       <c r="V885" s="1"/>
     </row>
-    <row r="886" spans="1:22">
+    <row r="886" spans="1:22" ht="14.25">
       <c r="A886" s="7"/>
       <c r="B886" s="25"/>
       <c r="C886" s="3"/>
@@ -22667,7 +22634,7 @@
       <c r="U886" s="1"/>
       <c r="V886" s="1"/>
     </row>
-    <row r="887" spans="1:22">
+    <row r="887" spans="1:22" ht="14.25">
       <c r="A887" s="7"/>
       <c r="B887" s="25"/>
       <c r="C887" s="3"/>
@@ -22691,7 +22658,7 @@
       <c r="U887" s="1"/>
       <c r="V887" s="1"/>
     </row>
-    <row r="888" spans="1:22">
+    <row r="888" spans="1:22" ht="14.25">
       <c r="A888" s="7"/>
       <c r="B888" s="25"/>
       <c r="C888" s="3"/>
@@ -22715,7 +22682,7 @@
       <c r="U888" s="1"/>
       <c r="V888" s="1"/>
     </row>
-    <row r="889" spans="1:22">
+    <row r="889" spans="1:22" ht="14.25">
       <c r="A889" s="7"/>
       <c r="B889" s="25"/>
       <c r="C889" s="3"/>
@@ -22739,7 +22706,7 @@
       <c r="U889" s="1"/>
       <c r="V889" s="1"/>
     </row>
-    <row r="890" spans="1:22">
+    <row r="890" spans="1:22" ht="14.25">
       <c r="A890" s="7"/>
       <c r="B890" s="25"/>
       <c r="C890" s="3"/>
@@ -22763,7 +22730,7 @@
       <c r="U890" s="1"/>
       <c r="V890" s="1"/>
     </row>
-    <row r="891" spans="1:22">
+    <row r="891" spans="1:22" ht="14.25">
       <c r="A891" s="7"/>
       <c r="B891" s="25"/>
       <c r="C891" s="3"/>
@@ -22787,7 +22754,7 @@
       <c r="U891" s="1"/>
       <c r="V891" s="1"/>
     </row>
-    <row r="892" spans="1:22">
+    <row r="892" spans="1:22" ht="14.25">
       <c r="A892" s="7"/>
       <c r="B892" s="25"/>
       <c r="C892" s="3"/>
@@ -22811,7 +22778,7 @@
       <c r="U892" s="1"/>
       <c r="V892" s="1"/>
     </row>
-    <row r="893" spans="1:22">
+    <row r="893" spans="1:22" ht="14.25">
       <c r="A893" s="7"/>
       <c r="B893" s="25"/>
       <c r="C893" s="3"/>
@@ -22835,7 +22802,7 @@
       <c r="U893" s="1"/>
       <c r="V893" s="1"/>
     </row>
-    <row r="894" spans="1:22">
+    <row r="894" spans="1:22" ht="14.25">
       <c r="A894" s="7"/>
       <c r="B894" s="25"/>
       <c r="C894" s="3"/>
@@ -22859,7 +22826,7 @@
       <c r="U894" s="1"/>
       <c r="V894" s="1"/>
     </row>
-    <row r="895" spans="1:22">
+    <row r="895" spans="1:22" ht="14.25">
       <c r="A895" s="7"/>
       <c r="B895" s="25"/>
       <c r="C895" s="3"/>
@@ -22883,7 +22850,7 @@
       <c r="U895" s="1"/>
       <c r="V895" s="1"/>
     </row>
-    <row r="896" spans="1:22">
+    <row r="896" spans="1:22" ht="14.25">
       <c r="A896" s="7"/>
       <c r="B896" s="25"/>
       <c r="C896" s="3"/>
@@ -22907,7 +22874,7 @@
       <c r="U896" s="1"/>
       <c r="V896" s="1"/>
     </row>
-    <row r="897" spans="1:22">
+    <row r="897" spans="1:22" ht="14.25">
       <c r="A897" s="7"/>
       <c r="B897" s="25"/>
       <c r="C897" s="3"/>
@@ -22931,7 +22898,7 @@
       <c r="U897" s="1"/>
       <c r="V897" s="1"/>
     </row>
-    <row r="898" spans="1:22">
+    <row r="898" spans="1:22" ht="14.25">
       <c r="A898" s="7"/>
       <c r="B898" s="25"/>
       <c r="C898" s="3"/>
@@ -22955,7 +22922,7 @@
       <c r="U898" s="1"/>
       <c r="V898" s="1"/>
     </row>
-    <row r="899" spans="1:22">
+    <row r="899" spans="1:22" ht="14.25">
       <c r="A899" s="7"/>
       <c r="B899" s="25"/>
       <c r="C899" s="3"/>
@@ -22979,7 +22946,7 @@
       <c r="U899" s="1"/>
       <c r="V899" s="1"/>
     </row>
-    <row r="900" spans="1:22">
+    <row r="900" spans="1:22" ht="14.25">
       <c r="A900" s="7"/>
       <c r="B900" s="25"/>
       <c r="C900" s="3"/>
@@ -23003,7 +22970,7 @@
       <c r="U900" s="1"/>
       <c r="V900" s="1"/>
     </row>
-    <row r="901" spans="1:22">
+    <row r="901" spans="1:22" ht="14.25">
       <c r="A901" s="7"/>
       <c r="B901" s="25"/>
       <c r="C901" s="3"/>
@@ -23027,7 +22994,7 @@
       <c r="U901" s="1"/>
       <c r="V901" s="1"/>
     </row>
-    <row r="902" spans="1:22">
+    <row r="902" spans="1:22" ht="14.25">
       <c r="A902" s="7"/>
       <c r="B902" s="25"/>
       <c r="C902" s="3"/>
@@ -23051,7 +23018,7 @@
       <c r="U902" s="1"/>
       <c r="V902" s="1"/>
     </row>
-    <row r="903" spans="1:22">
+    <row r="903" spans="1:22" ht="14.25">
       <c r="A903" s="7"/>
       <c r="B903" s="25"/>
       <c r="C903" s="3"/>
@@ -23075,7 +23042,7 @@
       <c r="U903" s="1"/>
       <c r="V903" s="1"/>
     </row>
-    <row r="904" spans="1:22">
+    <row r="904" spans="1:22" ht="14.25">
       <c r="A904" s="7"/>
       <c r="B904" s="25"/>
       <c r="C904" s="3"/>
@@ -23099,7 +23066,7 @@
       <c r="U904" s="1"/>
       <c r="V904" s="1"/>
     </row>
-    <row r="905" spans="1:22">
+    <row r="905" spans="1:22" ht="14.25">
       <c r="A905" s="7"/>
       <c r="B905" s="25"/>
       <c r="C905" s="3"/>
@@ -23123,7 +23090,7 @@
       <c r="U905" s="1"/>
       <c r="V905" s="1"/>
     </row>
-    <row r="906" spans="1:22">
+    <row r="906" spans="1:22" ht="14.25">
       <c r="A906" s="7"/>
       <c r="B906" s="25"/>
       <c r="C906" s="3"/>
@@ -23147,7 +23114,7 @@
       <c r="U906" s="1"/>
       <c r="V906" s="1"/>
     </row>
-    <row r="907" spans="1:22">
+    <row r="907" spans="1:22" ht="14.25">
       <c r="A907" s="7"/>
       <c r="B907" s="25"/>
       <c r="C907" s="3"/>
@@ -23171,7 +23138,7 @@
       <c r="U907" s="1"/>
       <c r="V907" s="1"/>
     </row>
-    <row r="908" spans="1:22">
+    <row r="908" spans="1:22" ht="14.25">
       <c r="A908" s="7"/>
       <c r="B908" s="25"/>
       <c r="C908" s="3"/>
@@ -23195,7 +23162,7 @@
       <c r="U908" s="1"/>
       <c r="V908" s="1"/>
     </row>
-    <row r="909" spans="1:22">
+    <row r="909" spans="1:22" ht="14.25">
       <c r="A909" s="7"/>
       <c r="B909" s="25"/>
       <c r="C909" s="3"/>
@@ -23219,7 +23186,7 @@
       <c r="U909" s="1"/>
       <c r="V909" s="1"/>
     </row>
-    <row r="910" spans="1:22">
+    <row r="910" spans="1:22" ht="14.25">
       <c r="A910" s="7"/>
       <c r="B910" s="25"/>
       <c r="C910" s="3"/>
@@ -23243,7 +23210,7 @@
       <c r="U910" s="1"/>
       <c r="V910" s="1"/>
     </row>
-    <row r="911" spans="1:22">
+    <row r="911" spans="1:22" ht="14.25">
       <c r="A911" s="7"/>
       <c r="B911" s="25"/>
       <c r="C911" s="3"/>
@@ -23267,7 +23234,7 @@
       <c r="U911" s="1"/>
       <c r="V911" s="1"/>
     </row>
-    <row r="912" spans="1:22">
+    <row r="912" spans="1:22" ht="14.25">
       <c r="A912" s="7"/>
       <c r="B912" s="25"/>
       <c r="C912" s="3"/>
@@ -23291,7 +23258,7 @@
       <c r="U912" s="1"/>
       <c r="V912" s="1"/>
     </row>
-    <row r="913" spans="1:22">
+    <row r="913" spans="1:22" ht="14.25">
       <c r="A913" s="7"/>
       <c r="B913" s="25"/>
       <c r="C913" s="3"/>
@@ -23315,7 +23282,7 @@
       <c r="U913" s="1"/>
       <c r="V913" s="1"/>
     </row>
-    <row r="914" spans="1:22">
+    <row r="914" spans="1:22" ht="14.25">
       <c r="A914" s="7"/>
       <c r="B914" s="25"/>
       <c r="C914" s="3"/>
@@ -23339,7 +23306,7 @@
       <c r="U914" s="1"/>
       <c r="V914" s="1"/>
     </row>
-    <row r="915" spans="1:22">
+    <row r="915" spans="1:22" ht="14.25">
       <c r="A915" s="7"/>
       <c r="B915" s="25"/>
       <c r="C915" s="3"/>
@@ -23363,7 +23330,7 @@
       <c r="U915" s="1"/>
       <c r="V915" s="1"/>
     </row>
-    <row r="916" spans="1:22">
+    <row r="916" spans="1:22" ht="14.25">
       <c r="A916" s="7"/>
       <c r="B916" s="25"/>
       <c r="C916" s="3"/>
@@ -23387,7 +23354,7 @@
       <c r="U916" s="1"/>
       <c r="V916" s="1"/>
     </row>
-    <row r="917" spans="1:22">
+    <row r="917" spans="1:22" ht="14.25">
       <c r="A917" s="7"/>
       <c r="B917" s="25"/>
       <c r="C917" s="3"/>
@@ -23411,7 +23378,7 @@
       <c r="U917" s="1"/>
       <c r="V917" s="1"/>
     </row>
-    <row r="918" spans="1:22">
+    <row r="918" spans="1:22" ht="14.25">
       <c r="A918" s="7"/>
       <c r="B918" s="25"/>
       <c r="C918" s="3"/>
@@ -23435,7 +23402,7 @@
       <c r="U918" s="1"/>
       <c r="V918" s="1"/>
     </row>
-    <row r="919" spans="1:22">
+    <row r="919" spans="1:22" ht="14.25">
       <c r="A919" s="7"/>
       <c r="B919" s="25"/>
       <c r="C919" s="3"/>
@@ -23459,7 +23426,7 @@
       <c r="U919" s="1"/>
       <c r="V919" s="1"/>
     </row>
-    <row r="920" spans="1:22">
+    <row r="920" spans="1:22" ht="14.25">
       <c r="A920" s="7"/>
       <c r="B920" s="25"/>
       <c r="C920" s="3"/>
@@ -23483,7 +23450,7 @@
       <c r="U920" s="1"/>
       <c r="V920" s="1"/>
     </row>
-    <row r="921" spans="1:22">
+    <row r="921" spans="1:22" ht="14.25">
       <c r="A921" s="7"/>
       <c r="B921" s="25"/>
       <c r="C921" s="3"/>
@@ -23507,7 +23474,7 @@
       <c r="U921" s="1"/>
       <c r="V921" s="1"/>
     </row>
-    <row r="922" spans="1:22">
+    <row r="922" spans="1:22" ht="14.25">
       <c r="A922" s="7"/>
       <c r="B922" s="25"/>
       <c r="C922" s="3"/>
@@ -23531,7 +23498,7 @@
       <c r="U922" s="1"/>
       <c r="V922" s="1"/>
     </row>
-    <row r="923" spans="1:22">
+    <row r="923" spans="1:22" ht="14.25">
       <c r="A923" s="7"/>
       <c r="B923" s="25"/>
       <c r="C923" s="3"/>
@@ -23555,7 +23522,7 @@
       <c r="U923" s="1"/>
       <c r="V923" s="1"/>
     </row>
-    <row r="924" spans="1:22">
+    <row r="924" spans="1:22" ht="14.25">
       <c r="A924" s="7"/>
       <c r="B924" s="25"/>
       <c r="C924" s="3"/>
@@ -23579,7 +23546,7 @@
       <c r="U924" s="1"/>
       <c r="V924" s="1"/>
     </row>
-    <row r="925" spans="1:22">
+    <row r="925" spans="1:22" ht="14.25">
       <c r="A925" s="7"/>
       <c r="B925" s="25"/>
       <c r="C925" s="3"/>
@@ -23603,7 +23570,7 @@
       <c r="U925" s="1"/>
       <c r="V925" s="1"/>
     </row>
-    <row r="926" spans="1:22">
+    <row r="926" spans="1:22" ht="14.25">
       <c r="A926" s="7"/>
       <c r="B926" s="25"/>
       <c r="C926" s="3"/>
@@ -23627,7 +23594,7 @@
       <c r="U926" s="1"/>
       <c r="V926" s="1"/>
     </row>
-    <row r="927" spans="1:22">
+    <row r="927" spans="1:22" ht="14.25">
       <c r="A927" s="7"/>
       <c r="B927" s="25"/>
       <c r="C927" s="3"/>
@@ -23651,7 +23618,7 @@
       <c r="U927" s="1"/>
       <c r="V927" s="1"/>
     </row>
-    <row r="928" spans="1:22">
+    <row r="928" spans="1:22" ht="14.25">
       <c r="A928" s="7"/>
       <c r="B928" s="25"/>
       <c r="C928" s="3"/>
@@ -23675,7 +23642,7 @@
       <c r="U928" s="1"/>
       <c r="V928" s="1"/>
     </row>
-    <row r="929" spans="1:22">
+    <row r="929" spans="1:22" ht="14.25">
       <c r="A929" s="7"/>
       <c r="B929" s="25"/>
       <c r="C929" s="3"/>
@@ -23699,7 +23666,7 @@
       <c r="U929" s="1"/>
       <c r="V929" s="1"/>
     </row>
-    <row r="930" spans="1:22">
+    <row r="930" spans="1:22" ht="14.25">
       <c r="A930" s="7"/>
       <c r="B930" s="25"/>
       <c r="C930" s="3"/>
@@ -23723,7 +23690,7 @@
       <c r="U930" s="1"/>
       <c r="V930" s="1"/>
     </row>
-    <row r="931" spans="1:22">
+    <row r="931" spans="1:22" ht="14.25">
       <c r="A931" s="7"/>
       <c r="B931" s="25"/>
       <c r="C931" s="3"/>
@@ -23747,7 +23714,7 @@
       <c r="U931" s="1"/>
       <c r="V931" s="1"/>
     </row>
-    <row r="932" spans="1:22">
+    <row r="932" spans="1:22" ht="14.25">
       <c r="A932" s="7"/>
       <c r="B932" s="25"/>
       <c r="C932" s="3"/>
@@ -23771,7 +23738,7 @@
       <c r="U932" s="1"/>
       <c r="V932" s="1"/>
     </row>
-    <row r="933" spans="1:22">
+    <row r="933" spans="1:22" ht="14.25">
       <c r="A933" s="7"/>
       <c r="B933" s="25"/>
       <c r="C933" s="3"/>
@@ -23795,7 +23762,7 @@
       <c r="U933" s="1"/>
       <c r="V933" s="1"/>
     </row>
-    <row r="934" spans="1:22">
+    <row r="934" spans="1:22" ht="14.25">
       <c r="A934" s="7"/>
       <c r="B934" s="25"/>
       <c r="C934" s="3"/>
@@ -23819,7 +23786,7 @@
       <c r="U934" s="1"/>
       <c r="V934" s="1"/>
     </row>
-    <row r="935" spans="1:22">
+    <row r="935" spans="1:22" ht="14.25">
       <c r="A935" s="7"/>
       <c r="B935" s="25"/>
       <c r="C935" s="3"/>
@@ -23843,7 +23810,7 @@
       <c r="U935" s="1"/>
       <c r="V935" s="1"/>
     </row>
-    <row r="936" spans="1:22">
+    <row r="936" spans="1:22" ht="14.25">
       <c r="A936" s="7"/>
       <c r="B936" s="25"/>
       <c r="C936" s="3"/>
@@ -23867,7 +23834,7 @@
       <c r="U936" s="1"/>
       <c r="V936" s="1"/>
     </row>
-    <row r="937" spans="1:22">
+    <row r="937" spans="1:22" ht="14.25">
       <c r="A937" s="7"/>
       <c r="B937" s="25"/>
       <c r="C937" s="3"/>
@@ -23891,7 +23858,7 @@
       <c r="U937" s="1"/>
       <c r="V937" s="1"/>
     </row>
-    <row r="938" spans="1:22">
+    <row r="938" spans="1:22" ht="14.25">
       <c r="A938" s="7"/>
       <c r="B938" s="25"/>
       <c r="C938" s="3"/>
@@ -23915,7 +23882,7 @@
       <c r="U938" s="1"/>
       <c r="V938" s="1"/>
     </row>
-    <row r="939" spans="1:22">
+    <row r="939" spans="1:22" ht="14.25">
       <c r="A939" s="7"/>
       <c r="B939" s="25"/>
       <c r="C939" s="3"/>
@@ -23939,7 +23906,7 @@
       <c r="U939" s="1"/>
       <c r="V939" s="1"/>
     </row>
-    <row r="940" spans="1:22">
+    <row r="940" spans="1:22" ht="14.25">
       <c r="A940" s="7"/>
       <c r="B940" s="25"/>
       <c r="C940" s="3"/>
@@ -23963,7 +23930,7 @@
       <c r="U940" s="1"/>
       <c r="V940" s="1"/>
     </row>
-    <row r="941" spans="1:22">
+    <row r="941" spans="1:22" ht="14.25">
       <c r="A941" s="7"/>
       <c r="B941" s="25"/>
       <c r="C941" s="3"/>
@@ -23987,7 +23954,7 @@
       <c r="U941" s="1"/>
       <c r="V941" s="1"/>
     </row>
-    <row r="942" spans="1:22">
+    <row r="942" spans="1:22" ht="14.25">
       <c r="A942" s="7"/>
       <c r="B942" s="25"/>
       <c r="C942" s="3"/>
@@ -24011,7 +23978,7 @@
       <c r="U942" s="1"/>
       <c r="V942" s="1"/>
     </row>
-    <row r="943" spans="1:22">
+    <row r="943" spans="1:22" ht="14.25">
       <c r="A943" s="7"/>
       <c r="B943" s="25"/>
       <c r="C943" s="3"/>
@@ -24035,7 +24002,7 @@
       <c r="U943" s="1"/>
       <c r="V943" s="1"/>
     </row>
-    <row r="944" spans="1:22">
+    <row r="944" spans="1:22" ht="14.25">
       <c r="A944" s="7"/>
       <c r="B944" s="25"/>
       <c r="C944" s="3"/>
@@ -24059,7 +24026,7 @@
       <c r="U944" s="1"/>
       <c r="V944" s="1"/>
     </row>
-    <row r="945" spans="1:22">
+    <row r="945" spans="1:22" ht="14.25">
       <c r="A945" s="7"/>
       <c r="B945" s="25"/>
       <c r="C945" s="3"/>
@@ -24083,7 +24050,7 @@
       <c r="U945" s="1"/>
       <c r="V945" s="1"/>
     </row>
-    <row r="946" spans="1:22">
+    <row r="946" spans="1:22" ht="14.25">
       <c r="A946" s="7"/>
       <c r="B946" s="25"/>
       <c r="C946" s="3"/>
@@ -24107,7 +24074,7 @@
       <c r="U946" s="1"/>
       <c r="V946" s="1"/>
     </row>
-    <row r="947" spans="1:22">
+    <row r="947" spans="1:22" ht="14.25">
       <c r="A947" s="7"/>
       <c r="B947" s="25"/>
       <c r="C947" s="3"/>
@@ -24131,7 +24098,7 @@
       <c r="U947" s="1"/>
       <c r="V947" s="1"/>
     </row>
-    <row r="948" spans="1:22">
+    <row r="948" spans="1:22" ht="14.25">
       <c r="A948" s="7"/>
       <c r="B948" s="25"/>
       <c r="C948" s="3"/>
@@ -24155,7 +24122,7 @@
       <c r="U948" s="1"/>
       <c r="V948" s="1"/>
     </row>
-    <row r="949" spans="1:22">
+    <row r="949" spans="1:22" ht="14.25">
       <c r="A949" s="7"/>
       <c r="B949" s="25"/>
       <c r="C949" s="3"/>
@@ -24179,7 +24146,7 @@
       <c r="U949" s="1"/>
       <c r="V949" s="1"/>
     </row>
-    <row r="950" spans="1:22">
+    <row r="950" spans="1:22" ht="14.25">
       <c r="A950" s="7"/>
       <c r="B950" s="25"/>
       <c r="C950" s="3"/>
@@ -24203,7 +24170,7 @@
       <c r="U950" s="1"/>
       <c r="V950" s="1"/>
     </row>
-    <row r="951" spans="1:22">
+    <row r="951" spans="1:22" ht="14.25">
       <c r="A951" s="7"/>
       <c r="B951" s="25"/>
       <c r="C951" s="3"/>
@@ -24227,7 +24194,7 @@
       <c r="U951" s="1"/>
       <c r="V951" s="1"/>
     </row>
-    <row r="952" spans="1:22">
+    <row r="952" spans="1:22" ht="14.25">
       <c r="A952" s="7"/>
       <c r="B952" s="25"/>
       <c r="C952" s="3"/>
@@ -24251,7 +24218,7 @@
       <c r="U952" s="1"/>
       <c r="V952" s="1"/>
     </row>
-    <row r="953" spans="1:22">
+    <row r="953" spans="1:22" ht="14.25">
       <c r="A953" s="7"/>
       <c r="B953" s="25"/>
       <c r="C953" s="3"/>
@@ -24275,7 +24242,7 @@
       <c r="U953" s="1"/>
       <c r="V953" s="1"/>
     </row>
-    <row r="954" spans="1:22">
+    <row r="954" spans="1:22" ht="14.25">
       <c r="A954" s="7"/>
       <c r="B954" s="25"/>
       <c r="C954" s="3"/>
@@ -24299,7 +24266,7 @@
       <c r="U954" s="1"/>
       <c r="V954" s="1"/>
     </row>
-    <row r="955" spans="1:22">
+    <row r="955" spans="1:22" ht="14.25">
       <c r="A955" s="7"/>
       <c r="B955" s="25"/>
       <c r="C955" s="3"/>
@@ -24323,7 +24290,7 @@
       <c r="U955" s="1"/>
       <c r="V955" s="1"/>
     </row>
-    <row r="956" spans="1:22">
+    <row r="956" spans="1:22" ht="14.25">
       <c r="A956" s="7"/>
       <c r="B956" s="25"/>
       <c r="C956" s="3"/>
@@ -24347,7 +24314,7 @@
       <c r="U956" s="1"/>
       <c r="V956" s="1"/>
     </row>
-    <row r="957" spans="1:22">
+    <row r="957" spans="1:22" ht="14.25">
       <c r="A957" s="7"/>
       <c r="B957" s="25"/>
       <c r="C957" s="3"/>
@@ -24371,7 +24338,7 @@
       <c r="U957" s="1"/>
       <c r="V957" s="1"/>
     </row>
-    <row r="958" spans="1:22">
+    <row r="958" spans="1:22" ht="14.25">
       <c r="A958" s="7"/>
       <c r="B958" s="25"/>
       <c r="C958" s="3"/>
@@ -24395,7 +24362,7 @@
       <c r="U958" s="1"/>
       <c r="V958" s="1"/>
     </row>
-    <row r="959" spans="1:22">
+    <row r="959" spans="1:22" ht="14.25">
       <c r="A959" s="7"/>
       <c r="B959" s="25"/>
       <c r="C959" s="3"/>
@@ -24419,7 +24386,7 @@
       <c r="U959" s="1"/>
       <c r="V959" s="1"/>
     </row>
-    <row r="960" spans="1:22">
+    <row r="960" spans="1:22" ht="14.25">
       <c r="A960" s="7"/>
       <c r="B960" s="25"/>
       <c r="C960" s="3"/>
@@ -24443,7 +24410,7 @@
       <c r="U960" s="1"/>
       <c r="V960" s="1"/>
     </row>
-    <row r="961" spans="1:22">
+    <row r="961" spans="1:22" ht="14.25">
       <c r="A961" s="7"/>
       <c r="B961" s="25"/>
       <c r="C961" s="3"/>
@@ -24467,7 +24434,7 @@
       <c r="U961" s="1"/>
       <c r="V961" s="1"/>
     </row>
-    <row r="962" spans="1:22">
+    <row r="962" spans="1:22" ht="14.25">
       <c r="A962" s="7"/>
       <c r="B962" s="25"/>
       <c r="C962" s="3"/>
@@ -24491,7 +24458,7 @@
       <c r="U962" s="1"/>
       <c r="V962" s="1"/>
     </row>
-    <row r="963" spans="1:22">
+    <row r="963" spans="1:22" ht="14.25">
       <c r="A963" s="7"/>
       <c r="B963" s="25"/>
       <c r="C963" s="3"/>
@@ -24515,7 +24482,7 @@
       <c r="U963" s="1"/>
       <c r="V963" s="1"/>
     </row>
-    <row r="964" spans="1:22">
+    <row r="964" spans="1:22" ht="14.25">
       <c r="A964" s="7"/>
       <c r="B964" s="25"/>
       <c r="C964" s="3"/>
@@ -24539,7 +24506,7 @@
       <c r="U964" s="1"/>
       <c r="V964" s="1"/>
     </row>
-    <row r="965" spans="1:22">
+    <row r="965" spans="1:22" ht="14.25">
       <c r="A965" s="7"/>
       <c r="B965" s="25"/>
       <c r="C965" s="3"/>
@@ -24563,7 +24530,7 @@
       <c r="U965" s="1"/>
       <c r="V965" s="1"/>
     </row>
-    <row r="966" spans="1:22">
+    <row r="966" spans="1:22" ht="14.25">
       <c r="A966" s="7"/>
       <c r="B966" s="25"/>
       <c r="C966" s="3"/>
@@ -24587,7 +24554,7 @@
       <c r="U966" s="1"/>
       <c r="V966" s="1"/>
     </row>
-    <row r="967" spans="1:22">
+    <row r="967" spans="1:22" ht="14.25">
       <c r="A967" s="7"/>
       <c r="B967" s="25"/>
       <c r="C967" s="3"/>
@@ -24611,7 +24578,7 @@
       <c r="U967" s="1"/>
       <c r="V967" s="1"/>
     </row>
-    <row r="968" spans="1:22">
+    <row r="968" spans="1:22" ht="14.25">
       <c r="A968" s="7"/>
       <c r="B968" s="25"/>
       <c r="C968" s="3"/>
@@ -24635,7 +24602,7 @@
       <c r="U968" s="1"/>
       <c r="V968" s="1"/>
     </row>
-    <row r="969" spans="1:22">
+    <row r="969" spans="1:22" ht="14.25">
       <c r="A969" s="7"/>
       <c r="B969" s="25"/>
       <c r="C969" s="3"/>
@@ -24659,7 +24626,7 @@
       <c r="U969" s="1"/>
       <c r="V969" s="1"/>
     </row>
-    <row r="970" spans="1:22">
+    <row r="970" spans="1:22" ht="14.25">
       <c r="A970" s="7"/>
       <c r="B970" s="25"/>
       <c r="C970" s="3"/>
@@ -24683,7 +24650,7 @@
       <c r="U970" s="1"/>
       <c r="V970" s="1"/>
     </row>
-    <row r="971" spans="1:22">
+    <row r="971" spans="1:22" ht="14.25">
       <c r="A971" s="7"/>
       <c r="B971" s="25"/>
       <c r="C971" s="3"/>
@@ -24707,7 +24674,7 @@
       <c r="U971" s="1"/>
       <c r="V971" s="1"/>
     </row>
-    <row r="972" spans="1:22">
+    <row r="972" spans="1:22" ht="14.25">
       <c r="A972" s="7"/>
       <c r="B972" s="25"/>
       <c r="C972" s="3"/>
@@ -24731,7 +24698,7 @@
       <c r="U972" s="1"/>
       <c r="V972" s="1"/>
     </row>
-    <row r="973" spans="1:22">
+    <row r="973" spans="1:22" ht="14.25">
       <c r="A973" s="7"/>
       <c r="B973" s="25"/>
       <c r="C973" s="3"/>
@@ -24755,7 +24722,7 @@
       <c r="U973" s="1"/>
       <c r="V973" s="1"/>
     </row>
-    <row r="974" spans="1:22">
+    <row r="974" spans="1:22" ht="14.25">
       <c r="A974" s="7"/>
       <c r="B974" s="25"/>
       <c r="C974" s="3"/>
@@ -24779,198 +24746,14 @@
       <c r="U974" s="1"/>
       <c r="V974" s="1"/>
     </row>
-    <row r="975" spans="1:22">
-      <c r="A975" s="7"/>
-      <c r="B975" s="25"/>
-      <c r="C975" s="3"/>
-      <c r="D975" s="1"/>
-      <c r="E975" s="1"/>
-      <c r="F975" s="1"/>
-      <c r="G975" s="1"/>
-      <c r="H975" s="1"/>
-      <c r="I975" s="1"/>
-      <c r="J975" s="1"/>
-      <c r="K975" s="1"/>
-      <c r="L975" s="1"/>
-      <c r="M975" s="1"/>
-      <c r="N975" s="1"/>
-      <c r="O975" s="1"/>
-      <c r="P975" s="1"/>
-      <c r="Q975" s="1"/>
-      <c r="R975" s="1"/>
-      <c r="S975" s="1"/>
-      <c r="T975" s="1"/>
-      <c r="U975" s="1"/>
-      <c r="V975" s="1"/>
-    </row>
-    <row r="976" spans="1:22">
-      <c r="A976" s="7"/>
-      <c r="B976" s="25"/>
-      <c r="C976" s="3"/>
-      <c r="D976" s="1"/>
-      <c r="E976" s="1"/>
-      <c r="F976" s="1"/>
-      <c r="G976" s="1"/>
-      <c r="H976" s="1"/>
-      <c r="I976" s="1"/>
-      <c r="J976" s="1"/>
-      <c r="K976" s="1"/>
-      <c r="L976" s="1"/>
-      <c r="M976" s="1"/>
-      <c r="N976" s="1"/>
-      <c r="O976" s="1"/>
-      <c r="P976" s="1"/>
-      <c r="Q976" s="1"/>
-      <c r="R976" s="1"/>
-      <c r="S976" s="1"/>
-      <c r="T976" s="1"/>
-      <c r="U976" s="1"/>
-      <c r="V976" s="1"/>
-    </row>
-    <row r="977" spans="1:22">
-      <c r="A977" s="7"/>
-      <c r="B977" s="25"/>
-      <c r="C977" s="3"/>
-      <c r="D977" s="1"/>
-      <c r="E977" s="1"/>
-      <c r="F977" s="1"/>
-      <c r="G977" s="1"/>
-      <c r="H977" s="1"/>
-      <c r="I977" s="1"/>
-      <c r="J977" s="1"/>
-      <c r="K977" s="1"/>
-      <c r="L977" s="1"/>
-      <c r="M977" s="1"/>
-      <c r="N977" s="1"/>
-      <c r="O977" s="1"/>
-      <c r="P977" s="1"/>
-      <c r="Q977" s="1"/>
-      <c r="R977" s="1"/>
-      <c r="S977" s="1"/>
-      <c r="T977" s="1"/>
-      <c r="U977" s="1"/>
-      <c r="V977" s="1"/>
-    </row>
-    <row r="978" spans="1:22">
-      <c r="A978" s="7"/>
-      <c r="B978" s="25"/>
-      <c r="C978" s="3"/>
-      <c r="D978" s="1"/>
-      <c r="E978" s="1"/>
-      <c r="F978" s="1"/>
-      <c r="G978" s="1"/>
-      <c r="H978" s="1"/>
-      <c r="I978" s="1"/>
-      <c r="J978" s="1"/>
-      <c r="K978" s="1"/>
-      <c r="L978" s="1"/>
-      <c r="M978" s="1"/>
-      <c r="N978" s="1"/>
-      <c r="O978" s="1"/>
-      <c r="P978" s="1"/>
-      <c r="Q978" s="1"/>
-      <c r="R978" s="1"/>
-      <c r="S978" s="1"/>
-      <c r="T978" s="1"/>
-      <c r="U978" s="1"/>
-      <c r="V978" s="1"/>
-    </row>
-    <row r="979" spans="1:22">
-      <c r="A979" s="7"/>
-      <c r="B979" s="25"/>
-      <c r="C979" s="3"/>
-      <c r="D979" s="1"/>
-      <c r="E979" s="1"/>
-      <c r="F979" s="1"/>
-      <c r="G979" s="1"/>
-      <c r="H979" s="1"/>
-      <c r="I979" s="1"/>
-      <c r="J979" s="1"/>
-      <c r="K979" s="1"/>
-      <c r="L979" s="1"/>
-      <c r="M979" s="1"/>
-      <c r="N979" s="1"/>
-      <c r="O979" s="1"/>
-      <c r="P979" s="1"/>
-      <c r="Q979" s="1"/>
-      <c r="R979" s="1"/>
-      <c r="S979" s="1"/>
-      <c r="T979" s="1"/>
-      <c r="U979" s="1"/>
-      <c r="V979" s="1"/>
-    </row>
-    <row r="980" spans="1:22">
-      <c r="A980" s="7"/>
-      <c r="B980" s="25"/>
-      <c r="C980" s="3"/>
-      <c r="D980" s="1"/>
-      <c r="E980" s="1"/>
-      <c r="F980" s="1"/>
-      <c r="G980" s="1"/>
-      <c r="H980" s="1"/>
-      <c r="I980" s="1"/>
-      <c r="J980" s="1"/>
-      <c r="K980" s="1"/>
-      <c r="L980" s="1"/>
-      <c r="M980" s="1"/>
-      <c r="N980" s="1"/>
-      <c r="O980" s="1"/>
-      <c r="P980" s="1"/>
-      <c r="Q980" s="1"/>
-      <c r="R980" s="1"/>
-      <c r="S980" s="1"/>
-      <c r="T980" s="1"/>
-      <c r="U980" s="1"/>
-      <c r="V980" s="1"/>
-    </row>
-    <row r="981" spans="1:22">
-      <c r="A981" s="7"/>
-      <c r="B981" s="25"/>
-      <c r="C981" s="3"/>
-      <c r="D981" s="1"/>
-      <c r="E981" s="1"/>
-      <c r="F981" s="1"/>
-      <c r="G981" s="1"/>
-      <c r="H981" s="1"/>
-      <c r="I981" s="1"/>
-      <c r="J981" s="1"/>
-      <c r="K981" s="1"/>
-      <c r="L981" s="1"/>
-      <c r="M981" s="1"/>
-      <c r="N981" s="1"/>
-      <c r="O981" s="1"/>
-      <c r="P981" s="1"/>
-      <c r="Q981" s="1"/>
-      <c r="R981" s="1"/>
-      <c r="S981" s="1"/>
-      <c r="T981" s="1"/>
-      <c r="U981" s="1"/>
-      <c r="V981" s="1"/>
-    </row>
-    <row r="982" spans="1:22">
-      <c r="A982" s="7"/>
-      <c r="B982" s="25"/>
-      <c r="C982" s="3"/>
-      <c r="D982" s="1"/>
-      <c r="E982" s="1"/>
-      <c r="F982" s="1"/>
-      <c r="G982" s="1"/>
-      <c r="H982" s="1"/>
-      <c r="I982" s="1"/>
-      <c r="J982" s="1"/>
-      <c r="K982" s="1"/>
-      <c r="L982" s="1"/>
-      <c r="M982" s="1"/>
-      <c r="N982" s="1"/>
-      <c r="O982" s="1"/>
-      <c r="P982" s="1"/>
-      <c r="Q982" s="1"/>
-      <c r="R982" s="1"/>
-      <c r="S982" s="1"/>
-      <c r="T982" s="1"/>
-      <c r="U982" s="1"/>
-      <c r="V982" s="1"/>
-    </row>
+    <row r="975" spans="1:22" ht="14.25"/>
+    <row r="976" spans="1:22" ht="14.25"/>
+    <row r="977" ht="14.25"/>
+    <row r="978" ht="14.25"/>
+    <row r="979" ht="14.25"/>
+    <row r="980" ht="14.25"/>
+    <row r="981" ht="14.25"/>
+    <row r="982" ht="14.25"/>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -24991,19 +24774,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100231ACC10D748F34BAA0C20ABFA72A7EA" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5b60ada5ef74d917189c377d37311689">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a56c8121-053f-455f-842b-cd566811d075" xmlns:ns3="76f06672-c643-4888-a225-c4422b0e89ee" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f62d863a5068cb9de04048c4fc264cf7" ns2:_="" ns3:_="">
-    <xsd:import namespace="a56c8121-053f-455f-842b-cd566811d075"/>
-    <xsd:import namespace="76f06672-c643-4888-a225-c4422b0e89ee"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F5D778AC6A79A84EAA5B25C5A2BFF7B6" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dba055ea2ef6f995fa2b93dd0ece404c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3cd0eaed-44fe-4f97-8632-c05a782ebbb7" xmlns:ns3="75164c79-2692-43d6-94a7-34b44bf80abd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f036b67ea408c255de0ae726e51a87d7" ns2:_="" ns3:_="">
+    <xsd:import namespace="3cd0eaed-44fe-4f97-8632-c05a782ebbb7"/>
+    <xsd:import namespace="75164c79-2692-43d6-94a7-34b44bf80abd"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -25012,11 +24786,11 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -25024,7 +24798,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a56c8121-053f-455f-842b-cd566811d075" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3cd0eaed-44fe-4f97-8632-c05a782ebbb7" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -25037,26 +24811,26 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="11" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="13" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="12" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="14" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="76f06672-c643-4888-a225-c4422b0e89ee" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="75164c79-2692-43d6-94a7-34b44bf80abd" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="13" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -25075,7 +24849,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="14" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -25182,6 +24956,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -25189,11 +24972,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AF01965-4B53-4043-B5ED-A531E4D3A7B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49834A2E-09C7-4BDB-ADFC-7D7BBA7484ED}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C37A5DE0-9FD1-4721-9C30-3A5B42A32EC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AF01965-4B53-4043-B5ED-A531E4D3A7B2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
